--- a/Design-Files/OFP_MCM_v1.6/BOM/Client-BOM-OFP_MCM_v1.6.xlsx
+++ b/Design-Files/OFP_MCM_v1.6/BOM/Client-BOM-OFP_MCM_v1.6.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\nabilfesal-smartmeter-hw\Design-Files\OFP_MCM_v1.6\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A98945-5294-4151-BCE5-7C6D46AA9351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="603">
   <si>
     <t>#</t>
   </si>
@@ -1802,18 +1806,6 @@
     <t>MyAntenna</t>
   </si>
   <si>
-    <t>FPC FFC Flexible Flat Cable Extension Board PCB Pitch 0.5 mm (40 Pin) Connector</t>
-  </si>
-  <si>
-    <t>CA-2660</t>
-  </si>
-  <si>
-    <t>RZCONNE</t>
-  </si>
-  <si>
-    <t>Aliexpress</t>
-  </si>
-  <si>
     <t>5 inch TFT LCD Display 800*480 RGB Interface LCD Touch Screen Panel</t>
   </si>
   <si>
@@ -1823,20 +1815,38 @@
     <t>QDTFT</t>
   </si>
   <si>
-    <t>Alibaba</t>
+    <t>Already Provided</t>
+  </si>
+  <si>
+    <t>FPC延长板 焊好2个0.5mm间距40p翻盖FPC连接器 组装 QWY(CN) RoHs</t>
+  </si>
+  <si>
+    <t>Moko Code: 12300000303070</t>
+  </si>
+  <si>
+    <t>LED SPACER MOUNTS for T-1 and T-13/4</t>
+  </si>
+  <si>
+    <t>Keystone</t>
+  </si>
+  <si>
+    <t>D15, D16, D17</t>
+  </si>
+  <si>
+    <t>TVS DIODE 3.3VWM 6.8VC SOD123F</t>
+  </si>
+  <si>
+    <t>SOD-123FL</t>
+  </si>
+  <si>
+    <t>SMF3.3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="32">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1925,160 +1935,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color indexed="12"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2097,194 +1955,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2375,266 +2047,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2677,9 +2094,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2704,71 +2118,27 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="0003A4CB"/>
-      <color rgb="002CD0B2"/>
+      <color rgb="FF03A4CB"/>
+      <color rgb="FF2CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3026,28 +2396,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K144"/>
+  <dimension ref="A1:K146"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.57142857142857" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7142857142857" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="23.1428571428571" customWidth="1"/>
-    <col min="7" max="7" width="27.2857142857143" customWidth="1"/>
-    <col min="8" max="8" width="20.8571428571429" customWidth="1"/>
-    <col min="9" max="9" width="8.14285714285714" customWidth="1"/>
-    <col min="10" max="10" width="9.28571428571429" customWidth="1"/>
-    <col min="11" max="11" width="27.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" customWidth="1"/>
+    <col min="11" max="11" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:11">
+    <row r="1" spans="1:11">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3056,11 +2427,11 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-    </row>
-    <row r="2" ht="15.75" spans="1:11">
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -3096,7 +2467,7 @@
     <row r="3" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="7">
-        <f>ROW(B3)-ROW($B$2)</f>
+        <f t="shared" ref="B3:B34" si="0">ROW(B3)-ROW($B$2)</f>
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -3125,10 +2496,10 @@
       </c>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" ht="15.75" spans="1:11">
+    <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="7">
-        <f>ROW(B4)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -3157,10 +2528,10 @@
       </c>
       <c r="K4" s="12"/>
     </row>
-    <row r="5" ht="24.75" spans="1:11">
+    <row r="5" spans="1:11" ht="24">
       <c r="A5" s="2"/>
       <c r="B5" s="7">
-        <f>ROW(B5)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -3189,10 +2560,10 @@
       </c>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" ht="48.75" spans="1:11">
+    <row r="6" spans="1:11" ht="48">
       <c r="A6" s="2"/>
       <c r="B6" s="7">
-        <f>ROW(B6)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C6" s="11" t="s">
@@ -3224,7 +2595,7 @@
     <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="7">
-        <f>ROW(B7)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -3253,10 +2624,10 @@
       </c>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" ht="24.75" spans="1:11">
+    <row r="8" spans="1:11" ht="24">
       <c r="A8" s="2"/>
       <c r="B8" s="7">
-        <f>ROW(B8)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -3288,7 +2659,7 @@
     <row r="9" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="7">
-        <f>ROW(B9)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C9" s="8" t="s">
@@ -3320,7 +2691,7 @@
     <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="7">
-        <f>ROW(B10)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C10" s="8" t="s">
@@ -3352,7 +2723,7 @@
     <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="7">
-        <f>ROW(B11)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C11" s="8" t="s">
@@ -3381,10 +2752,10 @@
       </c>
       <c r="K11" s="9"/>
     </row>
-    <row r="12" ht="24.75" spans="1:11">
+    <row r="12" spans="1:11" ht="24">
       <c r="A12" s="2"/>
       <c r="B12" s="7">
-        <f>ROW(B12)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -3413,10 +2784,10 @@
       </c>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" ht="15.75" spans="1:11">
+    <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="7">
-        <f>ROW(B13)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -3445,10 +2816,10 @@
       </c>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" ht="15.75" spans="1:11">
+    <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="7">
-        <f>ROW(B14)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C14" s="11" t="s">
@@ -3477,10 +2848,10 @@
       </c>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" ht="15.75" spans="1:11">
+    <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="7">
-        <f>ROW(B15)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -3509,10 +2880,10 @@
       </c>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" ht="15.75" spans="1:11">
+    <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="7">
-        <f>ROW(B16)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -3541,10 +2912,10 @@
       </c>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" ht="15.75" spans="1:11">
+    <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="7">
-        <f>ROW(B17)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C17" s="8" t="s">
@@ -3573,10 +2944,10 @@
       </c>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" ht="15.75" spans="1:11">
+    <row r="18" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="7">
-        <f>ROW(B18)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -3605,10 +2976,10 @@
       </c>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" ht="15.75" spans="1:11">
+    <row r="19" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="7">
-        <f>ROW(B19)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C19" s="8" t="s">
@@ -3637,10 +3008,10 @@
       </c>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" ht="15.75" spans="1:11">
+    <row r="20" spans="1:11">
       <c r="A20" s="2"/>
       <c r="B20" s="7">
-        <f>ROW(B20)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -3672,7 +3043,7 @@
     <row r="21" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="7">
-        <f>ROW(B21)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C21" s="8" t="s">
@@ -3704,7 +3075,7 @@
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="7">
-        <f>ROW(B22)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C22" s="11" t="s">
@@ -3736,7 +3107,7 @@
     <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="7">
-        <f>ROW(B23)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -3768,7 +3139,7 @@
     <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="7">
-        <f>ROW(B24)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C24" s="11" t="s">
@@ -3800,7 +3171,7 @@
     <row r="25" spans="1:11">
       <c r="A25" s="2"/>
       <c r="B25" s="7">
-        <f>ROW(B25)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C25" s="11" t="s">
@@ -3832,7 +3203,7 @@
     <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="7">
-        <f>ROW(B26)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C26" s="11" t="s">
@@ -3864,7 +3235,7 @@
     <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="7">
-        <f>ROW(B27)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -3896,7 +3267,7 @@
     <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="7">
-        <f>ROW(B28)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C28" s="11" t="s">
@@ -3928,7 +3299,7 @@
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="7">
-        <f>ROW(B29)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -3960,7 +3331,7 @@
     <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="7">
-        <f>ROW(B30)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C30" s="8" t="s">
@@ -3989,10 +3360,10 @@
       </c>
       <c r="K30" s="12"/>
     </row>
-    <row r="31" ht="15.75" spans="1:11">
+    <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="7">
-        <f>ROW(B31)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -4021,10 +3392,10 @@
       </c>
       <c r="K31" s="9"/>
     </row>
-    <row r="32" ht="15.75" spans="1:11">
+    <row r="32" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="7">
-        <f>ROW(B32)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C32" s="11" t="s">
@@ -4051,14 +3422,14 @@
       <c r="J32" s="14">
         <v>7</v>
       </c>
-      <c r="K32" s="17" t="s">
+      <c r="K32" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="33" ht="15.75" spans="1:11">
+    <row r="33" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="7">
-        <f>ROW(B33)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C33" s="8" t="s">
@@ -4085,14 +3456,14 @@
       <c r="J33" s="14">
         <v>1</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="K33" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="34" ht="24.75" spans="1:11">
+    <row r="34" spans="1:11" ht="36">
       <c r="A34" s="2"/>
       <c r="B34" s="7">
-        <f>ROW(B34)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C34" s="11" t="s">
@@ -4121,10 +3492,10 @@
       </c>
       <c r="K34" s="12"/>
     </row>
-    <row r="35" ht="24.75" spans="1:11">
+    <row r="35" spans="1:11" ht="24">
       <c r="A35" s="2"/>
       <c r="B35" s="7">
-        <f>ROW(B35)-ROW($B$2)</f>
+        <f t="shared" ref="B35:B67" si="1">ROW(B35)-ROW($B$2)</f>
         <v>33</v>
       </c>
       <c r="C35" s="8" t="s">
@@ -4153,10 +3524,10 @@
       </c>
       <c r="K35" s="9"/>
     </row>
-    <row r="36" ht="15.75" spans="1:11">
+    <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="7">
-        <f>ROW(B36)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="C36" s="11" t="s">
@@ -4183,14 +3554,14 @@
       <c r="J36" s="14">
         <v>1</v>
       </c>
-      <c r="K36" s="17" t="s">
+      <c r="K36" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="37" ht="24.75" spans="1:11">
+    <row r="37" spans="1:11" ht="24">
       <c r="A37" s="2"/>
       <c r="B37" s="7">
-        <f>ROW(B37)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -4219,10 +3590,10 @@
       </c>
       <c r="K37" s="9"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" ht="24">
       <c r="A38" s="2"/>
       <c r="B38" s="7">
-        <f>ROW(B38)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="C38" s="11" t="s">
@@ -4251,10 +3622,10 @@
       </c>
       <c r="K38" s="12"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" ht="15.75" thickBot="1">
       <c r="A39" s="2"/>
       <c r="B39" s="7">
-        <f>ROW(B39)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -4283,2016 +3654,2013 @@
       </c>
       <c r="K39" s="9"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" ht="15.75" thickBot="1">
       <c r="A40" s="2"/>
       <c r="B40" s="7">
-        <f>ROW(B40)-ROW($B$2)</f>
         <v>38</v>
       </c>
-      <c r="C40" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>15</v>
+      <c r="C40" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="I40" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="J40" s="12">
-        <v>2</v>
-      </c>
-      <c r="K40" s="12"/>
-    </row>
-    <row r="41" ht="36.75" spans="1:11">
+      <c r="J40" s="9">
+        <v>3</v>
+      </c>
+      <c r="K40" s="9"/>
+    </row>
+    <row r="41" spans="1:11" ht="15.75" thickBot="1">
       <c r="A41" s="2"/>
       <c r="B41" s="7">
-        <f>ROW(B41)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G41" s="10">
-        <v>5027740891</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>181</v>
+      <c r="C41" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="I41" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="J41" s="9">
-        <v>1</v>
-      </c>
-      <c r="K41" s="9"/>
-    </row>
-    <row r="42" ht="48.75" spans="1:11">
+      <c r="J41" s="12">
+        <v>2</v>
+      </c>
+      <c r="K41" s="12"/>
+    </row>
+    <row r="42" spans="1:11" ht="36">
       <c r="A42" s="2"/>
       <c r="B42" s="7">
-        <f>ROW(B42)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="C42" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>184</v>
+      <c r="C42" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>180</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G42" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>186</v>
+      <c r="G42" s="10">
+        <v>5027740891</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="I42" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="J42" s="12">
-        <v>1</v>
-      </c>
-      <c r="K42" s="12"/>
-    </row>
-    <row r="43" ht="24.75" spans="1:11">
+      <c r="J42" s="9">
+        <v>1</v>
+      </c>
+      <c r="K42" s="9"/>
+    </row>
+    <row r="43" spans="1:11" ht="48">
       <c r="A43" s="2"/>
       <c r="B43" s="7">
-        <f>ROW(B43)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>189</v>
+      <c r="C43" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>184</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G43" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>191</v>
+      <c r="G43" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>186</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="J43" s="9">
-        <v>1</v>
-      </c>
-      <c r="K43" s="9"/>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="J43" s="12">
+        <v>1</v>
+      </c>
+      <c r="K43" s="12"/>
+    </row>
+    <row r="44" spans="1:11" ht="24">
       <c r="A44" s="2"/>
       <c r="B44" s="7">
-        <f>ROW(B44)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="C44" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>194</v>
+      <c r="C44" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>189</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G44" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>196</v>
+      <c r="G44" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>191</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="J44" s="12">
-        <v>1</v>
-      </c>
-      <c r="K44" s="12"/>
-    </row>
-    <row r="45" ht="26.25" spans="1:11">
+      <c r="J44" s="9">
+        <v>1</v>
+      </c>
+      <c r="K44" s="9"/>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="2"/>
       <c r="B45" s="7">
-        <f>ROW(B45)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>199</v>
+      <c r="C45" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>194</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G45" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H45" s="9" t="s">
+      <c r="G45" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="H45" s="12" t="s">
         <v>196</v>
       </c>
       <c r="I45" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="J45" s="9">
-        <v>2</v>
-      </c>
-      <c r="K45" s="9"/>
-    </row>
-    <row r="46" ht="26.25" spans="1:11">
+      <c r="J45" s="12">
+        <v>1</v>
+      </c>
+      <c r="K45" s="12"/>
+    </row>
+    <row r="46" spans="1:11" ht="25.5">
       <c r="A46" s="2"/>
       <c r="B46" s="7">
-        <f>ROW(B46)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="D46" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E46" s="15" t="s">
+      <c r="D46" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="E46" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="15" t="s">
+      <c r="G46" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="H46" s="14" t="s">
+      <c r="H46" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="I46" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J46" s="14">
-        <v>1</v>
-      </c>
-      <c r="K46" s="17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="47" ht="26.25" spans="1:11">
+      <c r="I46" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="J46" s="9">
+        <v>2</v>
+      </c>
+      <c r="K46" s="9"/>
+    </row>
+    <row r="47" spans="1:11" ht="25.5">
       <c r="A47" s="2"/>
       <c r="B47" s="7">
-        <f>ROW(B47)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F47" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="F47" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J47" s="9">
-        <v>1</v>
-      </c>
-      <c r="K47" s="9"/>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="G47" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="I47" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J47" s="14">
+        <v>1</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="25.5">
       <c r="A48" s="2"/>
       <c r="B48" s="7">
-        <f>ROW(B48)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="J48" s="9">
         <v>1</v>
       </c>
       <c r="K48" s="9"/>
     </row>
-    <row r="49" ht="24.75" spans="1:11">
+    <row r="49" spans="1:11">
       <c r="A49" s="2"/>
       <c r="B49" s="7">
-        <f>ROW(B49)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>215</v>
+      <c r="C49" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G49" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="H49" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="I49" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="J49" s="12">
-        <v>3</v>
-      </c>
-      <c r="K49" s="12"/>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="G49" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="J49" s="9">
+        <v>1</v>
+      </c>
+      <c r="K49" s="9"/>
+    </row>
+    <row r="50" spans="1:11" ht="24">
       <c r="A50" s="2"/>
       <c r="B50" s="7">
-        <f>ROW(B50)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>220</v>
+      <c r="D50" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>215</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G50" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="I50" s="10" t="s">
+      <c r="G50" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="I50" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="J50" s="9">
-        <v>1</v>
-      </c>
-      <c r="K50" s="9"/>
-    </row>
-    <row r="51" ht="24.75" spans="1:11">
+      <c r="J50" s="12">
+        <v>3</v>
+      </c>
+      <c r="K50" s="12"/>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="2"/>
       <c r="B51" s="7">
-        <f>ROW(B51)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D51" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>224</v>
+      <c r="D51" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>220</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G51" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="H51" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="I51" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="J51" s="12">
-        <v>1</v>
-      </c>
-      <c r="K51" s="12"/>
-    </row>
-    <row r="52" ht="15.75" spans="1:11">
+      <c r="G51" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="J51" s="9">
+        <v>1</v>
+      </c>
+      <c r="K51" s="9"/>
+    </row>
+    <row r="52" spans="1:11" ht="24">
       <c r="A52" s="2"/>
       <c r="B52" s="7">
-        <f>ROW(B52)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D52" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="F52" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="G52" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J52" s="14">
-        <v>1</v>
-      </c>
-      <c r="K52" s="17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="53" ht="24.75" spans="1:11">
+      <c r="D52" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="J52" s="12">
+        <v>1</v>
+      </c>
+      <c r="K52" s="12"/>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="2"/>
       <c r="B53" s="7">
-        <f>ROW(B53)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="H53" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J53" s="12">
-        <v>1</v>
-      </c>
-      <c r="K53" s="12"/>
-    </row>
-    <row r="54" ht="24.75" spans="1:11">
+        <v>213</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G53" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J53" s="14">
+        <v>1</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="24">
       <c r="A54" s="2"/>
       <c r="B54" s="7">
-        <f>ROW(B54)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>241</v>
+      <c r="D54" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="H54" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="I54" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J54" s="9">
-        <v>5</v>
-      </c>
-      <c r="K54" s="9"/>
-    </row>
-    <row r="55" ht="24.75" spans="1:11">
+      <c r="J54" s="12">
+        <v>1</v>
+      </c>
+      <c r="K54" s="12"/>
+    </row>
+    <row r="55" spans="1:11" ht="24">
       <c r="A55" s="2"/>
       <c r="B55" s="7">
-        <f>ROW(B55)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D55" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="G55" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H55" s="12" t="s">
-        <v>246</v>
+      <c r="D55" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>241</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J55" s="12">
-        <v>2</v>
-      </c>
-      <c r="K55" s="12"/>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="J55" s="9">
+        <v>5</v>
+      </c>
+      <c r="K55" s="9"/>
+    </row>
+    <row r="56" spans="1:11" ht="24">
       <c r="A56" s="2"/>
       <c r="B56" s="7">
-        <f>ROW(B56)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="D56" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="H56" s="9" t="s">
+      <c r="D56" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="H56" s="12" t="s">
         <v>246</v>
       </c>
       <c r="I56" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J56" s="9">
-        <v>1</v>
-      </c>
-      <c r="K56" s="9"/>
-    </row>
-    <row r="57" ht="24.75" spans="1:11">
+      <c r="J56" s="12">
+        <v>2</v>
+      </c>
+      <c r="K56" s="12"/>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" s="2"/>
       <c r="B57" s="7">
-        <f>ROW(B57)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D57" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>241</v>
+      <c r="D57" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>246</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J57" s="12">
-        <v>1</v>
-      </c>
-      <c r="K57" s="12"/>
-    </row>
-    <row r="58" ht="36.75" spans="1:11">
+      <c r="J57" s="9">
+        <v>1</v>
+      </c>
+      <c r="K57" s="9"/>
+    </row>
+    <row r="58" spans="1:11" ht="24">
       <c r="A58" s="2"/>
       <c r="B58" s="7">
-        <f>ROW(B58)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>258</v>
+      <c r="C58" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>241</v>
       </c>
       <c r="I58" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J58" s="9">
-        <v>1</v>
-      </c>
-      <c r="K58" s="9"/>
-    </row>
-    <row r="59" spans="1:11">
+      <c r="J58" s="12">
+        <v>1</v>
+      </c>
+      <c r="K58" s="12"/>
+    </row>
+    <row r="59" spans="1:11" ht="36">
       <c r="A59" s="2"/>
       <c r="B59" s="7">
-        <f>ROW(B59)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="G59" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>156</v>
+      <c r="C59" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>258</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J59" s="12">
-        <v>1</v>
-      </c>
-      <c r="K59" s="12"/>
+      <c r="J59" s="9">
+        <v>1</v>
+      </c>
+      <c r="K59" s="9"/>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="2"/>
       <c r="B60" s="7">
-        <f>ROW(B60)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>268</v>
+      <c r="D60" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="H60" s="12" t="s">
+        <v>156</v>
       </c>
       <c r="I60" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J60" s="9">
-        <v>6</v>
-      </c>
-      <c r="K60" s="9"/>
+      <c r="J60" s="12">
+        <v>1</v>
+      </c>
+      <c r="K60" s="12"/>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2"/>
       <c r="B61" s="7">
-        <f>ROW(B61)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="C61" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="H61" s="12" t="s">
-        <v>74</v>
+      <c r="C61" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>268</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="J61" s="12">
-        <v>7</v>
-      </c>
-      <c r="K61" s="12"/>
+        <v>145</v>
+      </c>
+      <c r="J61" s="9">
+        <v>6</v>
+      </c>
+      <c r="K61" s="9"/>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2"/>
       <c r="B62" s="7">
-        <f>ROW(B62)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D62" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="F62" s="9" t="s">
+      <c r="D62" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="F62" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G62" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="H62" s="9" t="s">
+      <c r="G62" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="H62" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I62" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="J62" s="9">
-        <v>1</v>
-      </c>
-      <c r="K62" s="9"/>
+      <c r="I62" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="J62" s="12">
+        <v>7</v>
+      </c>
+      <c r="K62" s="12"/>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2"/>
       <c r="B63" s="7">
-        <f>ROW(B63)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D63" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="F63" s="12" t="s">
+      <c r="D63" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="F63" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G63" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="H63" s="12" t="s">
+      <c r="G63" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I63" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="J63" s="12">
-        <v>1</v>
-      </c>
-      <c r="K63" s="12"/>
+      <c r="I63" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="J63" s="9">
+        <v>1</v>
+      </c>
+      <c r="K63" s="9"/>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2"/>
       <c r="B64" s="7">
-        <f>ROW(B64)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D64" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="F64" s="9" t="s">
+      <c r="D64" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="F64" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G64" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="H64" s="9" t="s">
+      <c r="G64" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="H64" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I64" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="J64" s="9">
-        <v>1</v>
-      </c>
-      <c r="K64" s="9"/>
-    </row>
-    <row r="65" ht="15.75" spans="1:11">
+      <c r="I64" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="J64" s="12">
+        <v>1</v>
+      </c>
+      <c r="K64" s="12"/>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" s="2"/>
       <c r="B65" s="7">
-        <f>ROW(B65)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D65" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="12" t="s">
+      <c r="D65" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F65" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G65" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="H65" s="12" t="s">
+      <c r="G65" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I65" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="J65" s="12">
-        <v>1</v>
-      </c>
-      <c r="K65" s="12"/>
-    </row>
-    <row r="66" ht="15.75" spans="1:11">
+      <c r="I65" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="J65" s="9">
+        <v>1</v>
+      </c>
+      <c r="K65" s="9"/>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" s="2"/>
       <c r="B66" s="7">
-        <f>ROW(B66)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D66" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="H66" s="9" t="s">
+      <c r="D66" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G66" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="H66" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I66" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="J66" s="9">
-        <v>1</v>
-      </c>
-      <c r="K66" s="9"/>
-    </row>
-    <row r="67" ht="15.75" spans="1:11">
+      <c r="I66" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="J66" s="12">
+        <v>1</v>
+      </c>
+      <c r="K66" s="12"/>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" s="2"/>
       <c r="B67" s="7">
-        <f>ROW(B67)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="C67" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G67" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="H67" s="12" t="s">
+      <c r="C67" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I67" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="J67" s="12">
-        <v>1</v>
-      </c>
-      <c r="K67" s="12"/>
-    </row>
-    <row r="68" ht="15.75" spans="1:11">
+      <c r="I67" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="J67" s="9">
+        <v>1</v>
+      </c>
+      <c r="K67" s="9"/>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" s="2"/>
       <c r="B68" s="7">
-        <f>ROW(B68)-ROW($B$2)</f>
+        <f t="shared" ref="B68:B99" si="2">ROW(B68)-ROW($B$2)</f>
         <v>66</v>
       </c>
-      <c r="C68" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="F68" s="9" t="s">
+      <c r="C68" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="F68" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G68" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="H68" s="9" t="s">
+      <c r="G68" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="H68" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I68" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="J68" s="9">
-        <v>1</v>
-      </c>
-      <c r="K68" s="9"/>
-    </row>
-    <row r="69" ht="15.75" spans="1:11">
+      <c r="I68" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="J68" s="12">
+        <v>1</v>
+      </c>
+      <c r="K68" s="12"/>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" s="2"/>
       <c r="B69" s="7">
-        <f>ROW(B69)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D69" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="F69" s="12" t="s">
+      <c r="D69" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="F69" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G69" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="H69" s="12" t="s">
+      <c r="G69" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I69" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="J69" s="12">
-        <v>1</v>
-      </c>
-      <c r="K69" s="12"/>
-    </row>
-    <row r="70" ht="15.75" spans="1:11">
+      <c r="I69" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="J69" s="9">
+        <v>1</v>
+      </c>
+      <c r="K69" s="9"/>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" s="2"/>
       <c r="B70" s="7">
-        <f>ROW(B70)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="C70" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="F70" s="9" t="s">
+      <c r="C70" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="F70" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G70" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="H70" s="9" t="s">
+      <c r="G70" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="H70" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I70" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="J70" s="9">
-        <v>1</v>
-      </c>
-      <c r="K70" s="9"/>
-    </row>
-    <row r="71" ht="15.75" spans="1:11">
+      <c r="I70" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="J70" s="12">
+        <v>1</v>
+      </c>
+      <c r="K70" s="12"/>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" s="2"/>
       <c r="B71" s="7">
-        <f>ROW(B71)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="C71" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="F71" s="12" t="s">
+      <c r="C71" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F71" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G71" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="H71" s="12" t="s">
+      <c r="G71" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I71" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="J71" s="12">
-        <v>1</v>
-      </c>
-      <c r="K71" s="12"/>
+      <c r="I71" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="J71" s="9">
+        <v>1</v>
+      </c>
+      <c r="K71" s="9"/>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2"/>
       <c r="B72" s="7">
-        <f>ROW(B72)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D72" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="F72" s="9" t="s">
+      <c r="D72" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="F72" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G72" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="H72" s="9" t="s">
+      <c r="G72" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="H72" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I72" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="J72" s="9">
-        <v>6</v>
-      </c>
-      <c r="K72" s="9"/>
-    </row>
-    <row r="73" ht="15.75" spans="1:11">
+      <c r="I72" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="J72" s="12">
+        <v>1</v>
+      </c>
+      <c r="K72" s="12"/>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" s="2"/>
       <c r="B73" s="7">
-        <f>ROW(B73)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D73" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G73" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="H73" s="12" t="s">
+      <c r="D73" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I73" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="J73" s="12">
-        <v>1</v>
-      </c>
-      <c r="K73" s="12"/>
-    </row>
-    <row r="74" ht="24.75" spans="1:11">
+      <c r="I73" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="J73" s="9">
+        <v>6</v>
+      </c>
+      <c r="K73" s="9"/>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" s="2"/>
       <c r="B74" s="7">
-        <f>ROW(B74)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="C74" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="H74" s="9" t="s">
+      <c r="C74" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="H74" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I74" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="J74" s="9">
-        <v>18</v>
-      </c>
-      <c r="K74" s="9"/>
-    </row>
-    <row r="75" ht="15.75" spans="1:11">
+      <c r="I74" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="J74" s="12">
+        <v>1</v>
+      </c>
+      <c r="K74" s="12"/>
+    </row>
+    <row r="75" spans="1:11" ht="24">
       <c r="A75" s="2"/>
       <c r="B75" s="7">
-        <f>ROW(B75)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C75" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="F75" s="12" t="s">
+      <c r="C75" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="F75" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G75" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="H75" s="12" t="s">
+      <c r="G75" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I75" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="J75" s="12">
-        <v>2</v>
-      </c>
-      <c r="K75" s="12"/>
-    </row>
-    <row r="76" ht="15.75" spans="1:11">
+      <c r="I75" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="J75" s="9">
+        <v>18</v>
+      </c>
+      <c r="K75" s="9"/>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" s="2"/>
       <c r="B76" s="7">
-        <f>ROW(B76)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="F76" s="9" t="s">
+      <c r="C76" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="F76" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G76" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="H76" s="9" t="s">
+      <c r="G76" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="H76" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I76" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="J76" s="9">
-        <v>1</v>
-      </c>
-      <c r="K76" s="9"/>
-    </row>
-    <row r="77" ht="15.75" spans="1:11">
+      <c r="I76" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="J76" s="12">
+        <v>2</v>
+      </c>
+      <c r="K76" s="12"/>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="2"/>
       <c r="B77" s="7">
-        <f>ROW(B77)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C77" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="F77" s="12" t="s">
+      <c r="C77" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="F77" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G77" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="H77" s="12" t="s">
+      <c r="G77" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I77" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="J77" s="12">
-        <v>1</v>
-      </c>
-      <c r="K77" s="12"/>
-    </row>
-    <row r="78" ht="24.75" spans="1:11">
+      <c r="I77" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="J77" s="9">
+        <v>1</v>
+      </c>
+      <c r="K77" s="9"/>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="2"/>
       <c r="B78" s="7">
-        <f>ROW(B78)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="H78" s="9" t="s">
+      <c r="D78" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="H78" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I78" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="J78" s="9">
-        <v>10</v>
-      </c>
-      <c r="K78" s="9"/>
-    </row>
-    <row r="79" ht="15.75" spans="1:11">
+      <c r="I78" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="J78" s="12">
+        <v>1</v>
+      </c>
+      <c r="K78" s="12"/>
+    </row>
+    <row r="79" spans="1:11" ht="24">
       <c r="A79" s="2"/>
       <c r="B79" s="7">
-        <f>ROW(B79)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="C79" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="F79" s="12" t="s">
+      <c r="C79" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="F79" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G79" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="H79" s="12" t="s">
+      <c r="G79" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I79" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="J79" s="12">
-        <v>1</v>
-      </c>
-      <c r="K79" s="12"/>
-    </row>
-    <row r="80" ht="15.75" spans="1:11">
+      <c r="I79" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="J79" s="9">
+        <v>10</v>
+      </c>
+      <c r="K79" s="9"/>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="2"/>
       <c r="B80" s="7">
-        <f>ROW(B80)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C80" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="F80" s="9" t="s">
+      <c r="C80" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="F80" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G80" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="H80" s="9" t="s">
+      <c r="G80" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="H80" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I80" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="J80" s="9">
-        <v>1</v>
-      </c>
-      <c r="K80" s="9"/>
-    </row>
-    <row r="81" ht="15.75" spans="1:11">
+      <c r="I80" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J80" s="12">
+        <v>1</v>
+      </c>
+      <c r="K80" s="12"/>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81" s="2"/>
       <c r="B81" s="7">
-        <f>ROW(B81)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C81" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="F81" s="12" t="s">
+      <c r="C81" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="F81" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G81" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="H81" s="12" t="s">
+      <c r="G81" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I81" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="J81" s="12">
-        <v>1</v>
-      </c>
-      <c r="K81" s="12"/>
-    </row>
-    <row r="82" ht="15.75" spans="1:11">
+      <c r="I81" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="J81" s="9">
+        <v>1</v>
+      </c>
+      <c r="K81" s="9"/>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" s="2"/>
       <c r="B82" s="7">
-        <f>ROW(B82)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="D82" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="F82" s="9" t="s">
+      <c r="D82" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="F82" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G82" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="H82" s="9" t="s">
+      <c r="G82" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="H82" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I82" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="J82" s="9">
-        <v>1</v>
-      </c>
-      <c r="K82" s="9"/>
-    </row>
-    <row r="83" ht="15.75" spans="1:11">
+      <c r="I82" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="J82" s="12">
+        <v>1</v>
+      </c>
+      <c r="K82" s="12"/>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83" s="2"/>
       <c r="B83" s="7">
-        <f>ROW(B83)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D83" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="F83" s="12" t="s">
+      <c r="D83" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="F83" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G83" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="H83" s="12" t="s">
+      <c r="G83" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I83" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="J83" s="12">
-        <v>1</v>
-      </c>
-      <c r="K83" s="12"/>
+      <c r="I83" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="J83" s="9">
+        <v>1</v>
+      </c>
+      <c r="K83" s="9"/>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="2"/>
       <c r="B84" s="7">
-        <f>ROW(B84)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C84" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="F84" s="9" t="s">
+      <c r="C84" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="F84" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G84" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="H84" s="9" t="s">
+      <c r="G84" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="H84" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I84" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="J84" s="9">
-        <v>7</v>
-      </c>
-      <c r="K84" s="9"/>
+      <c r="I84" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="J84" s="12">
+        <v>1</v>
+      </c>
+      <c r="K84" s="12"/>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="2"/>
       <c r="B85" s="7">
-        <f>ROW(B85)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D85" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="F85" s="12" t="s">
+      <c r="D85" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="F85" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G85" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="H85" s="12" t="s">
+      <c r="G85" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I85" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="J85" s="12">
-        <v>4</v>
-      </c>
-      <c r="K85" s="12"/>
+      <c r="I85" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="J85" s="9">
+        <v>7</v>
+      </c>
+      <c r="K85" s="9"/>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="2"/>
       <c r="B86" s="7">
-        <f>ROW(B86)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="C86" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D86" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="F86" s="9" t="s">
+      <c r="D86" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="F86" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G86" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="H86" s="9" t="s">
+      <c r="G86" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="H86" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I86" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="J86" s="9">
-        <v>5</v>
-      </c>
-      <c r="K86" s="9"/>
-    </row>
-    <row r="87" ht="15.75" spans="1:11">
+      <c r="I86" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="J86" s="12">
+        <v>4</v>
+      </c>
+      <c r="K86" s="12"/>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87" s="2"/>
       <c r="B87" s="7">
-        <f>ROW(B87)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>85</v>
       </c>
       <c r="C87" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D87" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="F87" s="12" t="s">
+      <c r="D87" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F87" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G87" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="H87" s="12" t="s">
+      <c r="G87" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I87" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="J87" s="12">
-        <v>1</v>
-      </c>
-      <c r="K87" s="12"/>
-    </row>
-    <row r="88" ht="15.75" spans="1:11">
+      <c r="I87" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="J87" s="9">
+        <v>5</v>
+      </c>
+      <c r="K87" s="9"/>
+    </row>
+    <row r="88" spans="1:11">
       <c r="A88" s="2"/>
       <c r="B88" s="7">
-        <f>ROW(B88)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D88" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="F88" s="9" t="s">
+      <c r="D88" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="F88" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G88" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="H88" s="19" t="s">
+      <c r="G88" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="H88" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I88" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="J88" s="9">
-        <v>2</v>
-      </c>
-      <c r="K88" s="9"/>
-    </row>
-    <row r="89" ht="15.75" spans="1:11">
+      <c r="I88" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="J88" s="12">
+        <v>1</v>
+      </c>
+      <c r="K88" s="12"/>
+    </row>
+    <row r="89" spans="1:11">
       <c r="A89" s="2"/>
       <c r="B89" s="7">
-        <f>ROW(B89)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D89" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="F89" s="12" t="s">
+      <c r="D89" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="F89" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G89" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="H89" s="12" t="s">
+      <c r="G89" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="H89" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="I89" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="J89" s="12">
-        <v>1</v>
-      </c>
-      <c r="K89" s="12"/>
-    </row>
-    <row r="90" ht="15.75" spans="1:11">
+      <c r="I89" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="J89" s="9">
+        <v>2</v>
+      </c>
+      <c r="K89" s="9"/>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90" s="2"/>
       <c r="B90" s="7">
-        <f>ROW(B90)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D90" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="F90" s="9" t="s">
+      <c r="D90" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="F90" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G90" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="H90" s="9" t="s">
+      <c r="G90" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="H90" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I90" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="J90" s="9">
-        <v>1</v>
-      </c>
-      <c r="K90" s="9"/>
-    </row>
-    <row r="91" ht="15.75" spans="1:11">
+      <c r="I90" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="J90" s="12">
+        <v>1</v>
+      </c>
+      <c r="K90" s="12"/>
+    </row>
+    <row r="91" spans="1:11">
       <c r="A91" s="2"/>
       <c r="B91" s="7">
-        <f>ROW(B91)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="C91" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="D91" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="F91" s="12" t="s">
+      <c r="C91" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="F91" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G91" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="H91" s="12" t="s">
+      <c r="G91" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I91" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="J91" s="12">
-        <v>1</v>
-      </c>
-      <c r="K91" s="12"/>
-    </row>
-    <row r="92" ht="15.75" spans="1:11">
+      <c r="I91" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="J91" s="9">
+        <v>1</v>
+      </c>
+      <c r="K91" s="9"/>
+    </row>
+    <row r="92" spans="1:11">
       <c r="A92" s="2"/>
       <c r="B92" s="7">
-        <f>ROW(B92)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="H92" s="9" t="s">
+      <c r="D92" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="G92" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="H92" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I92" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="J92" s="9">
-        <v>1</v>
-      </c>
-      <c r="K92" s="9"/>
-    </row>
-    <row r="93" ht="15.75" spans="1:11">
+      <c r="I92" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="J92" s="12">
+        <v>1</v>
+      </c>
+      <c r="K92" s="12"/>
+    </row>
+    <row r="93" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="7">
-        <f>ROW(B93)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D93" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="F93" s="12" t="s">
+      <c r="D93" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="F93" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G93" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="H93" s="12" t="s">
+      <c r="G93" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I93" s="13" t="s">
-        <v>400</v>
-      </c>
-      <c r="J93" s="12">
-        <v>1</v>
-      </c>
-      <c r="K93" s="12"/>
-    </row>
-    <row r="94" ht="15.75" spans="1:11">
+      <c r="I93" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="J93" s="9">
+        <v>1</v>
+      </c>
+      <c r="K93" s="9"/>
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94" s="2"/>
       <c r="B94" s="7">
-        <f>ROW(B94)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="C94" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="H94" s="9" t="s">
+      <c r="C94" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G94" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="H94" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I94" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="J94" s="9">
-        <v>1</v>
-      </c>
-      <c r="K94" s="9"/>
-    </row>
-    <row r="95" ht="15.75" spans="1:11">
+      <c r="I94" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="J94" s="12">
+        <v>1</v>
+      </c>
+      <c r="K94" s="12"/>
+    </row>
+    <row r="95" spans="1:11">
       <c r="A95" s="2"/>
       <c r="B95" s="7">
-        <f>ROW(B95)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>93</v>
       </c>
-      <c r="C95" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="F95" s="12" t="s">
+      <c r="C95" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="F95" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G95" s="13" t="s">
-        <v>407</v>
-      </c>
-      <c r="H95" s="12" t="s">
+      <c r="G95" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I95" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="J95" s="12">
-        <v>3</v>
-      </c>
-      <c r="K95" s="12"/>
+      <c r="I95" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="J95" s="9">
+        <v>1</v>
+      </c>
+      <c r="K95" s="9"/>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="7">
-        <f>ROW(B96)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="C96" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="F96" s="9" t="s">
+      <c r="C96" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="F96" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G96" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="H96" s="9" t="s">
+      <c r="G96" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="H96" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I96" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="J96" s="9">
-        <v>6</v>
-      </c>
-      <c r="K96" s="9"/>
+      <c r="I96" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="J96" s="12">
+        <v>3</v>
+      </c>
+      <c r="K96" s="12"/>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="7">
-        <f>ROW(B97)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>95</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D97" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>414</v>
-      </c>
-      <c r="F97" s="12" t="s">
+      <c r="D97" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="F97" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G97" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="H97" s="12" t="s">
+      <c r="G97" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I97" s="13" t="s">
-        <v>416</v>
-      </c>
-      <c r="J97" s="12">
-        <v>1</v>
-      </c>
-      <c r="K97" s="12"/>
+      <c r="I97" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="J97" s="9">
+        <v>6</v>
+      </c>
+      <c r="K97" s="9"/>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="2"/>
       <c r="B98" s="7">
-        <f>ROW(B98)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D98" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="F98" s="9" t="s">
+      <c r="D98" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="F98" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G98" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="H98" s="9" t="s">
+      <c r="G98" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="H98" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I98" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="J98" s="9">
-        <v>1</v>
-      </c>
-      <c r="K98" s="9"/>
+      <c r="I98" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="J98" s="12">
+        <v>1</v>
+      </c>
+      <c r="K98" s="12"/>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="2"/>
       <c r="B99" s="7">
-        <f>ROW(B99)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>97</v>
       </c>
       <c r="C99" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D99" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="F99" s="12" t="s">
+      <c r="D99" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="F99" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G99" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="H99" s="12" t="s">
+      <c r="G99" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I99" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="J99" s="12">
-        <v>1</v>
-      </c>
-      <c r="K99" s="12"/>
-    </row>
-    <row r="100" ht="15.75" spans="1:11">
+      <c r="I99" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="J99" s="9">
+        <v>1</v>
+      </c>
+      <c r="K99" s="9"/>
+    </row>
+    <row r="100" spans="1:11">
       <c r="A100" s="2"/>
       <c r="B100" s="7">
-        <f>ROW(B100)-ROW($B$2)</f>
+        <f t="shared" ref="B100:B131" si="3">ROW(B100)-ROW($B$2)</f>
         <v>98</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D100" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="F100" s="9" t="s">
+      <c r="D100" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="F100" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G100" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="H100" s="9" t="s">
+      <c r="G100" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="H100" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I100" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="J100" s="9">
-        <v>2</v>
-      </c>
-      <c r="K100" s="9"/>
-    </row>
-    <row r="101" ht="15.75" spans="1:11">
+      <c r="I100" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="J100" s="12">
+        <v>1</v>
+      </c>
+      <c r="K100" s="12"/>
+    </row>
+    <row r="101" spans="1:11">
       <c r="A101" s="2"/>
       <c r="B101" s="7">
-        <f>ROW(B101)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>99</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C101" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D101" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="E101" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="F101" s="14" t="s">
+      <c r="D101" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="F101" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G101" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="H101" s="14" t="s">
+      <c r="G101" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="H101" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I101" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J101" s="14">
+      <c r="I101" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="J101" s="9">
         <v>2</v>
       </c>
-      <c r="K101" s="17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="102" ht="15.75" spans="1:11">
+      <c r="K101" s="9"/>
+    </row>
+    <row r="102" spans="1:11">
       <c r="A102" s="2"/>
       <c r="B102" s="7">
-        <f>ROW(B102)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="C102" s="8" t="s">
+      <c r="C102" s="11" t="s">
         <v>269</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="F102" s="14" t="s">
         <v>293</v>
       </c>
       <c r="G102" s="15" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="H102" s="14" t="s">
         <v>74</v>
@@ -6301,358 +5669,358 @@
         <v>136</v>
       </c>
       <c r="J102" s="14">
-        <v>1</v>
-      </c>
-      <c r="K102" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="K102" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="103" ht="36.75" spans="1:11">
+    <row r="103" spans="1:11">
       <c r="A103" s="2"/>
       <c r="B103" s="7">
-        <f>ROW(B103)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>101</v>
       </c>
-      <c r="C103" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>431</v>
-      </c>
-      <c r="E103" s="13" t="s">
-        <v>432</v>
-      </c>
-      <c r="F103" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G103" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="H103" s="12" t="s">
+      <c r="C103" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="G103" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="H103" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I103" s="13" t="s">
-        <v>434</v>
-      </c>
-      <c r="J103" s="12">
-        <v>1</v>
-      </c>
-      <c r="K103" s="12"/>
-    </row>
-    <row r="104" ht="15.75" spans="1:11">
+      <c r="I103" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J103" s="14">
+        <v>1</v>
+      </c>
+      <c r="K103" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="36">
       <c r="A104" s="2"/>
       <c r="B104" s="7">
-        <f>ROW(B104)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>102</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C104" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="D104" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="H104" s="9" t="s">
+      <c r="D104" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G104" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="H104" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I104" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="J104" s="9">
-        <v>1</v>
-      </c>
-      <c r="K104" s="9"/>
-    </row>
-    <row r="105" ht="15.75" spans="1:11">
+      <c r="I104" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="J104" s="12">
+        <v>1</v>
+      </c>
+      <c r="K104" s="12"/>
+    </row>
+    <row r="105" spans="1:11">
       <c r="A105" s="2"/>
       <c r="B105" s="7">
-        <f>ROW(B105)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>103</v>
       </c>
-      <c r="C105" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D105" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="E105" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="F105" s="12" t="s">
+      <c r="C105" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="F105" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G105" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="H105" s="12" t="s">
+      <c r="G105" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="H105" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I105" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="J105" s="12">
-        <v>1</v>
-      </c>
-      <c r="K105" s="12"/>
-    </row>
-    <row r="106" ht="15.75" spans="1:11">
+      <c r="I105" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="J105" s="9">
+        <v>1</v>
+      </c>
+      <c r="K105" s="9"/>
+    </row>
+    <row r="106" spans="1:11">
       <c r="A106" s="2"/>
       <c r="B106" s="7">
-        <f>ROW(B106)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>104</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D106" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="F106" s="9" t="s">
+      <c r="D106" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="F106" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G106" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="H106" s="9" t="s">
+      <c r="G106" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="H106" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I106" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="J106" s="9">
-        <v>1</v>
-      </c>
-      <c r="K106" s="9"/>
-    </row>
-    <row r="107" ht="15.75" spans="1:11">
+      <c r="I106" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="J106" s="12">
+        <v>1</v>
+      </c>
+      <c r="K106" s="12"/>
+    </row>
+    <row r="107" spans="1:11">
       <c r="A107" s="2"/>
       <c r="B107" s="7">
-        <f>ROW(B107)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>105</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C107" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D107" s="14" t="s">
-        <v>446</v>
-      </c>
-      <c r="E107" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="F107" s="14" t="s">
+      <c r="D107" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="F107" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G107" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="H107" s="14" t="s">
+      <c r="G107" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="H107" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I107" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J107" s="14">
-        <v>1</v>
-      </c>
-      <c r="K107" s="17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="108" ht="15.75" spans="1:11">
+      <c r="I107" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="J107" s="9">
+        <v>1</v>
+      </c>
+      <c r="K107" s="9"/>
+    </row>
+    <row r="108" spans="1:11">
       <c r="A108" s="2"/>
       <c r="B108" s="7">
-        <f>ROW(B108)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>106</v>
       </c>
-      <c r="C108" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F108" s="9" t="s">
+      <c r="C108" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="E108" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="F108" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="G108" s="10" t="s">
-        <v>449</v>
-      </c>
-      <c r="H108" s="9" t="s">
+      <c r="G108" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="H108" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I108" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="J108" s="9">
-        <v>1</v>
-      </c>
-      <c r="K108" s="9"/>
-    </row>
-    <row r="109" ht="15.75" spans="1:11">
+      <c r="I108" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J108" s="14">
+        <v>1</v>
+      </c>
+      <c r="K108" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
       <c r="A109" s="2"/>
       <c r="B109" s="7">
-        <f>ROW(B109)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
-      <c r="C109" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D109" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="E109" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="F109" s="14" t="s">
+      <c r="C109" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F109" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G109" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="H109" s="14" t="s">
+      <c r="G109" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="H109" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I109" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J109" s="14">
-        <v>1</v>
-      </c>
-      <c r="K109" s="17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="110" ht="15.75" spans="1:11">
+      <c r="I109" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="J109" s="9">
+        <v>1</v>
+      </c>
+      <c r="K109" s="9"/>
+    </row>
+    <row r="110" spans="1:11">
       <c r="A110" s="2"/>
       <c r="B110" s="7">
-        <f>ROW(B110)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>108</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="C110" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D110" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="F110" s="9" t="s">
+      <c r="D110" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="E110" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="F110" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="G110" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="H110" s="9" t="s">
+      <c r="G110" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="H110" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I110" s="10" t="s">
-        <v>454</v>
-      </c>
-      <c r="J110" s="9">
-        <v>4</v>
-      </c>
-      <c r="K110" s="9"/>
-    </row>
-    <row r="111" ht="15.75" spans="1:11">
+      <c r="I110" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J110" s="14">
+        <v>1</v>
+      </c>
+      <c r="K110" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
       <c r="A111" s="2"/>
       <c r="B111" s="7">
-        <f>ROW(B111)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>109</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C111" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D111" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="F111" s="12" t="s">
+      <c r="D111" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="F111" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="G111" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="H111" s="12" t="s">
+      <c r="G111" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="H111" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I111" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J111" s="12">
-        <v>1</v>
-      </c>
-      <c r="K111" s="12"/>
-    </row>
-    <row r="112" ht="15.75" spans="1:11">
+      <c r="I111" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="J111" s="9">
+        <v>4</v>
+      </c>
+      <c r="K111" s="9"/>
+    </row>
+    <row r="112" spans="1:11">
       <c r="A112" s="2"/>
       <c r="B112" s="7">
-        <f>ROW(B112)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>110</v>
       </c>
-      <c r="C112" s="8" t="s">
+      <c r="C112" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D112" s="14" t="s">
-        <v>458</v>
-      </c>
-      <c r="E112" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="F112" s="14" t="s">
+      <c r="D112" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="F112" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="G112" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="H112" s="14" t="s">
+      <c r="G112" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="H112" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I112" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J112" s="14">
-        <v>1</v>
-      </c>
-      <c r="K112" s="17" t="s">
-        <v>137</v>
-      </c>
+      <c r="I112" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="J112" s="12">
+        <v>1</v>
+      </c>
+      <c r="K112" s="12"/>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="2"/>
       <c r="B113" s="7">
-        <f>ROW(B113)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>111</v>
       </c>
-      <c r="C113" s="11" t="s">
-        <v>296</v>
+      <c r="C113" s="8" t="s">
+        <v>269</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="G113" s="15" t="s">
-        <v>326</v>
+        <v>427</v>
       </c>
       <c r="H113" s="14" t="s">
         <v>74</v>
@@ -6663,673 +6031,675 @@
       <c r="J113" s="14">
         <v>1</v>
       </c>
-      <c r="K113" s="17" t="s">
+      <c r="K113" s="16" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="2"/>
       <c r="B114" s="7">
-        <f>ROW(B114)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>112</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D114" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="E114" s="13" t="s">
-        <v>461</v>
-      </c>
-      <c r="F114" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="G114" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="H114" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="D114" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="F114" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="G114" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="H114" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I114" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="J114" s="12">
-        <v>6</v>
-      </c>
-      <c r="K114" s="12"/>
+      <c r="I114" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J114" s="14">
+        <v>1</v>
+      </c>
+      <c r="K114" s="16" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="2"/>
       <c r="B115" s="7">
-        <f>ROW(B115)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>113</v>
       </c>
       <c r="C115" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D115" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="F115" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G115" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="H115" s="9" t="s">
+      <c r="D115" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="G115" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="H115" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I115" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="J115" s="9">
-        <v>1</v>
-      </c>
-      <c r="K115" s="9"/>
-    </row>
-    <row r="116" ht="15.75" spans="1:11">
+      <c r="I115" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="J115" s="12">
+        <v>6</v>
+      </c>
+      <c r="K115" s="12"/>
+    </row>
+    <row r="116" spans="1:11">
       <c r="A116" s="2"/>
       <c r="B116" s="7">
-        <f>ROW(B116)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>114</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="D116" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>470</v>
+        <v>269</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>465</v>
       </c>
       <c r="F116" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G116" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="H116" s="12" t="s">
-        <v>472</v>
-      </c>
-      <c r="I116" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J116" s="12">
-        <v>1</v>
-      </c>
-      <c r="K116" s="12"/>
-    </row>
-    <row r="117" ht="48.75" spans="1:11">
+        <v>272</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="J116" s="9">
+        <v>1</v>
+      </c>
+      <c r="K116" s="9"/>
+    </row>
+    <row r="117" spans="1:11" ht="24">
       <c r="A117" s="2"/>
       <c r="B117" s="7">
-        <f>ROW(B117)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>115</v>
       </c>
-      <c r="C117" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>475</v>
+      <c r="C117" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>470</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G117" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>477</v>
+      <c r="G117" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="H117" s="12" t="s">
+        <v>472</v>
       </c>
       <c r="I117" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J117" s="9">
-        <v>1</v>
-      </c>
-      <c r="K117" s="9"/>
-    </row>
-    <row r="118" ht="36.75" spans="1:11">
+      <c r="J117" s="12">
+        <v>1</v>
+      </c>
+      <c r="K117" s="12"/>
+    </row>
+    <row r="118" spans="1:11" ht="48">
       <c r="A118" s="2"/>
       <c r="B118" s="7">
-        <f>ROW(B118)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>116</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C118" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="D118" s="12" t="s">
-        <v>478</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>479</v>
+      <c r="D118" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>475</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G118" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="H118" s="12" t="s">
+      <c r="G118" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="H118" s="9" t="s">
         <v>477</v>
       </c>
       <c r="I118" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J118" s="12">
-        <v>4</v>
-      </c>
-      <c r="K118" s="12"/>
-    </row>
-    <row r="119" ht="24.75" spans="1:11">
+      <c r="J118" s="9">
+        <v>1</v>
+      </c>
+      <c r="K118" s="9"/>
+    </row>
+    <row r="119" spans="1:11" ht="36">
       <c r="A119" s="2"/>
       <c r="B119" s="7">
-        <f>ROW(B119)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>117</v>
       </c>
-      <c r="C119" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="E119" s="10" t="s">
-        <v>483</v>
+      <c r="C119" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="E119" s="13" t="s">
+        <v>479</v>
       </c>
       <c r="F119" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="G119" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>486</v>
+        <v>34</v>
+      </c>
+      <c r="G119" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="H119" s="12" t="s">
+        <v>477</v>
       </c>
       <c r="I119" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J119" s="9">
-        <v>1</v>
-      </c>
-      <c r="K119" s="9"/>
-    </row>
-    <row r="120" spans="1:11">
+      <c r="J119" s="12">
+        <v>4</v>
+      </c>
+      <c r="K119" s="12"/>
+    </row>
+    <row r="120" spans="1:11" ht="24">
       <c r="A120" s="2"/>
       <c r="B120" s="7">
-        <f>ROW(B120)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>118</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C120" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="D120" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="E120" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="F120" s="12" t="s">
-        <v>489</v>
-      </c>
-      <c r="G120" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="H120" s="12" t="s">
-        <v>491</v>
+      <c r="D120" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="G120" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>486</v>
       </c>
       <c r="I120" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J120" s="12">
-        <v>1</v>
-      </c>
-      <c r="K120" s="12"/>
+      <c r="J120" s="9">
+        <v>1</v>
+      </c>
+      <c r="K120" s="9"/>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="2"/>
       <c r="B121" s="7">
-        <f>ROW(B121)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>119</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D121" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="E121" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="G121" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>496</v>
+      <c r="D121" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="F121" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="G121" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="H121" s="12" t="s">
+        <v>491</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J121" s="9">
-        <v>1</v>
-      </c>
-      <c r="K121" s="9"/>
-    </row>
-    <row r="122" ht="24.75" spans="1:11">
+      <c r="J121" s="12">
+        <v>1</v>
+      </c>
+      <c r="K121" s="12"/>
+    </row>
+    <row r="122" spans="1:11" ht="24">
       <c r="A122" s="2"/>
       <c r="B122" s="7">
-        <f>ROW(B122)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C122" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="D122" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="E122" s="13" t="s">
-        <v>498</v>
-      </c>
-      <c r="F122" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="G122" s="13" t="s">
-        <v>500</v>
-      </c>
-      <c r="H122" s="12" t="s">
-        <v>501</v>
+      <c r="D122" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="H122" s="9" t="s">
+        <v>496</v>
       </c>
       <c r="I122" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J122" s="12">
-        <v>1</v>
-      </c>
-      <c r="K122" s="12"/>
-    </row>
-    <row r="123" spans="1:11">
+      <c r="J122" s="9">
+        <v>1</v>
+      </c>
+      <c r="K122" s="9"/>
+    </row>
+    <row r="123" spans="1:11" ht="24">
       <c r="A123" s="2"/>
       <c r="B123" s="7">
-        <f>ROW(B123)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>121</v>
       </c>
-      <c r="C123" s="8" t="s">
+      <c r="C123" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D123" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="G123" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>506</v>
+      <c r="D123" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="G123" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="H123" s="12" t="s">
+        <v>501</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J123" s="9">
-        <v>1</v>
-      </c>
-      <c r="K123" s="9"/>
+      <c r="J123" s="12">
+        <v>1</v>
+      </c>
+      <c r="K123" s="12"/>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="2"/>
       <c r="B124" s="7">
-        <f>ROW(B124)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>122</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C124" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="D124" s="12" t="s">
-        <v>507</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>508</v>
-      </c>
-      <c r="F124" s="12" t="s">
-        <v>509</v>
-      </c>
-      <c r="G124" s="13" t="s">
-        <v>510</v>
-      </c>
-      <c r="H124" s="12" t="s">
+      <c r="D124" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="G124" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="H124" s="9" t="s">
         <v>506</v>
       </c>
       <c r="I124" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J124" s="12">
-        <v>1</v>
-      </c>
-      <c r="K124" s="12"/>
+      <c r="J124" s="9">
+        <v>1</v>
+      </c>
+      <c r="K124" s="9"/>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="2"/>
       <c r="B125" s="7">
-        <f>ROW(B125)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>123</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D125" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>512</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="G125" s="10" t="s">
-        <v>514</v>
-      </c>
-      <c r="H125" s="9" t="s">
+      <c r="D125" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="F125" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="G125" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="H125" s="12" t="s">
         <v>506</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J125" s="9">
-        <v>1</v>
-      </c>
-      <c r="K125" s="9"/>
+      <c r="J125" s="12">
+        <v>1</v>
+      </c>
+      <c r="K125" s="12"/>
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="2"/>
       <c r="B126" s="7">
-        <f>ROW(B126)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>124</v>
       </c>
-      <c r="C126" s="11" t="s">
+      <c r="C126" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="D126" s="12" t="s">
-        <v>515</v>
-      </c>
-      <c r="E126" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="F126" s="12" t="s">
-        <v>517</v>
-      </c>
-      <c r="G126" s="13" t="s">
-        <v>518</v>
-      </c>
-      <c r="H126" s="12" t="s">
+      <c r="D126" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="H126" s="9" t="s">
         <v>506</v>
       </c>
       <c r="I126" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J126" s="12">
-        <v>1</v>
-      </c>
-      <c r="K126" s="12"/>
+      <c r="J126" s="9">
+        <v>1</v>
+      </c>
+      <c r="K126" s="9"/>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="2"/>
       <c r="B127" s="7">
-        <f>ROW(B127)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>125</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D127" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="E127" s="10" t="s">
-        <v>520</v>
-      </c>
-      <c r="F127" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="G127" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>522</v>
+      <c r="D127" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="F127" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="G127" s="13" t="s">
+        <v>518</v>
+      </c>
+      <c r="H127" s="12" t="s">
+        <v>506</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J127" s="9">
-        <v>1</v>
-      </c>
-      <c r="K127" s="9"/>
+      <c r="J127" s="12">
+        <v>1</v>
+      </c>
+      <c r="K127" s="12"/>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="2"/>
       <c r="B128" s="7">
-        <f>ROW(B128)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>126</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C128" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="D128" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="F128" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="G128" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="H128" s="12" t="s">
-        <v>506</v>
+      <c r="D128" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="G128" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>522</v>
       </c>
       <c r="I128" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J128" s="12">
-        <v>1</v>
-      </c>
-      <c r="K128" s="12"/>
-    </row>
-    <row r="129" ht="24.75" spans="1:11">
+      <c r="J128" s="9">
+        <v>1</v>
+      </c>
+      <c r="K128" s="9"/>
+    </row>
+    <row r="129" spans="1:11">
       <c r="A129" s="2"/>
       <c r="B129" s="7">
-        <f>ROW(B129)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>127</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D129" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="F129" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="G129" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>531</v>
+      <c r="D129" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="G129" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="H129" s="12" t="s">
+        <v>506</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J129" s="9">
-        <v>1</v>
-      </c>
-      <c r="K129" s="9"/>
-    </row>
-    <row r="130" spans="1:11">
+      <c r="J129" s="12">
+        <v>1</v>
+      </c>
+      <c r="K129" s="12"/>
+    </row>
+    <row r="130" spans="1:11" ht="24">
       <c r="A130" s="2"/>
       <c r="B130" s="7">
-        <f>ROW(B130)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>128</v>
       </c>
-      <c r="C130" s="11" t="s">
+      <c r="C130" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="D130" s="12" t="s">
-        <v>532</v>
-      </c>
-      <c r="E130" s="13" t="s">
-        <v>533</v>
-      </c>
-      <c r="F130" s="12" t="s">
-        <v>534</v>
-      </c>
-      <c r="G130" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="H130" s="12" t="s">
-        <v>506</v>
+      <c r="D130" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="H130" s="9" t="s">
+        <v>531</v>
       </c>
       <c r="I130" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J130" s="12">
-        <v>1</v>
-      </c>
-      <c r="K130" s="12"/>
-    </row>
-    <row r="131" ht="15.75" spans="1:11">
+      <c r="J130" s="9">
+        <v>1</v>
+      </c>
+      <c r="K130" s="9"/>
+    </row>
+    <row r="131" spans="1:11" ht="24">
       <c r="A131" s="2"/>
       <c r="B131" s="7">
-        <f>ROW(B131)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>129</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D131" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="E131" s="10" t="s">
-        <v>537</v>
-      </c>
-      <c r="F131" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="G131" s="10" t="s">
-        <v>539</v>
-      </c>
-      <c r="H131" s="9" t="s">
+      <c r="D131" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="F131" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="G131" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="H131" s="12" t="s">
         <v>506</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J131" s="9">
-        <v>1</v>
-      </c>
-      <c r="K131" s="9"/>
-    </row>
-    <row r="132" ht="24.75" spans="1:11">
+      <c r="J131" s="12">
+        <v>1</v>
+      </c>
+      <c r="K131" s="12"/>
+    </row>
+    <row r="132" spans="1:11">
       <c r="A132" s="2"/>
       <c r="B132" s="7">
-        <f>ROW(B132)-ROW($B$2)</f>
+        <f t="shared" ref="B132:B145" si="4">ROW(B132)-ROW($B$2)</f>
         <v>130</v>
       </c>
-      <c r="C132" s="11" t="s">
+      <c r="C132" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="D132" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="E132" s="13" t="s">
-        <v>541</v>
+      <c r="D132" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>537</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G132" s="13" t="s">
-        <v>542</v>
-      </c>
-      <c r="H132" s="12" t="s">
-        <v>543</v>
+        <v>538</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>506</v>
       </c>
       <c r="I132" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J132" s="12">
-        <v>1</v>
-      </c>
-      <c r="K132" s="12"/>
-    </row>
-    <row r="133" spans="1:11">
+      <c r="J132" s="9">
+        <v>1</v>
+      </c>
+      <c r="K132" s="9"/>
+    </row>
+    <row r="133" spans="1:11" ht="24">
       <c r="A133" s="2"/>
       <c r="B133" s="7">
-        <f>ROW(B133)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>131</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D133" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>545</v>
+      <c r="D133" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="E133" s="13" t="s">
+        <v>541</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="G133" s="10" t="s">
-        <v>547</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>506</v>
+        <v>34</v>
+      </c>
+      <c r="G133" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="H133" s="12" t="s">
+        <v>543</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J133" s="9">
-        <v>1</v>
-      </c>
-      <c r="K133" s="9"/>
-    </row>
-    <row r="134" ht="36.75" spans="1:11">
+      <c r="J133" s="12">
+        <v>1</v>
+      </c>
+      <c r="K133" s="12"/>
+    </row>
+    <row r="134" spans="1:11">
       <c r="A134" s="2"/>
       <c r="B134" s="7">
-        <f>ROW(B134)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>132</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>139</v>
+        <v>481</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>552</v>
+        <v>506</v>
       </c>
       <c r="I134" s="13" t="s">
         <v>145</v>
@@ -7339,336 +6709,390 @@
       </c>
       <c r="K134" s="9"/>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" ht="36">
       <c r="A135" s="2"/>
       <c r="B135" s="7">
-        <f>ROW(B135)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>133</v>
       </c>
-      <c r="C135" s="11" t="s">
-        <v>481</v>
-      </c>
-      <c r="D135" s="12" t="s">
-        <v>553</v>
-      </c>
-      <c r="E135" s="13" t="s">
-        <v>554</v>
-      </c>
-      <c r="F135" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="G135" s="13" t="s">
-        <v>555</v>
-      </c>
-      <c r="H135" s="12" t="s">
-        <v>556</v>
+      <c r="C135" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D135" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>552</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J135" s="12">
-        <v>1</v>
-      </c>
-      <c r="K135" s="12"/>
-    </row>
-    <row r="136" ht="36.75" spans="1:11">
+      <c r="J135" s="9">
+        <v>1</v>
+      </c>
+      <c r="K135" s="9"/>
+    </row>
+    <row r="136" spans="1:11" ht="24">
       <c r="A136" s="2"/>
       <c r="B136" s="7">
-        <f>ROW(B136)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>134</v>
       </c>
-      <c r="C136" s="8" t="s">
-        <v>557</v>
-      </c>
-      <c r="D136" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="F136" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="G136" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="H136" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="I136" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="J136" s="9">
-        <v>1</v>
-      </c>
-      <c r="K136" s="9"/>
-    </row>
-    <row r="137" ht="15.75" spans="1:11">
+      <c r="C136" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="G136" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="H136" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="I136" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="J136" s="12">
+        <v>1</v>
+      </c>
+      <c r="K136" s="12"/>
+    </row>
+    <row r="137" spans="1:11" ht="36">
       <c r="A137" s="2"/>
       <c r="B137" s="7">
-        <f>ROW(B137)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>135</v>
       </c>
-      <c r="C137" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="D137" s="12" t="s">
-        <v>565</v>
-      </c>
-      <c r="E137" s="13" t="s">
-        <v>566</v>
-      </c>
-      <c r="F137" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="G137" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="H137" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="I137" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="J137" s="12">
-        <v>2</v>
-      </c>
-      <c r="K137" s="12"/>
-    </row>
-    <row r="138" ht="36.75" spans="1:11">
+      <c r="C137" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="G137" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="I137" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="J137" s="9">
+        <v>1</v>
+      </c>
+      <c r="K137" s="9"/>
+    </row>
+    <row r="138" spans="1:11" ht="24">
       <c r="A138" s="2"/>
       <c r="B138" s="7">
-        <f>ROW(B138)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>136</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="E138" s="13" t="s">
+        <v>566</v>
+      </c>
+      <c r="F138" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="G138" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="H138" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="I138" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="J138" s="12">
+        <v>2</v>
+      </c>
+      <c r="K138" s="12"/>
+    </row>
+    <row r="139" spans="1:11" ht="36">
+      <c r="A139" s="2"/>
+      <c r="B139" s="7">
+        <f t="shared" si="4"/>
+        <v>137</v>
+      </c>
+      <c r="C139" s="8" t="s">
         <v>571</v>
       </c>
-      <c r="D138" s="9" t="s">
+      <c r="D139" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="E138" s="10" t="s">
+      <c r="E139" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="F138" s="9" t="s">
+      <c r="F139" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="G138" s="10" t="s">
+      <c r="G139" s="10" t="s">
         <v>575</v>
       </c>
-      <c r="H138" s="9" t="s">
+      <c r="H139" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="I138" s="10" t="s">
+      <c r="I139" s="10" t="s">
         <v>563</v>
       </c>
-      <c r="J138" s="9">
-        <v>1</v>
-      </c>
-      <c r="K138" s="9"/>
-    </row>
-    <row r="139" ht="24.75" spans="2:11">
-      <c r="B139" s="20">
-        <f>ROW(B139)-ROW($B$2)</f>
-        <v>137</v>
-      </c>
-      <c r="C139" s="21" t="s">
+      <c r="J139" s="9">
+        <v>1</v>
+      </c>
+      <c r="K139" s="9"/>
+    </row>
+    <row r="140" spans="1:11" ht="24">
+      <c r="B140" s="19">
+        <f t="shared" si="4"/>
+        <v>138</v>
+      </c>
+      <c r="C140" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="D139" s="19" t="s">
+      <c r="D140" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E139" s="22" t="s">
+      <c r="E140" s="21" t="s">
         <v>578</v>
       </c>
-      <c r="F139" s="19" t="s">
+      <c r="F140" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G139" s="22" t="s">
+      <c r="G140" s="21" t="s">
         <v>579</v>
       </c>
-      <c r="H139" s="19" t="s">
+      <c r="H140" s="18" t="s">
         <v>580</v>
       </c>
-      <c r="I139" s="22" t="s">
+      <c r="I140" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="J139" s="19">
+      <c r="J140" s="18">
         <v>2</v>
       </c>
-      <c r="K139" s="19"/>
-    </row>
-    <row r="140" ht="26.25" spans="2:11">
-      <c r="B140" s="20">
-        <f>ROW(B140)-ROW($B$2)</f>
-        <v>138</v>
-      </c>
-      <c r="C140" s="21" t="s">
+      <c r="K140" s="18"/>
+    </row>
+    <row r="141" spans="1:11" ht="25.5">
+      <c r="B141" s="19">
+        <f t="shared" si="4"/>
+        <v>139</v>
+      </c>
+      <c r="C141" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="D140" s="19" t="s">
+      <c r="D141" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E140" s="22" t="s">
+      <c r="E141" s="21" t="s">
         <v>581</v>
       </c>
-      <c r="F140" s="23" t="s">
+      <c r="F141" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="G140" s="22" t="s">
+      <c r="G141" s="21" t="s">
         <v>582</v>
       </c>
-      <c r="H140" s="19" t="s">
+      <c r="H141" s="18" t="s">
         <v>583</v>
       </c>
-      <c r="I140" s="22" t="s">
+      <c r="I141" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="J140" s="19">
-        <v>1</v>
-      </c>
-      <c r="K140" s="24" t="s">
+      <c r="J141" s="18">
+        <v>1</v>
+      </c>
+      <c r="K141" s="23" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="141" ht="36.75" spans="2:11">
-      <c r="B141" s="20">
-        <f>ROW(B141)-ROW($B$2)</f>
-        <v>139</v>
-      </c>
-      <c r="C141" s="21" t="s">
+    <row r="142" spans="1:11" ht="36">
+      <c r="B142" s="19">
+        <f t="shared" si="4"/>
+        <v>140</v>
+      </c>
+      <c r="C142" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="D141" s="19" t="s">
+      <c r="D142" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E141" s="18" t="s">
+      <c r="E142" s="17" t="s">
         <v>585</v>
       </c>
-      <c r="F141" s="23" t="s">
+      <c r="F142" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="G141" s="18" t="s">
+      <c r="G142" s="17" t="s">
         <v>586</v>
       </c>
-      <c r="H141" s="23" t="s">
+      <c r="H142" s="22" t="s">
         <v>587</v>
       </c>
-      <c r="I141" s="18" t="s">
+      <c r="I142" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="J141" s="23">
-        <v>1</v>
-      </c>
-      <c r="K141" s="23"/>
-    </row>
-    <row r="142" ht="24.75" spans="2:11">
-      <c r="B142" s="20">
-        <f>ROW(B142)-ROW($B$2)</f>
-        <v>140</v>
-      </c>
-      <c r="C142" s="21" t="s">
+      <c r="J142" s="22">
+        <v>1</v>
+      </c>
+      <c r="K142" s="22"/>
+    </row>
+    <row r="143" spans="1:11" ht="24">
+      <c r="B143" s="19">
+        <f t="shared" si="4"/>
+        <v>141</v>
+      </c>
+      <c r="C143" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="D142" s="19" t="s">
+      <c r="D143" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E142" s="18" t="s">
+      <c r="E143" s="17" t="s">
         <v>588</v>
       </c>
-      <c r="F142" s="23" t="s">
+      <c r="F143" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="G142" s="18" t="s">
+      <c r="G143" s="17" t="s">
         <v>589</v>
       </c>
-      <c r="H142" s="23" t="s">
+      <c r="H143" s="22" t="s">
         <v>590</v>
       </c>
-      <c r="I142" s="18" t="s">
+      <c r="I143" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="J142" s="23">
+      <c r="J143" s="22">
         <v>2</v>
       </c>
-      <c r="K142" s="23"/>
-    </row>
-    <row r="143" ht="36.75" spans="2:11">
-      <c r="B143" s="20">
-        <f>ROW(B143)-ROW($B$2)</f>
-        <v>141</v>
-      </c>
-      <c r="C143" s="21" t="s">
+      <c r="K143" s="22"/>
+    </row>
+    <row r="144" spans="1:11" ht="36">
+      <c r="B144" s="19">
+        <f t="shared" si="4"/>
+        <v>142</v>
+      </c>
+      <c r="C144" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="D143" s="19" t="s">
+      <c r="D144" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E143" s="18" t="s">
+      <c r="E144" s="13" t="s">
+        <v>595</v>
+      </c>
+      <c r="F144" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="G144" s="17"/>
+      <c r="H144" s="22"/>
+      <c r="I144" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="J144" s="22">
+        <v>1</v>
+      </c>
+      <c r="K144" s="9" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="145" spans="2:11" ht="24.75" thickBot="1">
+      <c r="B145" s="19">
+        <f t="shared" si="4"/>
+        <v>143</v>
+      </c>
+      <c r="C145" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="D145" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="E145" s="17" t="s">
         <v>591</v>
       </c>
-      <c r="F143" s="23" t="s">
+      <c r="F145" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="G143" s="18" t="s">
+      <c r="G145" s="17" t="s">
         <v>592</v>
       </c>
-      <c r="H143" s="23" t="s">
+      <c r="H145" s="22" t="s">
         <v>593</v>
       </c>
-      <c r="I143" s="18" t="s">
+      <c r="I145" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="J143" s="23">
-        <v>1</v>
-      </c>
-      <c r="K143" s="25" t="s">
+      <c r="J145" s="22">
+        <v>1</v>
+      </c>
+      <c r="K145" s="22" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="144" ht="24.75" spans="2:11">
-      <c r="B144" s="20">
-        <f>ROW(B144)-ROW($B$2)</f>
-        <v>142</v>
-      </c>
-      <c r="C144" s="21" t="s">
+    <row r="146" spans="2:11" ht="24.75" thickBot="1">
+      <c r="B146" s="19">
+        <f>ROW(B146)-ROW($B$2)</f>
+        <v>144</v>
+      </c>
+      <c r="C146" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="D144" s="19" t="s">
+      <c r="D146" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E144" s="18" t="s">
-        <v>595</v>
-      </c>
-      <c r="F144" s="23" t="s">
+      <c r="E146" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="F146" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="G144" s="18" t="s">
-        <v>596</v>
-      </c>
-      <c r="H144" s="23" t="s">
-        <v>597</v>
-      </c>
-      <c r="I144" s="18" t="s">
+      <c r="G146" s="17">
+        <v>8900</v>
+      </c>
+      <c r="H146" s="22" t="s">
+        <v>598</v>
+      </c>
+      <c r="I146" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="J144" s="23">
-        <v>1</v>
-      </c>
-      <c r="K144" s="25" t="s">
-        <v>598</v>
-      </c>
+      <c r="J146" s="22">
+        <v>4</v>
+      </c>
+      <c r="K146" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I1:K1"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="K143" r:id="rId1" location="nav-specification" display="Aliexpress"/>
-    <hyperlink ref="K144" r:id="rId2" display="Alibaba"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Design-Files/OFP_MCM_v1.6/BOM/Client-BOM-OFP_MCM_v1.6.xlsx
+++ b/Design-Files/OFP_MCM_v1.6/BOM/Client-BOM-OFP_MCM_v1.6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\nabilfesal-smartmeter-hw\Design-Files\OFP_MCM_v1.6\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A98945-5294-4151-BCE5-7C6D46AA9351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921413CF-EB97-46D2-9211-A9537C381431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -615,12 +615,6 @@
     <t>J4</t>
   </si>
   <si>
-    <t>CONN FFC BOTTOM 40POS 0.5MM R/A</t>
-  </si>
-  <si>
-    <t>FH41-40S-0.5SH(05)</t>
-  </si>
-  <si>
     <t>Hirose</t>
   </si>
   <si>
@@ -1840,6 +1834,12 @@
   </si>
   <si>
     <t>SMF3.3</t>
+  </si>
+  <si>
+    <t>CONN FFC FPC 40POS 0.5MM R/A Top Bottom</t>
+  </si>
+  <si>
+    <t>FH34SRJ-40S-0.5SH(50)</t>
   </si>
 </sst>
 </file>
@@ -3663,16 +3663,16 @@
         <v>168</v>
       </c>
       <c r="D40" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="F40" s="9" t="s">
         <v>599</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="G40" s="10" t="s">
         <v>600</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>602</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>172</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K44" s="9"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" ht="24">
       <c r="A45" s="2"/>
       <c r="B45" s="7">
         <f t="shared" si="1"/>
@@ -3826,16 +3826,16 @@
         <v>193</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>194</v>
+        <v>601</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>195</v>
+        <v>602</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I45" s="10" t="s">
         <v>145</v>
@@ -3852,22 +3852,22 @@
         <v>44</v>
       </c>
       <c r="C46" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E46" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I46" s="10" t="s">
         <v>145</v>
@@ -3884,22 +3884,22 @@
         <v>45</v>
       </c>
       <c r="C47" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="E47" s="15" t="s">
         <v>197</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>199</v>
       </c>
       <c r="F47" s="14" t="s">
         <v>34</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>136</v>
@@ -3918,22 +3918,22 @@
         <v>46</v>
       </c>
       <c r="C48" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E48" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>145</v>
@@ -3950,25 +3950,25 @@
         <v>47</v>
       </c>
       <c r="C49" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="I49" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="J49" s="9">
         <v>1</v>
@@ -3982,25 +3982,25 @@
         <v>48</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>213</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>215</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G50" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="I50" s="13" t="s">
         <v>216</v>
-      </c>
-      <c r="H50" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>218</v>
       </c>
       <c r="J50" s="12">
         <v>3</v>
@@ -4014,25 +4014,25 @@
         <v>49</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J51" s="9">
         <v>1</v>
@@ -4046,25 +4046,25 @@
         <v>50</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I52" s="13" t="s">
         <v>225</v>
-      </c>
-      <c r="H52" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>227</v>
       </c>
       <c r="J52" s="12">
         <v>1</v>
@@ -4078,19 +4078,19 @@
         <v>51</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F53" s="14" t="s">
         <v>176</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H53" s="14" t="s">
         <v>15</v>
@@ -4112,22 +4112,22 @@
         <v>52</v>
       </c>
       <c r="C54" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E54" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="F54" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="E54" s="13" t="s">
+      <c r="G54" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="F54" s="12" t="s">
+      <c r="H54" s="12" t="s">
         <v>234</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="H54" s="12" t="s">
-        <v>236</v>
       </c>
       <c r="I54" s="13" t="s">
         <v>145</v>
@@ -4144,22 +4144,22 @@
         <v>53</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D55" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="G55" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="H55" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>145</v>
@@ -4176,22 +4176,22 @@
         <v>54</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D56" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F56" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="E56" s="13" t="s">
+      <c r="G56" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="F56" s="12" t="s">
+      <c r="H56" s="12" t="s">
         <v>244</v>
-      </c>
-      <c r="G56" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H56" s="12" t="s">
-        <v>246</v>
       </c>
       <c r="I56" s="13" t="s">
         <v>145</v>
@@ -4208,22 +4208,22 @@
         <v>55</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D57" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="F57" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="G57" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>250</v>
-      </c>
       <c r="H57" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>145</v>
@@ -4240,22 +4240,22 @@
         <v>56</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D58" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="G58" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="E58" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="F58" s="12" t="s">
+      <c r="H58" s="12" t="s">
         <v>239</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>241</v>
       </c>
       <c r="I58" s="13" t="s">
         <v>145</v>
@@ -4272,22 +4272,22 @@
         <v>57</v>
       </c>
       <c r="C59" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E59" s="10" t="s">
         <v>254</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>256</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>145</v>
@@ -4304,19 +4304,19 @@
         <v>58</v>
       </c>
       <c r="C60" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="F60" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="G60" s="13" t="s">
         <v>261</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="G60" s="13" t="s">
-        <v>263</v>
       </c>
       <c r="H60" s="12" t="s">
         <v>156</v>
@@ -4336,22 +4336,22 @@
         <v>59</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D61" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="F61" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="G61" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="H61" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>145</v>
@@ -4368,25 +4368,25 @@
         <v>60</v>
       </c>
       <c r="C62" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E62" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="F62" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="E62" s="13" t="s">
+      <c r="G62" s="13" t="s">
         <v>271</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G62" s="13" t="s">
-        <v>273</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J62" s="12">
         <v>7</v>
@@ -4400,25 +4400,25 @@
         <v>61</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D63" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>275</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>277</v>
       </c>
       <c r="H63" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J63" s="9">
         <v>1</v>
@@ -4432,25 +4432,25 @@
         <v>62</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D64" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G64" s="13" t="s">
         <v>279</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G64" s="13" t="s">
-        <v>281</v>
       </c>
       <c r="H64" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J64" s="12">
         <v>1</v>
@@ -4464,25 +4464,25 @@
         <v>63</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D65" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G65" s="10" t="s">
         <v>283</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>285</v>
       </c>
       <c r="H65" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J65" s="9">
         <v>1</v>
@@ -4496,25 +4496,25 @@
         <v>64</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D66" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G66" s="13" t="s">
         <v>287</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G66" s="13" t="s">
-        <v>289</v>
       </c>
       <c r="H66" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J66" s="12">
         <v>1</v>
@@ -4528,25 +4528,25 @@
         <v>65</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D67" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="F67" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="G67" s="10" t="s">
         <v>292</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>294</v>
       </c>
       <c r="H67" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J67" s="9">
         <v>1</v>
@@ -4560,25 +4560,25 @@
         <v>66</v>
       </c>
       <c r="C68" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="E68" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="F68" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G68" s="13" t="s">
         <v>297</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G68" s="13" t="s">
-        <v>299</v>
       </c>
       <c r="H68" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J68" s="12">
         <v>1</v>
@@ -4592,25 +4592,25 @@
         <v>67</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D69" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G69" s="10" t="s">
         <v>301</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G69" s="10" t="s">
-        <v>303</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J69" s="9">
         <v>1</v>
@@ -4624,25 +4624,25 @@
         <v>68</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D70" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G70" s="13" t="s">
         <v>305</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G70" s="13" t="s">
-        <v>307</v>
       </c>
       <c r="H70" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J70" s="12">
         <v>1</v>
@@ -4656,25 +4656,25 @@
         <v>69</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D71" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G71" s="10" t="s">
         <v>308</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>310</v>
       </c>
       <c r="H71" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J71" s="9">
         <v>1</v>
@@ -4688,25 +4688,25 @@
         <v>70</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D72" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G72" s="13" t="s">
         <v>312</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G72" s="13" t="s">
-        <v>314</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J72" s="12">
         <v>1</v>
@@ -4720,25 +4720,25 @@
         <v>71</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D73" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G73" s="10" t="s">
         <v>316</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>318</v>
       </c>
       <c r="H73" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J73" s="9">
         <v>6</v>
@@ -4752,25 +4752,25 @@
         <v>72</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D74" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G74" s="13" t="s">
         <v>320</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G74" s="13" t="s">
-        <v>322</v>
       </c>
       <c r="H74" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J74" s="12">
         <v>1</v>
@@ -4784,25 +4784,25 @@
         <v>73</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D75" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G75" s="10" t="s">
         <v>324</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>326</v>
       </c>
       <c r="H75" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J75" s="9">
         <v>18</v>
@@ -4816,25 +4816,25 @@
         <v>74</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D76" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G76" s="13" t="s">
         <v>328</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G76" s="13" t="s">
-        <v>330</v>
       </c>
       <c r="H76" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J76" s="12">
         <v>2</v>
@@ -4848,25 +4848,25 @@
         <v>75</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D77" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G77" s="10" t="s">
         <v>332</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>334</v>
       </c>
       <c r="H77" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J77" s="9">
         <v>1</v>
@@ -4880,25 +4880,25 @@
         <v>76</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D78" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G78" s="13" t="s">
         <v>336</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G78" s="13" t="s">
-        <v>338</v>
       </c>
       <c r="H78" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J78" s="12">
         <v>1</v>
@@ -4912,25 +4912,25 @@
         <v>77</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D79" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G79" s="10" t="s">
         <v>340</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>342</v>
       </c>
       <c r="H79" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J79" s="9">
         <v>10</v>
@@ -4944,25 +4944,25 @@
         <v>78</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D80" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G80" s="13" t="s">
         <v>343</v>
-      </c>
-      <c r="E80" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G80" s="13" t="s">
-        <v>345</v>
       </c>
       <c r="H80" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J80" s="12">
         <v>1</v>
@@ -4976,25 +4976,25 @@
         <v>79</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D81" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G81" s="10" t="s">
         <v>347</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>349</v>
       </c>
       <c r="H81" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J81" s="9">
         <v>1</v>
@@ -5008,25 +5008,25 @@
         <v>80</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D82" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G82" s="13" t="s">
         <v>351</v>
-      </c>
-      <c r="E82" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G82" s="13" t="s">
-        <v>353</v>
       </c>
       <c r="H82" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J82" s="12">
         <v>1</v>
@@ -5040,25 +5040,25 @@
         <v>81</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D83" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G83" s="10" t="s">
         <v>355</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>357</v>
       </c>
       <c r="H83" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J83" s="9">
         <v>1</v>
@@ -5072,25 +5072,25 @@
         <v>82</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D84" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G84" s="13" t="s">
         <v>359</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G84" s="13" t="s">
-        <v>361</v>
       </c>
       <c r="H84" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J84" s="12">
         <v>1</v>
@@ -5104,25 +5104,25 @@
         <v>83</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D85" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G85" s="10" t="s">
         <v>363</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>365</v>
       </c>
       <c r="H85" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J85" s="9">
         <v>7</v>
@@ -5136,25 +5136,25 @@
         <v>84</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D86" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="F86" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G86" s="13" t="s">
         <v>366</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="F86" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G86" s="13" t="s">
-        <v>368</v>
       </c>
       <c r="H86" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J86" s="12">
         <v>4</v>
@@ -5168,25 +5168,25 @@
         <v>85</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D87" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G87" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>372</v>
       </c>
       <c r="H87" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J87" s="9">
         <v>5</v>
@@ -5200,25 +5200,25 @@
         <v>86</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D88" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G88" s="13" t="s">
         <v>373</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="F88" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G88" s="13" t="s">
-        <v>375</v>
       </c>
       <c r="H88" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J88" s="12">
         <v>1</v>
@@ -5232,25 +5232,25 @@
         <v>87</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D89" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G89" s="17" t="s">
         <v>377</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G89" s="17" t="s">
-        <v>379</v>
       </c>
       <c r="H89" s="18" t="s">
         <v>74</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J89" s="9">
         <v>2</v>
@@ -5264,25 +5264,25 @@
         <v>88</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D90" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G90" s="13" t="s">
         <v>381</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="F90" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G90" s="13" t="s">
-        <v>383</v>
       </c>
       <c r="H90" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J90" s="12">
         <v>1</v>
@@ -5296,25 +5296,25 @@
         <v>89</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D91" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G91" s="10" t="s">
         <v>385</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>387</v>
       </c>
       <c r="H91" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J91" s="9">
         <v>1</v>
@@ -5328,25 +5328,25 @@
         <v>90</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D92" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G92" s="13" t="s">
         <v>389</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="F92" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G92" s="13" t="s">
-        <v>391</v>
       </c>
       <c r="H92" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J92" s="12">
         <v>1</v>
@@ -5360,25 +5360,25 @@
         <v>91</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D93" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G93" s="10" t="s">
         <v>393</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>395</v>
       </c>
       <c r="H93" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J93" s="9">
         <v>1</v>
@@ -5392,25 +5392,25 @@
         <v>92</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D94" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G94" s="13" t="s">
         <v>397</v>
-      </c>
-      <c r="E94" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="F94" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G94" s="13" t="s">
-        <v>399</v>
       </c>
       <c r="H94" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J94" s="12">
         <v>1</v>
@@ -5424,25 +5424,25 @@
         <v>93</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D95" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G95" s="10" t="s">
         <v>401</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>403</v>
       </c>
       <c r="H95" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J95" s="9">
         <v>1</v>
@@ -5456,25 +5456,25 @@
         <v>94</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D96" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G96" s="13" t="s">
         <v>405</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="F96" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G96" s="13" t="s">
-        <v>407</v>
       </c>
       <c r="H96" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J96" s="12">
         <v>3</v>
@@ -5488,25 +5488,25 @@
         <v>95</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D97" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G97" s="10" t="s">
         <v>409</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>411</v>
       </c>
       <c r="H97" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J97" s="9">
         <v>6</v>
@@ -5520,25 +5520,25 @@
         <v>96</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D98" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="F98" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G98" s="13" t="s">
         <v>413</v>
-      </c>
-      <c r="E98" s="13" t="s">
-        <v>414</v>
-      </c>
-      <c r="F98" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G98" s="13" t="s">
-        <v>415</v>
       </c>
       <c r="H98" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J98" s="12">
         <v>1</v>
@@ -5552,25 +5552,25 @@
         <v>97</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D99" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G99" s="10" t="s">
         <v>417</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>419</v>
       </c>
       <c r="H99" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J99" s="9">
         <v>1</v>
@@ -5584,25 +5584,25 @@
         <v>98</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D100" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="F100" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G100" s="13" t="s">
         <v>421</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="F100" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G100" s="13" t="s">
-        <v>423</v>
       </c>
       <c r="H100" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J100" s="12">
         <v>1</v>
@@ -5616,25 +5616,25 @@
         <v>99</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D101" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G101" s="10" t="s">
         <v>425</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G101" s="10" t="s">
-        <v>427</v>
       </c>
       <c r="H101" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J101" s="9">
         <v>2</v>
@@ -5648,19 +5648,19 @@
         <v>100</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G102" s="15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H102" s="14" t="s">
         <v>74</v>
@@ -5682,19 +5682,19 @@
         <v>101</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G103" s="15" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H103" s="14" t="s">
         <v>74</v>
@@ -5716,25 +5716,25 @@
         <v>102</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D104" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G104" s="13" t="s">
         <v>431</v>
-      </c>
-      <c r="E104" s="13" t="s">
-        <v>432</v>
-      </c>
-      <c r="F104" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G104" s="13" t="s">
-        <v>433</v>
       </c>
       <c r="H104" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J104" s="12">
         <v>1</v>
@@ -5748,25 +5748,25 @@
         <v>103</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D105" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G105" s="10" t="s">
         <v>435</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G105" s="10" t="s">
-        <v>437</v>
       </c>
       <c r="H105" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J105" s="9">
         <v>1</v>
@@ -5780,25 +5780,25 @@
         <v>104</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D106" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="F106" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G106" s="13" t="s">
         <v>439</v>
-      </c>
-      <c r="E106" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="F106" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G106" s="13" t="s">
-        <v>441</v>
       </c>
       <c r="H106" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J106" s="12">
         <v>1</v>
@@ -5812,25 +5812,25 @@
         <v>105</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D107" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G107" s="10" t="s">
         <v>443</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>445</v>
       </c>
       <c r="H107" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J107" s="9">
         <v>1</v>
@@ -5844,19 +5844,19 @@
         <v>106</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H108" s="14" t="s">
         <v>74</v>
@@ -5878,25 +5878,25 @@
         <v>107</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D109" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G109" s="10" t="s">
         <v>447</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F109" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G109" s="10" t="s">
-        <v>449</v>
       </c>
       <c r="H109" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J109" s="9">
         <v>1</v>
@@ -5910,19 +5910,19 @@
         <v>108</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H110" s="14" t="s">
         <v>74</v>
@@ -5944,25 +5944,25 @@
         <v>109</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D111" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G111" s="10" t="s">
         <v>451</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="F111" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G111" s="10" t="s">
-        <v>453</v>
       </c>
       <c r="H111" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J111" s="9">
         <v>4</v>
@@ -5976,25 +5976,25 @@
         <v>110</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D112" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="F112" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G112" s="13" t="s">
         <v>455</v>
-      </c>
-      <c r="E112" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="F112" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G112" s="13" t="s">
-        <v>457</v>
       </c>
       <c r="H112" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J112" s="12">
         <v>1</v>
@@ -6008,19 +6008,19 @@
         <v>111</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G113" s="15" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H113" s="14" t="s">
         <v>74</v>
@@ -6042,19 +6042,19 @@
         <v>112</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H114" s="14" t="s">
         <v>74</v>
@@ -6076,25 +6076,25 @@
         <v>113</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D115" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="F115" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="E115" s="13" t="s">
+      <c r="G115" s="13" t="s">
         <v>461</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="G115" s="13" t="s">
-        <v>463</v>
       </c>
       <c r="H115" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J115" s="12">
         <v>6</v>
@@ -6108,25 +6108,25 @@
         <v>114</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D116" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G116" s="10" t="s">
         <v>464</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="F116" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G116" s="10" t="s">
-        <v>466</v>
       </c>
       <c r="H116" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J116" s="9">
         <v>1</v>
@@ -6140,22 +6140,22 @@
         <v>115</v>
       </c>
       <c r="C117" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="E117" s="13" t="s">
         <v>468</v>
-      </c>
-      <c r="D117" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>470</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G117" s="13" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="I117" s="13" t="s">
         <v>145</v>
@@ -6172,22 +6172,22 @@
         <v>116</v>
       </c>
       <c r="C118" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="E118" s="10" t="s">
         <v>473</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>475</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G118" s="10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="I118" s="13" t="s">
         <v>145</v>
@@ -6204,22 +6204,22 @@
         <v>117</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G119" s="13" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="I119" s="13" t="s">
         <v>145</v>
@@ -6236,22 +6236,22 @@
         <v>118</v>
       </c>
       <c r="C120" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="E120" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="D120" s="9" t="s">
+      <c r="F120" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="E120" s="10" t="s">
+      <c r="G120" s="10" t="s">
         <v>483</v>
       </c>
-      <c r="F120" s="9" t="s">
+      <c r="H120" s="9" t="s">
         <v>484</v>
-      </c>
-      <c r="G120" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="H120" s="9" t="s">
-        <v>486</v>
       </c>
       <c r="I120" s="13" t="s">
         <v>145</v>
@@ -6268,22 +6268,22 @@
         <v>119</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D121" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="F121" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="E121" s="13" t="s">
+      <c r="G121" s="13" t="s">
         <v>488</v>
       </c>
-      <c r="F121" s="12" t="s">
+      <c r="H121" s="12" t="s">
         <v>489</v>
-      </c>
-      <c r="G121" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="H121" s="12" t="s">
-        <v>491</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>145</v>
@@ -6300,22 +6300,22 @@
         <v>120</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D122" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="F122" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="E122" s="10" t="s">
+      <c r="G122" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="F122" s="9" t="s">
+      <c r="H122" s="9" t="s">
         <v>494</v>
-      </c>
-      <c r="G122" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="H122" s="9" t="s">
-        <v>496</v>
       </c>
       <c r="I122" s="13" t="s">
         <v>145</v>
@@ -6332,22 +6332,22 @@
         <v>121</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D123" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>496</v>
+      </c>
+      <c r="F123" s="12" t="s">
         <v>497</v>
       </c>
-      <c r="E123" s="13" t="s">
+      <c r="G123" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="F123" s="12" t="s">
+      <c r="H123" s="12" t="s">
         <v>499</v>
-      </c>
-      <c r="G123" s="13" t="s">
-        <v>500</v>
-      </c>
-      <c r="H123" s="12" t="s">
-        <v>501</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>145</v>
@@ -6364,22 +6364,22 @@
         <v>122</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D124" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="F124" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="E124" s="10" t="s">
+      <c r="G124" s="10" t="s">
         <v>503</v>
       </c>
-      <c r="F124" s="9" t="s">
+      <c r="H124" s="9" t="s">
         <v>504</v>
-      </c>
-      <c r="G124" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="H124" s="9" t="s">
-        <v>506</v>
       </c>
       <c r="I124" s="13" t="s">
         <v>145</v>
@@ -6396,22 +6396,22 @@
         <v>123</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D125" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="F125" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="E125" s="13" t="s">
+      <c r="G125" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="F125" s="12" t="s">
-        <v>509</v>
-      </c>
-      <c r="G125" s="13" t="s">
-        <v>510</v>
-      </c>
       <c r="H125" s="12" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>145</v>
@@ -6428,22 +6428,22 @@
         <v>124</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D126" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="F126" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="E126" s="10" t="s">
+      <c r="G126" s="10" t="s">
         <v>512</v>
       </c>
-      <c r="F126" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="G126" s="10" t="s">
-        <v>514</v>
-      </c>
       <c r="H126" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I126" s="13" t="s">
         <v>145</v>
@@ -6460,22 +6460,22 @@
         <v>125</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D127" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="F127" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="E127" s="13" t="s">
+      <c r="G127" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="F127" s="12" t="s">
-        <v>517</v>
-      </c>
-      <c r="G127" s="13" t="s">
-        <v>518</v>
-      </c>
       <c r="H127" s="12" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>145</v>
@@ -6492,22 +6492,22 @@
         <v>126</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D128" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="G128" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="E128" s="10" t="s">
+      <c r="H128" s="9" t="s">
         <v>520</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="G128" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="H128" s="9" t="s">
-        <v>522</v>
       </c>
       <c r="I128" s="13" t="s">
         <v>145</v>
@@ -6524,22 +6524,22 @@
         <v>127</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D129" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="F129" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="E129" s="13" t="s">
+      <c r="G129" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="F129" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="G129" s="13" t="s">
-        <v>526</v>
-      </c>
       <c r="H129" s="12" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>145</v>
@@ -6556,22 +6556,22 @@
         <v>128</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D130" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="F130" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="E130" s="10" t="s">
+      <c r="G130" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="F130" s="9" t="s">
+      <c r="H130" s="9" t="s">
         <v>529</v>
-      </c>
-      <c r="G130" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="H130" s="9" t="s">
-        <v>531</v>
       </c>
       <c r="I130" s="13" t="s">
         <v>145</v>
@@ -6588,22 +6588,22 @@
         <v>129</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D131" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>531</v>
+      </c>
+      <c r="F131" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="E131" s="13" t="s">
+      <c r="G131" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="F131" s="12" t="s">
-        <v>534</v>
-      </c>
-      <c r="G131" s="13" t="s">
-        <v>535</v>
-      </c>
       <c r="H131" s="12" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>145</v>
@@ -6620,22 +6620,22 @@
         <v>130</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D132" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="F132" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="E132" s="10" t="s">
+      <c r="G132" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="F132" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="G132" s="10" t="s">
-        <v>539</v>
-      </c>
       <c r="H132" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I132" s="13" t="s">
         <v>145</v>
@@ -6652,22 +6652,22 @@
         <v>131</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G133" s="13" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>145</v>
@@ -6684,22 +6684,22 @@
         <v>132</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D134" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="F134" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="E134" s="10" t="s">
+      <c r="G134" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="F134" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="G134" s="10" t="s">
-        <v>547</v>
-      </c>
       <c r="H134" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="I134" s="13" t="s">
         <v>145</v>
@@ -6719,19 +6719,19 @@
         <v>139</v>
       </c>
       <c r="D135" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="F135" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="E135" s="10" t="s">
+      <c r="G135" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="F135" s="9" t="s">
+      <c r="H135" s="9" t="s">
         <v>550</v>
-      </c>
-      <c r="G135" s="10" t="s">
-        <v>551</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>552</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>145</v>
@@ -6748,22 +6748,22 @@
         <v>134</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D136" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="G136" s="13" t="s">
         <v>553</v>
       </c>
-      <c r="E136" s="13" t="s">
+      <c r="H136" s="12" t="s">
         <v>554</v>
-      </c>
-      <c r="F136" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="G136" s="13" t="s">
-        <v>555</v>
-      </c>
-      <c r="H136" s="12" t="s">
-        <v>556</v>
       </c>
       <c r="I136" s="13" t="s">
         <v>145</v>
@@ -6780,25 +6780,25 @@
         <v>135</v>
       </c>
       <c r="C137" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="E137" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="D137" s="9" t="s">
+      <c r="F137" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="E137" s="10" t="s">
+      <c r="G137" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="F137" s="9" t="s">
+      <c r="H137" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="G137" s="10" t="s">
+      <c r="I137" s="10" t="s">
         <v>561</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="I137" s="10" t="s">
-        <v>563</v>
       </c>
       <c r="J137" s="9">
         <v>1</v>
@@ -6812,25 +6812,25 @@
         <v>136</v>
       </c>
       <c r="C138" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="E138" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="D138" s="12" t="s">
+      <c r="F138" s="12" t="s">
         <v>565</v>
       </c>
-      <c r="E138" s="13" t="s">
+      <c r="G138" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="F138" s="12" t="s">
+      <c r="H138" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="G138" s="13" t="s">
+      <c r="I138" s="13" t="s">
         <v>568</v>
-      </c>
-      <c r="H138" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="I138" s="13" t="s">
-        <v>570</v>
       </c>
       <c r="J138" s="12">
         <v>2</v>
@@ -6844,25 +6844,25 @@
         <v>137</v>
       </c>
       <c r="C139" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="E139" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="D139" s="9" t="s">
+      <c r="F139" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="E139" s="10" t="s">
+      <c r="G139" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="F139" s="9" t="s">
+      <c r="H139" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="G139" s="10" t="s">
-        <v>575</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>576</v>
-      </c>
       <c r="I139" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J139" s="9">
         <v>1</v>
@@ -6875,22 +6875,22 @@
         <v>138</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>145</v>
       </c>
       <c r="E140" s="21" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F140" s="18" t="s">
         <v>34</v>
       </c>
       <c r="G140" s="21" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H140" s="18" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="I140" s="21" t="s">
         <v>145</v>
@@ -6906,22 +6906,22 @@
         <v>139</v>
       </c>
       <c r="C141" s="20" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D141" s="18" t="s">
         <v>145</v>
       </c>
       <c r="E141" s="21" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F141" s="22" t="s">
         <v>34</v>
       </c>
       <c r="G141" s="21" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H141" s="18" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="I141" s="21" t="s">
         <v>145</v>
@@ -6930,7 +6930,7 @@
         <v>1</v>
       </c>
       <c r="K141" s="23" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="36">
@@ -6939,22 +6939,22 @@
         <v>140</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D142" s="18" t="s">
         <v>145</v>
       </c>
       <c r="E142" s="17" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F142" s="22" t="s">
         <v>34</v>
       </c>
       <c r="G142" s="17" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H142" s="22" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="I142" s="17" t="s">
         <v>145</v>
@@ -6970,22 +6970,22 @@
         <v>141</v>
       </c>
       <c r="C143" s="20" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>145</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F143" s="22" t="s">
         <v>34</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="H143" s="22" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="I143" s="17" t="s">
         <v>145</v>
@@ -7001,13 +7001,13 @@
         <v>142</v>
       </c>
       <c r="C144" s="20" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D144" s="18" t="s">
         <v>145</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F144" s="22" t="s">
         <v>34</v>
@@ -7021,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="K144" s="9" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="145" spans="2:11" ht="24.75" thickBot="1">
@@ -7030,22 +7030,22 @@
         <v>143</v>
       </c>
       <c r="C145" s="20" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D145" s="18" t="s">
         <v>145</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F145" s="22" t="s">
         <v>34</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="H145" s="22" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="I145" s="17" t="s">
         <v>145</v>
@@ -7054,7 +7054,7 @@
         <v>1</v>
       </c>
       <c r="K145" s="22" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="146" spans="2:11" ht="24.75" thickBot="1">
@@ -7063,13 +7063,13 @@
         <v>144</v>
       </c>
       <c r="C146" s="20" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D146" s="18" t="s">
         <v>145</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F146" s="22" t="s">
         <v>34</v>
@@ -7078,7 +7078,7 @@
         <v>8900</v>
       </c>
       <c r="H146" s="22" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="I146" s="17" t="s">
         <v>145</v>

--- a/Design-Files/OFP_MCM_v1.6/BOM/Client-BOM-OFP_MCM_v1.6.xlsx
+++ b/Design-Files/OFP_MCM_v1.6/BOM/Client-BOM-OFP_MCM_v1.6.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\nabilfesal-smartmeter-hw\Design-Files\OFP_MCM_v1.6\BOM\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921413CF-EB97-46D2-9211-A9537C381431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="638">
   <si>
     <t>#</t>
   </si>
@@ -99,7 +95,7 @@
     <t>Capacitor</t>
   </si>
   <si>
-    <t>C4, C11, C16, C20, C33, C37, C41, C57, C58, C93, C94, C149</t>
+    <t>C4, C11, C16, C20, C33, C37, C41, C57, C58, C93, C94</t>
   </si>
   <si>
     <t>CAP CER 10UF 10V X7R 0603</t>
@@ -114,7 +110,7 @@
     <t>10uF</t>
   </si>
   <si>
-    <t>C7, C12, C13, C14, C15, C18, C19, C24, C27, C28, C29, C30, C31, C35, C36, C39, C40, C43, C44, C46, C95, C97, C111, C114, C117, C120, C124, C127, C130, C133</t>
+    <t>C7, C12, C13, C14, C15, C18, C19, C24, C27, C28, C29, C30, C31, C35, C36, C39, C40, C43, C44, C46, C95, C97, C111, C114, C117, C120, C124, C127, C130, C133, C149, C150</t>
   </si>
   <si>
     <t>CAP CER 0.1UF 25V X7R 0402</t>
@@ -147,7 +143,7 @@
     <t>0.47F</t>
   </si>
   <si>
-    <t>C9, C49, C52, C53, C59, C75, C80, C83, C101, C106, C139, C140</t>
+    <t>C9, C49, C52, C53, C59, C75, C80, C83, C101, C106, C139, C140, C151</t>
   </si>
   <si>
     <t>CAP CER 0.1UF 50V X7R 0603</t>
@@ -207,7 +203,7 @@
     <t>10nF</t>
   </si>
   <si>
-    <t>C47, C48, C78, C79, C89, C90, C91, C92, C104</t>
+    <t>C47, C48, C78, C79, C89, C90, C91, C92, C104, C153</t>
   </si>
   <si>
     <t>CAP CER 10UF 50V X7R 1210</t>
@@ -273,7 +269,7 @@
     <t>33nF</t>
   </si>
   <si>
-    <t>C60, C61, C67, C68, C76, C77, C81, C82</t>
+    <t>C60, C61, C67, C68, C76, C77, C81, C82, C154, C155</t>
   </si>
   <si>
     <t>CAP CER 22UF 6.3V X7R 0805</t>
@@ -444,12 +440,51 @@
     <t>DNP</t>
   </si>
   <si>
-    <t>DO NOT PLACE</t>
-  </si>
-  <si>
     <t>C143</t>
   </si>
   <si>
+    <t>C152</t>
+  </si>
+  <si>
+    <t>CAP CER 47UF 25V X5R 1206</t>
+  </si>
+  <si>
+    <t>Cap-1206</t>
+  </si>
+  <si>
+    <t>C3216X5R1E476M160AC</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>47uF</t>
+  </si>
+  <si>
+    <t>C156</t>
+  </si>
+  <si>
+    <t>CAP CER 22UF 25V X5R 0805</t>
+  </si>
+  <si>
+    <t>CC0805MKX5R8BB226</t>
+  </si>
+  <si>
+    <t>C157</t>
+  </si>
+  <si>
+    <t>CAP TANT 100UF 20% 25V 2917</t>
+  </si>
+  <si>
+    <t>Case-E</t>
+  </si>
+  <si>
+    <t>TAJE107M025RNJ</t>
+  </si>
+  <si>
+    <t>Kyocera AVX</t>
+  </si>
+  <si>
     <t>(TVS/ESD)</t>
   </si>
   <si>
@@ -552,6 +587,33 @@
     <t>Littelfuse</t>
   </si>
   <si>
+    <t>D15, D16</t>
+  </si>
+  <si>
+    <t>TVS DIODE 3.6VWM 19VC 2X1SON</t>
+  </si>
+  <si>
+    <t>2-X1SON (1x.60)</t>
+  </si>
+  <si>
+    <t>TPD1E0B04DPYR</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>D17, D18, D19</t>
+  </si>
+  <si>
+    <t>TVS DIODE 3.3VWM 6.8VC SOD123F</t>
+  </si>
+  <si>
+    <t>SOD-123FL</t>
+  </si>
+  <si>
+    <t>SMF3.3</t>
+  </si>
+  <si>
     <t>Ferrite Bead</t>
   </si>
   <si>
@@ -567,7 +629,7 @@
     <t>BLM18PG221SN1D</t>
   </si>
   <si>
-    <t>SD Card Connector</t>
+    <t>Connector</t>
   </si>
   <si>
     <t>J1</t>
@@ -615,6 +677,12 @@
     <t>J4</t>
   </si>
   <si>
+    <t>CONN FFC BOTTOM 40POS 0.5MM R/A</t>
+  </si>
+  <si>
+    <t>FH41-40S-0.5SH(05)</t>
+  </si>
+  <si>
     <t>Hirose</t>
   </si>
   <si>
@@ -666,36 +734,36 @@
     <t>6.8uH</t>
   </si>
   <si>
+    <t>L2, L3, L4</t>
+  </si>
+  <si>
+    <t>2.9A 4.7uH ±20% 2.9A SMD,4x4mm Power Inductors ROHS</t>
+  </si>
+  <si>
+    <t>SMNR4030-4R7MT</t>
+  </si>
+  <si>
+    <t>SXN(Shun Xiang Nuo Elec)</t>
+  </si>
+  <si>
+    <t>4.7uH</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>FIXED IND 4.7UH 1.9A 84 MOHM SMD</t>
+  </si>
+  <si>
+    <t>SRN4018-4R7M</t>
+  </si>
+  <si>
+    <t>Bourns</t>
+  </si>
+  <si>
     <t>Inductor</t>
   </si>
   <si>
-    <t>L2, L3, L4</t>
-  </si>
-  <si>
-    <t>2.9A 4.7uH ±20% 2.9A SMD,4x4mm Power Inductors ROHS</t>
-  </si>
-  <si>
-    <t>SMNR4030-4R7MT</t>
-  </si>
-  <si>
-    <t>SXN(Shun Xiang Nuo Elec)</t>
-  </si>
-  <si>
-    <t>4.7uH</t>
-  </si>
-  <si>
-    <t>L5</t>
-  </si>
-  <si>
-    <t>FIXED IND 4.7UH 1.9A 84 MOHM SMD</t>
-  </si>
-  <si>
-    <t>SRN4018-4R7M</t>
-  </si>
-  <si>
-    <t>Bourns</t>
-  </si>
-  <si>
     <t>L6</t>
   </si>
   <si>
@@ -720,6 +788,21 @@
     <t>LQG18HH47NJ00D</t>
   </si>
   <si>
+    <t>L8</t>
+  </si>
+  <si>
+    <t>2.3A 3.9uH ±20% 3.3A SMD,4x4mm Power Inductors ROHS</t>
+  </si>
+  <si>
+    <t>FNR4030S3R9MT</t>
+  </si>
+  <si>
+    <t>cjiang</t>
+  </si>
+  <si>
+    <t>3.9uH</t>
+  </si>
+  <si>
     <t>LED</t>
   </si>
   <si>
@@ -834,6 +917,21 @@
     <t>Rohm</t>
   </si>
   <si>
+    <t>(BJT)</t>
+  </si>
+  <si>
+    <t>Q8</t>
+  </si>
+  <si>
+    <t>40V 200mW 100 200mA NPN SOT-23 Bipolar (BJT) ROHS</t>
+  </si>
+  <si>
+    <t>MMBT3904</t>
+  </si>
+  <si>
+    <t>ElecSuper</t>
+  </si>
+  <si>
     <t>Resistor</t>
   </si>
   <si>
@@ -864,6 +962,9 @@
     <t>3.3R</t>
   </si>
   <si>
+    <t>Resistors</t>
+  </si>
+  <si>
     <t>R9</t>
   </si>
   <si>
@@ -915,9 +1016,6 @@
     <t>120R</t>
   </si>
   <si>
-    <t>Resistors</t>
-  </si>
-  <si>
     <t>R13</t>
   </si>
   <si>
@@ -951,18 +1049,6 @@
     <t>RT0402BRD0710KL</t>
   </si>
   <si>
-    <t>R16</t>
-  </si>
-  <si>
-    <t>RES SMD 11K OHM 0.1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RT0402BRE0711KL</t>
-  </si>
-  <si>
-    <t>11K</t>
-  </si>
-  <si>
     <t>R17</t>
   </si>
   <si>
@@ -1047,7 +1133,7 @@
     <t>200K</t>
   </si>
   <si>
-    <t>R39, R42, R45, R52, R55, R57, R58, R82, R84, R104</t>
+    <t>R39, R42, R52, R55, R57, R58, R82, R84, R104, R118</t>
   </si>
   <si>
     <t>RES SMD 0R, 1%, 0.1W, 0603</t>
@@ -1059,13 +1145,13 @@
     <t>R40</t>
   </si>
   <si>
-    <t>RES SMD 511K OHM 0.1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RT0603BRD07511KL</t>
-  </si>
-  <si>
-    <t>511K</t>
+    <t>RES SMD 536K OHM 0.1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RT0603BRD07536KL</t>
+  </si>
+  <si>
+    <t>536K</t>
   </si>
   <si>
     <t>R41</t>
@@ -1083,13 +1169,13 @@
     <t>R43</t>
   </si>
   <si>
-    <t>RES SMD 88.7KOHM 0.1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RT0603BRD0788K7L</t>
-  </si>
-  <si>
-    <t>88.7K</t>
+    <t>RES SMD 107K OHM 0.1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RT0603BRD07107KL</t>
+  </si>
+  <si>
+    <t>107K</t>
   </si>
   <si>
     <t>R44</t>
@@ -1104,6 +1190,9 @@
     <t>10.2K</t>
   </si>
   <si>
+    <t>R45, R83, R110, R119</t>
+  </si>
+  <si>
     <t>R46</t>
   </si>
   <si>
@@ -1125,7 +1214,7 @@
     <t>RC0603FR-0710KL</t>
   </si>
   <si>
-    <t>R49, R59, R62, R73</t>
+    <t>R49, R59, R62, R73, R123, R124, R125, R126, R127</t>
   </si>
   <si>
     <t>RES 20K OHM 1% 1/10W 0603</t>
@@ -1254,7 +1343,7 @@
     <t>51K</t>
   </si>
   <si>
-    <t>R77, R97, R98, R114, R120, R121</t>
+    <t>R77, R81, R97, R98, R114, R120, R121, R128</t>
   </si>
   <si>
     <t>RES SMD 680 OHM 1% 1/10W 0603</t>
@@ -1302,7 +1391,10 @@
     <t>100R</t>
   </si>
   <si>
-    <t>R81, R86</t>
+    <t>R85</t>
+  </si>
+  <si>
+    <t>R86</t>
   </si>
   <si>
     <t>RES SMD 10 OHM 1% 1/10W 0603</t>
@@ -1314,12 +1406,6 @@
     <t>10R</t>
   </si>
   <si>
-    <t>R83, R110</t>
-  </si>
-  <si>
-    <t>R85</t>
-  </si>
-  <si>
     <t>R87</t>
   </si>
   <si>
@@ -1407,16 +1493,13 @@
     <t>R113</t>
   </si>
   <si>
-    <t>R118, R123, R124, R125, R126, R127</t>
-  </si>
-  <si>
-    <t>RES SMD 100 OHM 1% 1/8W 0805</t>
-  </si>
-  <si>
-    <t>RES-0805</t>
-  </si>
-  <si>
-    <t>AC0805FR-07100RL</t>
+    <t>R116</t>
+  </si>
+  <si>
+    <t>RES 680 OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RC0402FR-07680RL</t>
   </si>
   <si>
     <t>R122</t>
@@ -1545,9 +1628,6 @@
     <t>TPS62933DRLR</t>
   </si>
   <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
     <t>U6</t>
   </si>
   <si>
@@ -1671,6 +1751,18 @@
     <t>TXS0108EPWR</t>
   </si>
   <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>IC XPND 400KHZ I2C SMBUS 16TSSOP</t>
+  </si>
+  <si>
+    <t>TSSOP_16</t>
+  </si>
+  <si>
+    <t>PCA9557PW,118</t>
+  </si>
+  <si>
     <t>U17</t>
   </si>
   <si>
@@ -1689,13 +1781,40 @@
     <t>U18</t>
   </si>
   <si>
-    <t>TVS DIODE 3.3VWM 15VC 8-SOIC</t>
-  </si>
-  <si>
-    <t>SRDA3.3-4DR2G</t>
-  </si>
-  <si>
-    <t>onsemi</t>
+    <t>DG ISO 5KV 4CH CAN/RS232 16-SOIC</t>
+  </si>
+  <si>
+    <t>SOIC-16-300mil</t>
+  </si>
+  <si>
+    <t>ISO6742FDWR</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>U19</t>
+  </si>
+  <si>
+    <t>10W wide-voltage input, isolated and regulated single-channel/positive-negative dual-channel output DC/DC power supply module</t>
+  </si>
+  <si>
+    <t>VRB1212S-10WR3</t>
+  </si>
+  <si>
+    <t>YLPTEC</t>
+  </si>
+  <si>
+    <t>U20</t>
+  </si>
+  <si>
+    <t>IC REG BUCK 3.3V 2A TSOT26</t>
+  </si>
+  <si>
+    <t>TSOT-23-6</t>
+  </si>
+  <si>
+    <t>AP63203WU-7</t>
   </si>
   <si>
     <t>Crytal</t>
@@ -1800,6 +1919,12 @@
     <t>MyAntenna</t>
   </si>
   <si>
+    <t>FPC延长板 焊好2个0.5mm间距40p翻盖FPC连接器 组装 QWY(CN) RoHs</t>
+  </si>
+  <si>
+    <t>Moko Code: 12300000303070</t>
+  </si>
+  <si>
     <t>5 inch TFT LCD Display 800*480 RGB Interface LCD Touch Screen Panel</t>
   </si>
   <si>
@@ -1812,41 +1937,23 @@
     <t>Already Provided</t>
   </si>
   <si>
-    <t>FPC延长板 焊好2个0.5mm间距40p翻盖FPC连接器 组装 QWY(CN) RoHs</t>
-  </si>
-  <si>
-    <t>Moko Code: 12300000303070</t>
-  </si>
-  <si>
     <t>LED SPACER MOUNTS for T-1 and T-13/4</t>
   </si>
   <si>
     <t>Keystone</t>
-  </si>
-  <si>
-    <t>D15, D16, D17</t>
-  </si>
-  <si>
-    <t>TVS DIODE 3.3VWM 6.8VC SOD123F</t>
-  </si>
-  <si>
-    <t>SOD-123FL</t>
-  </si>
-  <si>
-    <t>SMF3.3</t>
-  </si>
-  <si>
-    <t>CONN FFC FPC 40POS 0.5MM R/A Top Bottom</t>
-  </si>
-  <si>
-    <t>FH34SRJ-40S-0.5SH(50)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1907,27 +2014,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
@@ -1935,8 +2021,152 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1955,8 +2185,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -2047,11 +2463,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2094,51 +2752,77 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF03A4CB"/>
-      <color rgb="FF2CD0B2"/>
+      <color rgb="0003A4CB"/>
+      <color rgb="002CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2396,29 +3080,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K146"/>
+  <dimension ref="A1:K154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.57142857142857" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7142857142857" style="1" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" customWidth="1"/>
-    <col min="7" max="7" width="27.28515625" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" customWidth="1"/>
-    <col min="11" max="11" width="27.140625" customWidth="1"/>
+    <col min="6" max="6" width="23.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="27.2857142857143" customWidth="1"/>
+    <col min="8" max="8" width="20.8571428571429" customWidth="1"/>
+    <col min="9" max="9" width="8.14285714285714" customWidth="1"/>
+    <col min="10" max="10" width="9.28571428571429" customWidth="1"/>
+    <col min="11" max="11" width="23.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" ht="15.75" spans="1:11">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2427,11 +3110,11 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+    </row>
+    <row r="2" ht="15.75" spans="1:11">
       <c r="A2" s="2"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -2464,10 +3147,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" ht="15.75" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="7">
-        <f t="shared" ref="B3:B34" si="0">ROW(B3)-ROW($B$2)</f>
+        <f>ROW(B3)-ROW($B$2)</f>
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -2496,10 +3179,10 @@
       </c>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" ht="15.75" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B4)-ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -2528,10 +3211,10 @@
       </c>
       <c r="K4" s="12"/>
     </row>
-    <row r="5" spans="1:11" ht="24">
+    <row r="5" ht="24.75" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B5)-ROW($B$2)</f>
         <v>3</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -2556,14 +3239,14 @@
         <v>26</v>
       </c>
       <c r="J5" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="48">
+    <row r="6" ht="48.75" spans="1:11">
       <c r="A6" s="2"/>
       <c r="B6" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B6)-ROW($B$2)</f>
         <v>4</v>
       </c>
       <c r="C6" s="11" t="s">
@@ -2588,14 +3271,14 @@
         <v>30</v>
       </c>
       <c r="J6" s="12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B7)-ROW($B$2)</f>
         <v>5</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -2624,10 +3307,10 @@
       </c>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="24">
+    <row r="8" ht="24.75" spans="1:11">
       <c r="A8" s="2"/>
       <c r="B8" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B8)-ROW($B$2)</f>
         <v>6</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -2652,14 +3335,14 @@
         <v>30</v>
       </c>
       <c r="J8" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B9)-ROW($B$2)</f>
         <v>7</v>
       </c>
       <c r="C9" s="8" t="s">
@@ -2691,7 +3374,7 @@
     <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B10)-ROW($B$2)</f>
         <v>8</v>
       </c>
       <c r="C10" s="8" t="s">
@@ -2723,7 +3406,7 @@
     <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B11)-ROW($B$2)</f>
         <v>9</v>
       </c>
       <c r="C11" s="8" t="s">
@@ -2752,10 +3435,10 @@
       </c>
       <c r="K11" s="9"/>
     </row>
-    <row r="12" spans="1:11" ht="24">
+    <row r="12" ht="24.75" spans="1:11">
       <c r="A12" s="2"/>
       <c r="B12" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B12)-ROW($B$2)</f>
         <v>10</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -2784,10 +3467,10 @@
       </c>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" ht="15.75" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B13)-ROW($B$2)</f>
         <v>11</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -2812,14 +3495,14 @@
         <v>26</v>
       </c>
       <c r="J13" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" ht="15.75" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B14)-ROW($B$2)</f>
         <v>12</v>
       </c>
       <c r="C14" s="11" t="s">
@@ -2848,10 +3531,10 @@
       </c>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" ht="15.75" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B15)-ROW($B$2)</f>
         <v>13</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -2880,10 +3563,10 @@
       </c>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" ht="15.75" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B16)-ROW($B$2)</f>
         <v>14</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -2912,10 +3595,10 @@
       </c>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" ht="15.75" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B17)-ROW($B$2)</f>
         <v>15</v>
       </c>
       <c r="C17" s="8" t="s">
@@ -2944,10 +3627,10 @@
       </c>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" ht="15.75" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B18)-ROW($B$2)</f>
         <v>16</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -2972,14 +3655,14 @@
         <v>66</v>
       </c>
       <c r="J18" s="12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" ht="15.75" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B19)-ROW($B$2)</f>
         <v>17</v>
       </c>
       <c r="C19" s="8" t="s">
@@ -3008,10 +3691,10 @@
       </c>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" ht="15.75" spans="1:11">
       <c r="A20" s="2"/>
       <c r="B20" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B20)-ROW($B$2)</f>
         <v>18</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -3043,7 +3726,7 @@
     <row r="21" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B21)-ROW($B$2)</f>
         <v>19</v>
       </c>
       <c r="C21" s="8" t="s">
@@ -3075,7 +3758,7 @@
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B22)-ROW($B$2)</f>
         <v>20</v>
       </c>
       <c r="C22" s="11" t="s">
@@ -3107,7 +3790,7 @@
     <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B23)-ROW($B$2)</f>
         <v>21</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -3139,7 +3822,7 @@
     <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B24)-ROW($B$2)</f>
         <v>22</v>
       </c>
       <c r="C24" s="11" t="s">
@@ -3171,7 +3854,7 @@
     <row r="25" spans="1:11">
       <c r="A25" s="2"/>
       <c r="B25" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B25)-ROW($B$2)</f>
         <v>23</v>
       </c>
       <c r="C25" s="11" t="s">
@@ -3203,7 +3886,7 @@
     <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B26)-ROW($B$2)</f>
         <v>24</v>
       </c>
       <c r="C26" s="11" t="s">
@@ -3235,7 +3918,7 @@
     <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B27)-ROW($B$2)</f>
         <v>25</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -3267,7 +3950,7 @@
     <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B28)-ROW($B$2)</f>
         <v>26</v>
       </c>
       <c r="C28" s="11" t="s">
@@ -3299,7 +3982,7 @@
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B29)-ROW($B$2)</f>
         <v>27</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -3331,7 +4014,7 @@
     <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B30)-ROW($B$2)</f>
         <v>28</v>
       </c>
       <c r="C30" s="8" t="s">
@@ -3360,10 +4043,10 @@
       </c>
       <c r="K30" s="12"/>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" ht="15.75" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B31)-ROW($B$2)</f>
         <v>29</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -3392,13 +4075,13 @@
       </c>
       <c r="K31" s="9"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" ht="15.75" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B32)-ROW($B$2)</f>
         <v>30</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="14" t="s">
@@ -3422,21 +4105,19 @@
       <c r="J32" s="14">
         <v>7</v>
       </c>
-      <c r="K32" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" ht="15.75" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B33)-ROW($B$2)</f>
         <v>31</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>39</v>
@@ -3456,68 +4137,66 @@
       <c r="J33" s="14">
         <v>1</v>
       </c>
-      <c r="K33" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="36">
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" ht="15.75" spans="1:11">
       <c r="A34" s="2"/>
       <c r="B34" s="7">
-        <f t="shared" si="0"/>
+        <f>ROW(B34)-ROW($B$2)</f>
         <v>32</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="F34" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="G34" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="H34" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="I34" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="H34" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>145</v>
-      </c>
       <c r="J34" s="12">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K34" s="12"/>
     </row>
-    <row r="35" spans="1:11" ht="24">
+    <row r="35" spans="1:11">
       <c r="A35" s="2"/>
       <c r="B35" s="7">
-        <f t="shared" ref="B35:B67" si="1">ROW(B35)-ROW($B$2)</f>
+        <f>ROW(B35)-ROW($B$2)</f>
         <v>33</v>
       </c>
       <c r="C35" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>150</v>
-      </c>
       <c r="H35" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>145</v>
+        <v>74</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="J35" s="9">
         <v>1</v>
@@ -3527,544 +4206,541 @@
     <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B36)-ROW($B$2)</f>
         <v>34</v>
       </c>
-      <c r="C36" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J36" s="14">
-        <v>1</v>
-      </c>
-      <c r="K36" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="24">
+      <c r="C36" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="J36" s="12">
+        <v>1</v>
+      </c>
+      <c r="K36" s="12"/>
+    </row>
+    <row r="37" ht="24.75" spans="1:11">
       <c r="A37" s="2"/>
       <c r="B37" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B37)-ROW($B$2)</f>
         <v>35</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D37" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="I37" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>145</v>
-      </c>
       <c r="J37" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K37" s="9"/>
     </row>
-    <row r="38" spans="1:11" ht="24">
+    <row r="38" ht="24.75" spans="1:11">
       <c r="A38" s="2"/>
       <c r="B38" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B38)-ROW($B$2)</f>
         <v>36</v>
       </c>
       <c r="C38" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="F38" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="G38" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="H38" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="F38" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="I38" s="10" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="J38" s="12">
         <v>1</v>
       </c>
       <c r="K38" s="12"/>
     </row>
-    <row r="39" spans="1:11" ht="15.75" thickBot="1">
+    <row r="39" ht="15.75" spans="1:11">
       <c r="A39" s="2"/>
       <c r="B39" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B39)-ROW($B$2)</f>
         <v>37</v>
       </c>
       <c r="C39" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="G39" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="H39" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E39" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J39" s="9">
-        <v>1</v>
-      </c>
-      <c r="K39" s="9"/>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" thickBot="1">
+      <c r="I39" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J39" s="14">
+        <v>1</v>
+      </c>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" ht="24.75" spans="1:11">
       <c r="A40" s="2"/>
       <c r="B40" s="7">
+        <f>ROW(B40)-ROW($B$2)</f>
         <v>38</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>598</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>599</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>600</v>
-      </c>
-      <c r="H40" s="9" t="s">
+      <c r="C40" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F40" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="I40" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J40" s="9">
-        <v>3</v>
-      </c>
-      <c r="K40" s="9"/>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" thickBot="1">
+      <c r="G40" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J40" s="12">
+        <v>1</v>
+      </c>
+      <c r="K40" s="12"/>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="2"/>
       <c r="B41" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B41)-ROW($B$2)</f>
         <v>39</v>
       </c>
-      <c r="C41" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E41" s="13" t="s">
+      <c r="C41" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="D41" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="E41" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="H41" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J41" s="12">
-        <v>2</v>
-      </c>
-      <c r="K41" s="12"/>
-    </row>
-    <row r="42" spans="1:11" ht="36">
+      <c r="F41" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J41" s="9">
+        <v>1</v>
+      </c>
+      <c r="K41" s="9"/>
+    </row>
+    <row r="42" ht="15.75" spans="1:11">
       <c r="A42" s="2"/>
       <c r="B42" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B42)-ROW($B$2)</f>
         <v>40</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G42" s="10">
-        <v>5027740891</v>
-      </c>
-      <c r="H42" s="9" t="s">
+      <c r="C42" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="I42" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J42" s="9">
-        <v>1</v>
-      </c>
-      <c r="K42" s="9"/>
-    </row>
-    <row r="43" spans="1:11" ht="48">
+      <c r="D42" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J42" s="12">
+        <v>1</v>
+      </c>
+      <c r="K42" s="12"/>
+    </row>
+    <row r="43" ht="15.75" spans="1:11">
       <c r="A43" s="2"/>
       <c r="B43" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B43)-ROW($B$2)</f>
         <v>41</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>184</v>
+        <v>181</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>187</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G43" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J43" s="12">
-        <v>1</v>
-      </c>
-      <c r="K43" s="12"/>
-    </row>
-    <row r="44" spans="1:11" ht="24">
+        <v>188</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J43" s="9">
+        <v>2</v>
+      </c>
+      <c r="K43" s="9"/>
+    </row>
+    <row r="44" ht="15.75" spans="1:11">
       <c r="A44" s="2"/>
       <c r="B44" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B44)-ROW($B$2)</f>
         <v>42</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="H44" s="9" t="s">
+      <c r="C44" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D44" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="I44" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J44" s="9">
-        <v>1</v>
-      </c>
-      <c r="K44" s="9"/>
-    </row>
-    <row r="45" spans="1:11" ht="24">
+      <c r="E44" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J44" s="12">
+        <v>3</v>
+      </c>
+      <c r="K44" s="12"/>
+    </row>
+    <row r="45" ht="15.75" spans="1:11">
       <c r="A45" s="2"/>
       <c r="B45" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B45)-ROW($B$2)</f>
         <v>43</v>
       </c>
-      <c r="C45" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>601</v>
+      <c r="C45" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>197</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>602</v>
-      </c>
-      <c r="H45" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J45" s="12">
-        <v>1</v>
-      </c>
-      <c r="K45" s="12"/>
-    </row>
-    <row r="46" spans="1:11" ht="25.5">
+        <v>198</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J45" s="9">
+        <v>2</v>
+      </c>
+      <c r="K45" s="9"/>
+    </row>
+    <row r="46" ht="36.75" spans="1:11">
       <c r="A46" s="2"/>
       <c r="B46" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B46)-ROW($B$2)</f>
         <v>44</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>197</v>
+      <c r="C46" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J46" s="9">
-        <v>2</v>
-      </c>
-      <c r="K46" s="9"/>
-    </row>
-    <row r="47" spans="1:11" ht="25.5">
+      <c r="G46" s="13">
+        <v>5027740891</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J46" s="12">
+        <v>1</v>
+      </c>
+      <c r="K46" s="12"/>
+    </row>
+    <row r="47" ht="48.75" spans="1:11">
       <c r="A47" s="2"/>
       <c r="B47" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B47)-ROW($B$2)</f>
         <v>45</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="F47" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F47" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J47" s="14">
-        <v>1</v>
-      </c>
-      <c r="K47" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="25.5">
+      <c r="G47" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J47" s="9">
+        <v>1</v>
+      </c>
+      <c r="K47" s="9"/>
+    </row>
+    <row r="48" ht="24.75" spans="1:11">
       <c r="A48" s="2"/>
       <c r="B48" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B48)-ROW($B$2)</f>
         <v>46</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>202</v>
+      <c r="C48" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>211</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G48" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J48" s="9">
-        <v>1</v>
-      </c>
-      <c r="K48" s="9"/>
+      <c r="G48" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J48" s="12">
+        <v>1</v>
+      </c>
+      <c r="K48" s="12"/>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2"/>
       <c r="B49" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B49)-ROW($B$2)</f>
         <v>47</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>210</v>
+        <v>218</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="J49" s="9">
         <v>1</v>
       </c>
       <c r="K49" s="9"/>
     </row>
-    <row r="50" spans="1:11" ht="24">
+    <row r="50" ht="26.25" spans="1:11">
       <c r="A50" s="2"/>
       <c r="B50" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B50)-ROW($B$2)</f>
         <v>48</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="J50" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50" s="12"/>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" ht="26.25" spans="1:11">
       <c r="A51" s="2"/>
       <c r="B51" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B51)-ROW($B$2)</f>
         <v>49</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E51" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="H51" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="J51" s="9">
-        <v>1</v>
-      </c>
-      <c r="K51" s="9"/>
-    </row>
-    <row r="52" spans="1:11" ht="24">
+      <c r="I51" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J51" s="14">
+        <v>1</v>
+      </c>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" ht="26.25" spans="1:11">
       <c r="A52" s="2"/>
       <c r="B52" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B52)-ROW($B$2)</f>
         <v>50</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>225</v>
+        <v>158</v>
       </c>
       <c r="J52" s="12">
         <v>1</v>
@@ -4074,799 +4750,797 @@
     <row r="53" spans="1:11">
       <c r="A53" s="2"/>
       <c r="B53" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B53)-ROW($B$2)</f>
         <v>51</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="G53" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I53" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J53" s="14">
-        <v>1</v>
-      </c>
-      <c r="K53" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="24">
+        <v>229</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="J53" s="12">
+        <v>1</v>
+      </c>
+      <c r="K53" s="12"/>
+    </row>
+    <row r="54" ht="24.75" spans="1:11">
       <c r="A54" s="2"/>
       <c r="B54" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B54)-ROW($B$2)</f>
         <v>52</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="D54" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H54" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J54" s="12">
-        <v>1</v>
-      </c>
-      <c r="K54" s="12"/>
-    </row>
-    <row r="55" spans="1:11" ht="24">
+      <c r="D54" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="J54" s="9">
+        <v>3</v>
+      </c>
+      <c r="K54" s="9"/>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="2"/>
       <c r="B55" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B55)-ROW($B$2)</f>
         <v>53</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="D55" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>236</v>
+      <c r="D55" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>241</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H55" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="H55" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="I55" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="I55" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J55" s="9">
-        <v>5</v>
-      </c>
-      <c r="K55" s="9"/>
-    </row>
-    <row r="56" spans="1:11" ht="24">
+      <c r="J55" s="12">
+        <v>1</v>
+      </c>
+      <c r="K55" s="12"/>
+    </row>
+    <row r="56" ht="24.75" spans="1:11">
       <c r="A56" s="2"/>
       <c r="B56" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B56)-ROW($B$2)</f>
         <v>54</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="G56" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="H56" s="12" t="s">
+      <c r="C56" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="I56" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J56" s="12">
-        <v>2</v>
-      </c>
-      <c r="K56" s="12"/>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="D56" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="J56" s="9">
+        <v>1</v>
+      </c>
+      <c r="K56" s="9"/>
+    </row>
+    <row r="57" ht="15.75" spans="1:11">
       <c r="A57" s="2"/>
       <c r="B57" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B57)-ROW($B$2)</f>
         <v>55</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J57" s="9">
-        <v>1</v>
-      </c>
-      <c r="K57" s="9"/>
-    </row>
-    <row r="58" spans="1:11" ht="24">
+      <c r="D57" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="G57" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J57" s="14">
+        <v>1</v>
+      </c>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" ht="24.75" spans="1:11">
       <c r="A58" s="2"/>
       <c r="B58" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B58)-ROW($B$2)</f>
         <v>56</v>
       </c>
-      <c r="C58" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J58" s="12">
-        <v>1</v>
-      </c>
-      <c r="K58" s="12"/>
-    </row>
-    <row r="59" spans="1:11" ht="36">
+      <c r="C58" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="J58" s="9">
+        <v>1</v>
+      </c>
+      <c r="K58" s="9"/>
+    </row>
+    <row r="59" ht="24.75" spans="1:11">
       <c r="A59" s="2"/>
       <c r="B59" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B59)-ROW($B$2)</f>
         <v>57</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>256</v>
+      <c r="C59" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="H59" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J59" s="9">
-        <v>1</v>
-      </c>
-      <c r="K59" s="9"/>
-    </row>
-    <row r="60" spans="1:11">
+        <v>158</v>
+      </c>
+      <c r="J59" s="12">
+        <v>1</v>
+      </c>
+      <c r="K59" s="12"/>
+    </row>
+    <row r="60" ht="24.75" spans="1:11">
       <c r="A60" s="2"/>
       <c r="B60" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B60)-ROW($B$2)</f>
         <v>58</v>
       </c>
-      <c r="C60" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="D60" s="12" t="s">
+      <c r="C60" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="E60" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="G60" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="H60" s="12" t="s">
-        <v>156</v>
+      <c r="D60" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>268</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J60" s="12">
-        <v>1</v>
-      </c>
-      <c r="K60" s="12"/>
-    </row>
-    <row r="61" spans="1:11">
+        <v>158</v>
+      </c>
+      <c r="J60" s="9">
+        <v>5</v>
+      </c>
+      <c r="K60" s="9"/>
+    </row>
+    <row r="61" ht="24.75" spans="1:11">
       <c r="A61" s="2"/>
       <c r="B61" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B61)-ROW($B$2)</f>
         <v>59</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>266</v>
+      <c r="C61" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="G61" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>273</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J61" s="9">
-        <v>6</v>
-      </c>
-      <c r="K61" s="9"/>
+        <v>158</v>
+      </c>
+      <c r="J61" s="12">
+        <v>2</v>
+      </c>
+      <c r="K61" s="12"/>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2"/>
       <c r="B62" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B62)-ROW($B$2)</f>
         <v>60</v>
       </c>
-      <c r="C62" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="G62" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>74</v>
+      <c r="C62" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>273</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="J62" s="12">
-        <v>7</v>
-      </c>
-      <c r="K62" s="12"/>
-    </row>
-    <row r="63" spans="1:11">
+        <v>158</v>
+      </c>
+      <c r="J62" s="9">
+        <v>1</v>
+      </c>
+      <c r="K62" s="9"/>
+    </row>
+    <row r="63" ht="24.75" spans="1:11">
       <c r="A63" s="2"/>
       <c r="B63" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B63)-ROW($B$2)</f>
         <v>61</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I63" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="J63" s="9">
-        <v>1</v>
-      </c>
-      <c r="K63" s="9"/>
-    </row>
-    <row r="64" spans="1:11">
+        <v>258</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="G63" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="H63" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="I63" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J63" s="12">
+        <v>1</v>
+      </c>
+      <c r="K63" s="12"/>
+    </row>
+    <row r="64" ht="36.75" spans="1:11">
       <c r="A64" s="2"/>
       <c r="B64" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B64)-ROW($B$2)</f>
         <v>62</v>
       </c>
-      <c r="C64" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="G64" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="H64" s="12" t="s">
-        <v>74</v>
+      <c r="C64" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="J64" s="12">
-        <v>1</v>
-      </c>
-      <c r="K64" s="12"/>
-    </row>
-    <row r="65" spans="1:11">
+        <v>158</v>
+      </c>
+      <c r="J64" s="9">
+        <v>1</v>
+      </c>
+      <c r="K64" s="9"/>
+    </row>
+    <row r="65" ht="15.75" spans="1:11">
       <c r="A65" s="2"/>
       <c r="B65" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B65)-ROW($B$2)</f>
         <v>63</v>
       </c>
-      <c r="C65" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I65" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="J65" s="9">
-        <v>1</v>
-      </c>
-      <c r="K65" s="9"/>
+      <c r="C65" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="G65" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="H65" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="I65" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J65" s="12">
+        <v>1</v>
+      </c>
+      <c r="K65" s="12"/>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="2"/>
       <c r="B66" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B66)-ROW($B$2)</f>
         <v>64</v>
       </c>
-      <c r="C66" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="E66" s="13" t="s">
+      <c r="C66" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="F66" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="G66" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="H66" s="12" t="s">
-        <v>74</v>
+      <c r="D66" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>295</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="J66" s="12">
-        <v>1</v>
-      </c>
-      <c r="K66" s="12"/>
-    </row>
-    <row r="67" spans="1:11">
+        <v>158</v>
+      </c>
+      <c r="J66" s="9">
+        <v>6</v>
+      </c>
+      <c r="K66" s="9"/>
+    </row>
+    <row r="67" ht="24.75" spans="1:11">
       <c r="A67" s="2"/>
       <c r="B67" s="7">
-        <f t="shared" si="1"/>
+        <f>ROW(B67)-ROW($B$2)</f>
         <v>65</v>
       </c>
-      <c r="C67" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="D67" s="9" t="s">
+      <c r="C67" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="F67" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="E67" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I67" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="J67" s="9">
-        <v>1</v>
-      </c>
-      <c r="K67" s="9"/>
+      <c r="G67" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="H67" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="I67" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J67" s="12">
+        <v>1</v>
+      </c>
+      <c r="K67" s="12"/>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2"/>
       <c r="B68" s="7">
-        <f t="shared" ref="B68:B99" si="2">ROW(B68)-ROW($B$2)</f>
+        <f>ROW(B68)-ROW($B$2)</f>
         <v>66</v>
       </c>
-      <c r="C68" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="G68" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="H68" s="12" t="s">
+      <c r="C68" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="H68" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I68" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="J68" s="12">
-        <v>1</v>
-      </c>
-      <c r="K68" s="12"/>
+      <c r="I68" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="J68" s="9">
+        <v>7</v>
+      </c>
+      <c r="K68" s="9"/>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="2"/>
       <c r="B69" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B69)-ROW($B$2)</f>
         <v>67</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G69" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="H69" s="9" t="s">
+      <c r="D69" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="H69" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I69" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="J69" s="9">
-        <v>1</v>
-      </c>
-      <c r="K69" s="9"/>
+      <c r="I69" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="J69" s="12">
+        <v>1</v>
+      </c>
+      <c r="K69" s="12"/>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="2"/>
       <c r="B70" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B70)-ROW($B$2)</f>
         <v>68</v>
       </c>
-      <c r="C70" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="E70" s="13" t="s">
+      <c r="C70" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="F70" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="F70" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="G70" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="H70" s="12" t="s">
+      <c r="G70" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="H70" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I70" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="J70" s="12">
-        <v>1</v>
-      </c>
-      <c r="K70" s="12"/>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="I70" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="J70" s="9">
+        <v>1</v>
+      </c>
+      <c r="K70" s="9"/>
+    </row>
+    <row r="71" ht="15.75" spans="1:11">
       <c r="A71" s="2"/>
       <c r="B71" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B71)-ROW($B$2)</f>
         <v>69</v>
       </c>
-      <c r="C71" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="H71" s="9" t="s">
+      <c r="C71" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="H71" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I71" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="J71" s="9">
-        <v>1</v>
-      </c>
-      <c r="K71" s="9"/>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="I71" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="J71" s="12">
+        <v>1</v>
+      </c>
+      <c r="K71" s="12"/>
+    </row>
+    <row r="72" ht="15.75" spans="1:11">
       <c r="A72" s="2"/>
       <c r="B72" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B72)-ROW($B$2)</f>
         <v>70</v>
       </c>
-      <c r="C72" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="G72" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="H72" s="12" t="s">
+      <c r="C72" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H72" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I72" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="J72" s="12">
-        <v>1</v>
-      </c>
-      <c r="K72" s="12"/>
-    </row>
-    <row r="73" spans="1:11">
+      <c r="I72" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="J72" s="9">
+        <v>1</v>
+      </c>
+      <c r="K72" s="9"/>
+    </row>
+    <row r="73" ht="15.75" spans="1:11">
       <c r="A73" s="2"/>
       <c r="B73" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B73)-ROW($B$2)</f>
         <v>71</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="H73" s="9" t="s">
+      <c r="C73" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="H73" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I73" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="J73" s="9">
-        <v>6</v>
-      </c>
-      <c r="K73" s="9"/>
-    </row>
-    <row r="74" spans="1:11">
+      <c r="I73" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="J73" s="12">
+        <v>1</v>
+      </c>
+      <c r="K73" s="12"/>
+    </row>
+    <row r="74" ht="15.75" spans="1:11">
       <c r="A74" s="2"/>
       <c r="B74" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B74)-ROW($B$2)</f>
         <v>72</v>
       </c>
-      <c r="C74" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="G74" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="H74" s="12" t="s">
+      <c r="C74" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="H74" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I74" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="J74" s="12">
-        <v>1</v>
-      </c>
-      <c r="K74" s="12"/>
-    </row>
-    <row r="75" spans="1:11" ht="24">
+      <c r="I74" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="J74" s="9">
+        <v>1</v>
+      </c>
+      <c r="K74" s="9"/>
+    </row>
+    <row r="75" ht="15.75" spans="1:11">
       <c r="A75" s="2"/>
       <c r="B75" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B75)-ROW($B$2)</f>
         <v>73</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="H75" s="9" t="s">
+      <c r="C75" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="H75" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I75" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="J75" s="9">
-        <v>18</v>
-      </c>
-      <c r="K75" s="9"/>
+      <c r="I75" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="J75" s="12">
+        <v>1</v>
+      </c>
+      <c r="K75" s="12"/>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="2"/>
       <c r="B76" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B76)-ROW($B$2)</f>
         <v>74</v>
       </c>
-      <c r="C76" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="G76" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="H76" s="12" t="s">
+      <c r="C76" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="H76" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I76" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="J76" s="12">
-        <v>2</v>
-      </c>
-      <c r="K76" s="12"/>
+      <c r="I76" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="J76" s="9">
+        <v>1</v>
+      </c>
+      <c r="K76" s="9"/>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="2"/>
       <c r="B77" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B77)-ROW($B$2)</f>
         <v>75</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="H77" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="J77" s="9">
         <v>1</v>
@@ -4876,865 +5550,861 @@
     <row r="78" spans="1:11">
       <c r="A78" s="2"/>
       <c r="B78" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B78)-ROW($B$2)</f>
         <v>76</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="G78" s="13" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="H78" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="J78" s="12">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K78" s="12"/>
     </row>
-    <row r="79" spans="1:11" ht="24">
+    <row r="79" ht="15.75" spans="1:11">
       <c r="A79" s="2"/>
       <c r="B79" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B79)-ROW($B$2)</f>
         <v>77</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="H79" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="J79" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K79" s="9"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" ht="24.75" spans="1:11">
       <c r="A80" s="2"/>
       <c r="B80" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B80)-ROW($B$2)</f>
         <v>78</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="H80" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="J80" s="12">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K80" s="12"/>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" ht="15.75" spans="1:11">
       <c r="A81" s="2"/>
       <c r="B81" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B81)-ROW($B$2)</f>
         <v>79</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="H81" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="J81" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" s="9"/>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" ht="15.75" spans="1:11">
       <c r="A82" s="2"/>
       <c r="B82" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B82)-ROW($B$2)</f>
         <v>80</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="G82" s="13" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="H82" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="J82" s="12">
         <v>1</v>
       </c>
       <c r="K82" s="12"/>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" ht="15.75" spans="1:11">
       <c r="A83" s="2"/>
       <c r="B83" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B83)-ROW($B$2)</f>
         <v>81</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="H83" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="J83" s="9">
         <v>1</v>
       </c>
       <c r="K83" s="9"/>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" ht="24.75" spans="1:11">
       <c r="A84" s="2"/>
       <c r="B84" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B84)-ROW($B$2)</f>
         <v>82</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="H84" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="J84" s="12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K84" s="12"/>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" ht="15.75" spans="1:11">
       <c r="A85" s="2"/>
       <c r="B85" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B85)-ROW($B$2)</f>
         <v>83</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="H85" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>284</v>
+        <v>374</v>
       </c>
       <c r="J85" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K85" s="9"/>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" ht="15.75" spans="1:11">
       <c r="A86" s="2"/>
       <c r="B86" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B86)-ROW($B$2)</f>
         <v>84</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H86" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="J86" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K86" s="12"/>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" ht="15.75" spans="1:11">
       <c r="A87" s="2"/>
       <c r="B87" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B87)-ROW($B$2)</f>
         <v>85</v>
       </c>
-      <c r="C87" s="11" t="s">
-        <v>267</v>
+      <c r="C87" s="8" t="s">
+        <v>311</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="H87" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>288</v>
+        <v>382</v>
       </c>
       <c r="J87" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K87" s="9"/>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" ht="15.75" spans="1:11">
       <c r="A88" s="2"/>
       <c r="B88" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B88)-ROW($B$2)</f>
         <v>86</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G88" s="13" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="H88" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="J88" s="12">
         <v>1</v>
       </c>
       <c r="K88" s="12"/>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" ht="15.75" spans="1:11">
       <c r="A89" s="2"/>
       <c r="B89" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B89)-ROW($B$2)</f>
         <v>87</v>
       </c>
-      <c r="C89" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="G89" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="H89" s="18" t="s">
+      <c r="C89" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D89" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="F89" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="G89" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="H89" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I89" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="J89" s="9">
-        <v>2</v>
-      </c>
-      <c r="K89" s="9"/>
-    </row>
-    <row r="90" spans="1:11">
+      <c r="I89" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J89" s="14">
+        <v>4</v>
+      </c>
+      <c r="K89" s="17"/>
+    </row>
+    <row r="90" ht="15.75" spans="1:11">
       <c r="A90" s="2"/>
       <c r="B90" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B90)-ROW($B$2)</f>
         <v>88</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F90" s="12" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="H90" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="J90" s="12">
         <v>1</v>
       </c>
       <c r="K90" s="12"/>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" ht="15.75" spans="1:11">
       <c r="A91" s="2"/>
       <c r="B91" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B91)-ROW($B$2)</f>
         <v>89</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="H91" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>386</v>
+        <v>319</v>
       </c>
       <c r="J91" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K91" s="9"/>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" ht="24.75" spans="1:11">
       <c r="A92" s="2"/>
       <c r="B92" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B92)-ROW($B$2)</f>
         <v>90</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F92" s="12" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="H92" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="J92" s="12">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K92" s="12"/>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B93)-ROW($B$2)</f>
         <v>91</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="H93" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>394</v>
+        <v>323</v>
       </c>
       <c r="J93" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K93" s="9"/>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" ht="15.75" spans="1:11">
       <c r="A94" s="2"/>
       <c r="B94" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B94)-ROW($B$2)</f>
         <v>92</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="G94" s="13" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="H94" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="J94" s="12">
         <v>1</v>
       </c>
       <c r="K94" s="12"/>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" ht="15.75" spans="1:11">
       <c r="A95" s="2"/>
       <c r="B95" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B95)-ROW($B$2)</f>
         <v>93</v>
       </c>
-      <c r="C95" s="8" t="s">
-        <v>267</v>
+      <c r="C95" s="11" t="s">
+        <v>311</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>401</v>
+        <v>326</v>
+      </c>
+      <c r="G95" s="13" t="s">
+        <v>408</v>
       </c>
       <c r="H95" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="J95" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K95" s="9"/>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" ht="15.75" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B96)-ROW($B$2)</f>
         <v>94</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="F96" s="12" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G96" s="13" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="H96" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="J96" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K96" s="12"/>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" ht="15.75" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B97)-ROW($B$2)</f>
         <v>95</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="H97" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="J97" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K97" s="9"/>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" ht="15.75" spans="1:11">
       <c r="A98" s="2"/>
       <c r="B98" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B98)-ROW($B$2)</f>
         <v>96</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F98" s="12" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="H98" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="J98" s="12">
         <v>1</v>
       </c>
       <c r="K98" s="12"/>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" ht="15.75" spans="1:11">
       <c r="A99" s="2"/>
       <c r="B99" s="7">
-        <f t="shared" si="2"/>
+        <f>ROW(B99)-ROW($B$2)</f>
         <v>97</v>
       </c>
-      <c r="C99" s="11" t="s">
-        <v>267</v>
+      <c r="C99" s="8" t="s">
+        <v>311</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="H99" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="J99" s="9">
         <v>1</v>
       </c>
       <c r="K99" s="9"/>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" ht="15.75" spans="1:11">
       <c r="A100" s="2"/>
       <c r="B100" s="7">
-        <f t="shared" ref="B100:B131" si="3">ROW(B100)-ROW($B$2)</f>
+        <f>ROW(B100)-ROW($B$2)</f>
         <v>98</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="F100" s="12" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="H100" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="J100" s="12">
         <v>1</v>
       </c>
       <c r="K100" s="12"/>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" ht="15.75" spans="1:11">
       <c r="A101" s="2"/>
       <c r="B101" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B101)-ROW($B$2)</f>
         <v>99</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="H101" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="J101" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K101" s="9"/>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" ht="15.75" spans="1:11">
       <c r="A102" s="2"/>
       <c r="B102" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B102)-ROW($B$2)</f>
         <v>100</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D102" s="14" t="s">
-        <v>427</v>
-      </c>
-      <c r="E102" s="15" t="s">
-        <v>339</v>
-      </c>
-      <c r="F102" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="G102" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="H102" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G102" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="H102" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I102" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J102" s="14">
-        <v>2</v>
-      </c>
-      <c r="K102" s="16" t="s">
-        <v>137</v>
-      </c>
+      <c r="I102" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="J102" s="12">
+        <v>3</v>
+      </c>
+      <c r="K102" s="12"/>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="2"/>
       <c r="B103" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B103)-ROW($B$2)</f>
         <v>101</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="D103" s="14" t="s">
-        <v>428</v>
-      </c>
-      <c r="E103" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="F103" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="G103" s="15" t="s">
-        <v>363</v>
-      </c>
-      <c r="H103" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="H103" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I103" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J103" s="14">
-        <v>1</v>
-      </c>
-      <c r="K103" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="36">
+      <c r="I103" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="J103" s="9">
+        <v>8</v>
+      </c>
+      <c r="K103" s="9"/>
+    </row>
+    <row r="104" spans="1:11">
       <c r="A104" s="2"/>
       <c r="B104" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B104)-ROW($B$2)</f>
         <v>102</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="G104" s="13" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="H104" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="J104" s="12">
         <v>1</v>
@@ -5744,283 +6414,279 @@
     <row r="105" spans="1:11">
       <c r="A105" s="2"/>
       <c r="B105" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B105)-ROW($B$2)</f>
         <v>103</v>
       </c>
-      <c r="C105" s="8" t="s">
-        <v>294</v>
+      <c r="C105" s="11" t="s">
+        <v>301</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="F105" s="9" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="H105" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="J105" s="9">
         <v>1</v>
       </c>
       <c r="K105" s="9"/>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" ht="15.75" spans="1:11">
       <c r="A106" s="2"/>
       <c r="B106" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B106)-ROW($B$2)</f>
         <v>104</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="F106" s="12" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="H106" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="J106" s="12">
         <v>1</v>
       </c>
       <c r="K106" s="12"/>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" ht="15.75" spans="1:11">
       <c r="A107" s="2"/>
       <c r="B107" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B107)-ROW($B$2)</f>
         <v>105</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="H107" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="E107" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="F107" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="G107" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="H107" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I107" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="J107" s="9">
-        <v>1</v>
-      </c>
-      <c r="K107" s="9"/>
-    </row>
-    <row r="108" spans="1:11">
+      <c r="I107" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J107" s="14">
+        <v>1</v>
+      </c>
+      <c r="K107" s="17"/>
+    </row>
+    <row r="108" ht="15.75" spans="1:11">
       <c r="A108" s="2"/>
       <c r="B108" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B108)-ROW($B$2)</f>
         <v>106</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D108" s="14" t="s">
-        <v>444</v>
-      </c>
-      <c r="E108" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="F108" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="G108" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="H108" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="E108" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G108" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="H108" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I108" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J108" s="14">
-        <v>1</v>
-      </c>
-      <c r="K108" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11">
+      <c r="I108" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="J108" s="12">
+        <v>1</v>
+      </c>
+      <c r="K108" s="12"/>
+    </row>
+    <row r="109" ht="36.75" spans="1:11">
       <c r="A109" s="2"/>
       <c r="B109" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B109)-ROW($B$2)</f>
         <v>107</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="F109" s="9" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="H109" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>272</v>
+        <v>462</v>
       </c>
       <c r="J109" s="9">
         <v>1</v>
       </c>
       <c r="K109" s="9"/>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" ht="15.75" spans="1:11">
       <c r="A110" s="2"/>
       <c r="B110" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B110)-ROW($B$2)</f>
         <v>108</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D110" s="14" t="s">
-        <v>448</v>
-      </c>
-      <c r="E110" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="F110" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="G110" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="H110" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="F110" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G110" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="H110" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I110" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J110" s="14">
-        <v>1</v>
-      </c>
-      <c r="K110" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11">
+      <c r="I110" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="J110" s="12">
+        <v>1</v>
+      </c>
+      <c r="K110" s="12"/>
+    </row>
+    <row r="111" ht="15.75" spans="1:11">
       <c r="A111" s="2"/>
       <c r="B111" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B111)-ROW($B$2)</f>
         <v>109</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="F111" s="9" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="H111" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="J111" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K111" s="9"/>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" ht="15.75" spans="1:11">
       <c r="A112" s="2"/>
       <c r="B112" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B112)-ROW($B$2)</f>
         <v>110</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="F112" s="12" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G112" s="13" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="H112" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="J112" s="12">
         <v>1</v>
       </c>
       <c r="K112" s="12"/>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" ht="15.75" spans="1:11">
       <c r="A113" s="2"/>
       <c r="B113" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B113)-ROW($B$2)</f>
         <v>111</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="G113" s="15" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="H113" s="14" t="s">
         <v>74</v>
@@ -6031,820 +6697,816 @@
       <c r="J113" s="14">
         <v>1</v>
       </c>
-      <c r="K113" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
+      <c r="K113" s="17"/>
+    </row>
+    <row r="114" ht="15.75" spans="1:11">
       <c r="A114" s="2"/>
       <c r="B114" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B114)-ROW($B$2)</f>
         <v>112</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="D114" s="14" t="s">
-        <v>457</v>
-      </c>
-      <c r="E114" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="F114" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="G114" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="H114" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G114" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="H114" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I114" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J114" s="14">
-        <v>1</v>
-      </c>
-      <c r="K114" s="16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
+      <c r="I114" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="J114" s="12">
+        <v>1</v>
+      </c>
+      <c r="K114" s="12"/>
+    </row>
+    <row r="115" ht="15.75" spans="1:11">
       <c r="A115" s="2"/>
       <c r="B115" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B115)-ROW($B$2)</f>
         <v>113</v>
       </c>
-      <c r="C115" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="G115" s="13" t="s">
-        <v>461</v>
-      </c>
-      <c r="H115" s="12" t="s">
+      <c r="C115" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D115" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="E115" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="F115" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="G115" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="H115" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I115" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="J115" s="12">
-        <v>6</v>
-      </c>
-      <c r="K115" s="12"/>
-    </row>
-    <row r="116" spans="1:11">
+      <c r="I115" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J115" s="14">
+        <v>1</v>
+      </c>
+      <c r="K115" s="17"/>
+    </row>
+    <row r="116" ht="15.75" spans="1:11">
       <c r="A116" s="2"/>
       <c r="B116" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B116)-ROW($B$2)</f>
         <v>114</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D116" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="F116" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G116" s="10" t="s">
-        <v>464</v>
-      </c>
-      <c r="H116" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="F116" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G116" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="H116" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I116" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="J116" s="9">
-        <v>1</v>
-      </c>
-      <c r="K116" s="9"/>
-    </row>
-    <row r="117" spans="1:11" ht="24">
+      <c r="I116" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="J116" s="12">
+        <v>4</v>
+      </c>
+      <c r="K116" s="12"/>
+    </row>
+    <row r="117" ht="15.75" spans="1:11">
       <c r="A117" s="2"/>
       <c r="B117" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B117)-ROW($B$2)</f>
         <v>115</v>
       </c>
-      <c r="C117" s="11" t="s">
-        <v>466</v>
-      </c>
-      <c r="D117" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>468</v>
+      <c r="C117" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>484</v>
       </c>
       <c r="F117" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G117" s="13" t="s">
-        <v>469</v>
-      </c>
-      <c r="H117" s="12" t="s">
-        <v>470</v>
-      </c>
-      <c r="I117" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J117" s="12">
-        <v>1</v>
-      </c>
-      <c r="K117" s="12"/>
-    </row>
-    <row r="118" spans="1:11" ht="48">
+        <v>326</v>
+      </c>
+      <c r="G117" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I117" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="J117" s="9">
+        <v>1</v>
+      </c>
+      <c r="K117" s="9"/>
+    </row>
+    <row r="118" ht="15.75" spans="1:11">
       <c r="A118" s="2"/>
       <c r="B118" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B118)-ROW($B$2)</f>
         <v>116</v>
       </c>
-      <c r="C118" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>473</v>
-      </c>
-      <c r="F118" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G118" s="10" t="s">
-        <v>474</v>
-      </c>
-      <c r="H118" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="I118" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J118" s="9">
-        <v>1</v>
-      </c>
-      <c r="K118" s="9"/>
-    </row>
-    <row r="119" spans="1:11" ht="36">
+      <c r="C118" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D118" s="14" t="s">
+        <v>486</v>
+      </c>
+      <c r="E118" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="F118" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="G118" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="H118" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I118" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J118" s="14">
+        <v>1</v>
+      </c>
+      <c r="K118" s="17"/>
+    </row>
+    <row r="119" ht="15.75" spans="1:11">
       <c r="A119" s="2"/>
       <c r="B119" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B119)-ROW($B$2)</f>
         <v>117</v>
       </c>
-      <c r="C119" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="E119" s="13" t="s">
-        <v>477</v>
-      </c>
-      <c r="F119" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G119" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="H119" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="I119" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J119" s="12">
-        <v>4</v>
-      </c>
-      <c r="K119" s="12"/>
-    </row>
-    <row r="120" spans="1:11" ht="24">
+      <c r="C119" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D119" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="E119" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="F119" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="G119" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="H119" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I119" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J119" s="14">
+        <v>1</v>
+      </c>
+      <c r="K119" s="17"/>
+    </row>
+    <row r="120" ht="15.75" spans="1:11">
       <c r="A120" s="2"/>
       <c r="B120" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B120)-ROW($B$2)</f>
         <v>118</v>
       </c>
-      <c r="C120" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="D120" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="E120" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="F120" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="G120" s="10" t="s">
-        <v>483</v>
-      </c>
-      <c r="H120" s="9" t="s">
-        <v>484</v>
+      <c r="C120" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="F120" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="G120" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="H120" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="I120" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J120" s="9">
-        <v>1</v>
-      </c>
-      <c r="K120" s="9"/>
-    </row>
-    <row r="121" spans="1:11">
+        <v>441</v>
+      </c>
+      <c r="J120" s="12">
+        <v>1</v>
+      </c>
+      <c r="K120" s="12"/>
+    </row>
+    <row r="121" ht="15.75" spans="1:11">
       <c r="A121" s="2"/>
       <c r="B121" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B121)-ROW($B$2)</f>
         <v>119</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="D121" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="E121" s="13" t="s">
-        <v>486</v>
-      </c>
-      <c r="F121" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="G121" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="H121" s="12" t="s">
-        <v>489</v>
-      </c>
-      <c r="I121" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J121" s="12">
-        <v>1</v>
-      </c>
-      <c r="K121" s="12"/>
-    </row>
-    <row r="122" spans="1:11" ht="24">
+        <v>301</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I121" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="J121" s="9">
+        <v>1</v>
+      </c>
+      <c r="K121" s="9"/>
+    </row>
+    <row r="122" ht="15.75" spans="1:11">
       <c r="A122" s="2"/>
       <c r="B122" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B122)-ROW($B$2)</f>
         <v>120</v>
       </c>
-      <c r="C122" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="D122" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="E122" s="10" t="s">
-        <v>491</v>
+      <c r="C122" s="11" t="s">
+        <v>495</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>497</v>
       </c>
       <c r="F122" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="G122" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="H122" s="9" t="s">
-        <v>494</v>
+        <v>34</v>
+      </c>
+      <c r="G122" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="H122" s="12" t="s">
+        <v>499</v>
       </c>
       <c r="I122" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J122" s="9">
-        <v>1</v>
-      </c>
-      <c r="K122" s="9"/>
-    </row>
-    <row r="123" spans="1:11" ht="24">
+        <v>158</v>
+      </c>
+      <c r="J122" s="12">
+        <v>1</v>
+      </c>
+      <c r="K122" s="12"/>
+    </row>
+    <row r="123" ht="48.75" spans="1:11">
       <c r="A123" s="2"/>
       <c r="B123" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B123)-ROW($B$2)</f>
         <v>121</v>
       </c>
-      <c r="C123" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="E123" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="F123" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="G123" s="13" t="s">
-        <v>498</v>
-      </c>
-      <c r="H123" s="12" t="s">
-        <v>499</v>
+      <c r="C123" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G123" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>504</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J123" s="12">
-        <v>1</v>
-      </c>
-      <c r="K123" s="12"/>
-    </row>
-    <row r="124" spans="1:11">
+        <v>158</v>
+      </c>
+      <c r="J123" s="9">
+        <v>1</v>
+      </c>
+      <c r="K123" s="9"/>
+    </row>
+    <row r="124" ht="36.75" spans="1:11">
       <c r="A124" s="2"/>
       <c r="B124" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B124)-ROW($B$2)</f>
         <v>122</v>
       </c>
-      <c r="C124" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="D124" s="9" t="s">
+      <c r="C124" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="E124" s="10" t="s">
-        <v>501</v>
+      <c r="D124" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>506</v>
       </c>
       <c r="F124" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="G124" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="H124" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G124" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="H124" s="12" t="s">
         <v>504</v>
       </c>
       <c r="I124" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J124" s="9">
-        <v>1</v>
-      </c>
-      <c r="K124" s="9"/>
-    </row>
-    <row r="125" spans="1:11">
+        <v>158</v>
+      </c>
+      <c r="J124" s="12">
+        <v>4</v>
+      </c>
+      <c r="K124" s="12"/>
+    </row>
+    <row r="125" ht="24.75" spans="1:11">
       <c r="A125" s="2"/>
       <c r="B125" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B125)-ROW($B$2)</f>
         <v>123</v>
       </c>
-      <c r="C125" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="D125" s="12" t="s">
-        <v>505</v>
-      </c>
-      <c r="E125" s="13" t="s">
-        <v>506</v>
-      </c>
-      <c r="F125" s="12" t="s">
-        <v>507</v>
-      </c>
-      <c r="G125" s="13" t="s">
+      <c r="C125" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="H125" s="12" t="s">
-        <v>504</v>
+      <c r="D125" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="G125" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>513</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J125" s="12">
-        <v>1</v>
-      </c>
-      <c r="K125" s="12"/>
+        <v>158</v>
+      </c>
+      <c r="J125" s="9">
+        <v>1</v>
+      </c>
+      <c r="K125" s="9"/>
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="2"/>
       <c r="B126" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B126)-ROW($B$2)</f>
         <v>124</v>
       </c>
-      <c r="C126" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="D126" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="E126" s="10" t="s">
-        <v>510</v>
-      </c>
-      <c r="F126" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="G126" s="10" t="s">
-        <v>512</v>
-      </c>
-      <c r="H126" s="9" t="s">
-        <v>504</v>
+      <c r="C126" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="E126" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="F126" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="G126" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="H126" s="12" t="s">
+        <v>518</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J126" s="9">
-        <v>1</v>
-      </c>
-      <c r="K126" s="9"/>
+        <v>158</v>
+      </c>
+      <c r="J126" s="12">
+        <v>1</v>
+      </c>
+      <c r="K126" s="12"/>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="2"/>
       <c r="B127" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B127)-ROW($B$2)</f>
         <v>125</v>
       </c>
-      <c r="C127" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="E127" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="F127" s="12" t="s">
-        <v>515</v>
-      </c>
-      <c r="G127" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="H127" s="12" t="s">
-        <v>504</v>
+      <c r="C127" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G127" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>523</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J127" s="12">
-        <v>1</v>
-      </c>
-      <c r="K127" s="12"/>
-    </row>
-    <row r="128" spans="1:11">
+        <v>158</v>
+      </c>
+      <c r="J127" s="9">
+        <v>1</v>
+      </c>
+      <c r="K127" s="9"/>
+    </row>
+    <row r="128" ht="24.75" spans="1:11">
       <c r="A128" s="2"/>
       <c r="B128" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B128)-ROW($B$2)</f>
         <v>126</v>
       </c>
-      <c r="C128" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="D128" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="G128" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="H128" s="9" t="s">
-        <v>520</v>
+      <c r="C128" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="F128" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="G128" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="H128" s="12" t="s">
+        <v>528</v>
       </c>
       <c r="I128" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J128" s="9">
-        <v>1</v>
-      </c>
-      <c r="K128" s="9"/>
+        <v>158</v>
+      </c>
+      <c r="J128" s="12">
+        <v>1</v>
+      </c>
+      <c r="K128" s="12"/>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="2"/>
       <c r="B129" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B129)-ROW($B$2)</f>
         <v>127</v>
       </c>
-      <c r="C129" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="D129" s="12" t="s">
-        <v>521</v>
-      </c>
-      <c r="E129" s="13" t="s">
-        <v>522</v>
-      </c>
-      <c r="F129" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G129" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="H129" s="12" t="s">
-        <v>504</v>
+      <c r="C129" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="G129" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J129" s="12">
-        <v>1</v>
-      </c>
-      <c r="K129" s="12"/>
-    </row>
-    <row r="130" spans="1:11" ht="24">
+        <v>158</v>
+      </c>
+      <c r="J129" s="9">
+        <v>1</v>
+      </c>
+      <c r="K129" s="9"/>
+    </row>
+    <row r="130" spans="1:11">
       <c r="A130" s="2"/>
       <c r="B130" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B130)-ROW($B$2)</f>
         <v>128</v>
       </c>
-      <c r="C130" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="D130" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="E130" s="10" t="s">
-        <v>526</v>
-      </c>
-      <c r="F130" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="G130" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="H130" s="9" t="s">
-        <v>529</v>
+      <c r="C130" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="E130" s="13" t="s">
+        <v>534</v>
+      </c>
+      <c r="F130" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="G130" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="H130" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J130" s="9">
-        <v>1</v>
-      </c>
-      <c r="K130" s="9"/>
-    </row>
-    <row r="131" spans="1:11" ht="24">
+        <v>158</v>
+      </c>
+      <c r="J130" s="12">
+        <v>1</v>
+      </c>
+      <c r="K130" s="12"/>
+    </row>
+    <row r="131" spans="1:11">
       <c r="A131" s="2"/>
       <c r="B131" s="7">
-        <f t="shared" si="3"/>
+        <f>ROW(B131)-ROW($B$2)</f>
         <v>129</v>
       </c>
-      <c r="C131" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="E131" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="F131" s="12" t="s">
-        <v>532</v>
-      </c>
-      <c r="G131" s="13" t="s">
-        <v>533</v>
-      </c>
-      <c r="H131" s="12" t="s">
-        <v>504</v>
+      <c r="C131" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="G131" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="I131" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J131" s="12">
-        <v>1</v>
-      </c>
-      <c r="K131" s="12"/>
+        <v>158</v>
+      </c>
+      <c r="J131" s="9">
+        <v>1</v>
+      </c>
+      <c r="K131" s="9"/>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="2"/>
       <c r="B132" s="7">
-        <f t="shared" ref="B132:B145" si="4">ROW(B132)-ROW($B$2)</f>
+        <f>ROW(B132)-ROW($B$2)</f>
         <v>130</v>
       </c>
-      <c r="C132" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="D132" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="E132" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="F132" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="G132" s="10" t="s">
-        <v>537</v>
-      </c>
-      <c r="H132" s="9" t="s">
-        <v>504</v>
+      <c r="C132" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="E132" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="F132" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="G132" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="H132" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J132" s="9">
-        <v>1</v>
-      </c>
-      <c r="K132" s="9"/>
-    </row>
-    <row r="133" spans="1:11" ht="24">
+        <v>158</v>
+      </c>
+      <c r="J132" s="12">
+        <v>1</v>
+      </c>
+      <c r="K132" s="12"/>
+    </row>
+    <row r="133" spans="1:11">
       <c r="A133" s="2"/>
       <c r="B133" s="7">
-        <f t="shared" si="4"/>
+        <f>ROW(B133)-ROW($B$2)</f>
         <v>131</v>
       </c>
-      <c r="C133" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="D133" s="12" t="s">
-        <v>538</v>
-      </c>
-      <c r="E133" s="13" t="s">
-        <v>539</v>
+      <c r="C133" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="E133" s="10" t="s">
+        <v>546</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G133" s="13" t="s">
-        <v>540</v>
-      </c>
-      <c r="H133" s="12" t="s">
-        <v>541</v>
+        <v>289</v>
+      </c>
+      <c r="G133" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="H133" s="9" t="s">
+        <v>548</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J133" s="12">
-        <v>1</v>
-      </c>
-      <c r="K133" s="12"/>
+        <v>158</v>
+      </c>
+      <c r="J133" s="9">
+        <v>1</v>
+      </c>
+      <c r="K133" s="9"/>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="2"/>
       <c r="B134" s="7">
-        <f t="shared" si="4"/>
+        <f>ROW(B134)-ROW($B$2)</f>
         <v>132</v>
       </c>
-      <c r="C134" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="D134" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="E134" s="10" t="s">
-        <v>543</v>
-      </c>
-      <c r="F134" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="G134" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="H134" s="9" t="s">
-        <v>504</v>
+      <c r="C134" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="E134" s="13" t="s">
+        <v>550</v>
+      </c>
+      <c r="F134" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="G134" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="H134" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="J134" s="9">
-        <v>1</v>
-      </c>
-      <c r="K134" s="9"/>
-    </row>
-    <row r="135" spans="1:11" ht="36">
+        <v>158</v>
+      </c>
+      <c r="J134" s="12">
+        <v>1</v>
+      </c>
+      <c r="K134" s="12"/>
+    </row>
+    <row r="135" ht="24.75" spans="1:11">
       <c r="A135" s="2"/>
       <c r="B135" s="7">
-        <f t="shared" si="4"/>
+        <f>ROW(B135)-ROW($B$2)</f>
         <v>133</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>139</v>
+        <v>508</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="J135" s="9">
         <v>1</v>
       </c>
       <c r="K135" s="9"/>
     </row>
-    <row r="136" spans="1:11" ht="24">
+    <row r="136" spans="1:11">
       <c r="A136" s="2"/>
       <c r="B136" s="7">
-        <f t="shared" si="4"/>
+        <f>ROW(B136)-ROW($B$2)</f>
         <v>134</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>479</v>
+        <v>508</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="F136" s="12" t="s">
-        <v>492</v>
+        <v>560</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>554</v>
+        <v>190</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="J136" s="12">
         <v>1</v>
       </c>
       <c r="K136" s="12"/>
     </row>
-    <row r="137" spans="1:11" ht="36">
+    <row r="137" ht="15.75" spans="1:11">
       <c r="A137" s="2"/>
       <c r="B137" s="7">
-        <f t="shared" si="4"/>
+        <f>ROW(B137)-ROW($B$2)</f>
         <v>135</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>555</v>
+        <v>508</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="I137" s="10" t="s">
-        <v>561</v>
+        <v>190</v>
+      </c>
+      <c r="I137" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="J137" s="9">
         <v>1</v>
       </c>
       <c r="K137" s="9"/>
     </row>
-    <row r="138" spans="1:11" ht="24">
+    <row r="138" ht="24.75" spans="1:11">
       <c r="A138" s="2"/>
       <c r="B138" s="7">
-        <f t="shared" si="4"/>
+        <f>ROW(B138)-ROW($B$2)</f>
         <v>136</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>562</v>
+        <v>508</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>564</v>
-      </c>
-      <c r="F138" s="12" t="s">
-        <v>565</v>
+        <v>567</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="I138" s="13" t="s">
-        <v>568</v>
+        <v>158</v>
       </c>
       <c r="J138" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K138" s="12"/>
     </row>
-    <row r="139" spans="1:11" ht="36">
+    <row r="139" ht="15.75" spans="1:11">
       <c r="A139" s="2"/>
       <c r="B139" s="7">
-        <f t="shared" si="4"/>
+        <f>ROW(B139)-ROW($B$2)</f>
         <v>137</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>569</v>
+        <v>508</v>
       </c>
       <c r="D139" s="9" t="s">
         <v>570</v>
@@ -6859,234 +7521,490 @@
         <v>573</v>
       </c>
       <c r="H139" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="I139" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J139" s="9">
+        <v>1</v>
+      </c>
+      <c r="K139" s="9"/>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140" s="2"/>
+      <c r="B140" s="7">
+        <f>ROW(B140)-ROW($B$2)</f>
+        <v>138</v>
+      </c>
+      <c r="C140" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D140" s="12" t="s">
         <v>574</v>
       </c>
-      <c r="I139" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="J139" s="9">
-        <v>1</v>
-      </c>
-      <c r="K139" s="9"/>
-    </row>
-    <row r="140" spans="1:11" ht="24">
-      <c r="B140" s="19">
-        <f t="shared" si="4"/>
-        <v>138</v>
-      </c>
-      <c r="C140" s="20" t="s">
+      <c r="E140" s="13" t="s">
         <v>575</v>
       </c>
-      <c r="D140" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E140" s="21" t="s">
+      <c r="F140" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="F140" s="18" t="s">
+      <c r="G140" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="H140" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="I140" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J140" s="12">
+        <v>1</v>
+      </c>
+      <c r="K140" s="12"/>
+    </row>
+    <row r="141" ht="36.75" spans="1:11">
+      <c r="A141" s="2"/>
+      <c r="B141" s="7">
+        <f>ROW(B141)-ROW($B$2)</f>
+        <v>139</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="G141" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="I141" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J141" s="9">
+        <v>1</v>
+      </c>
+      <c r="K141" s="9"/>
+    </row>
+    <row r="142" ht="15.75" spans="1:11">
+      <c r="A142" s="2"/>
+      <c r="B142" s="7">
+        <f>ROW(B142)-ROW($B$2)</f>
+        <v>140</v>
+      </c>
+      <c r="C142" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="E142" s="13" t="s">
+        <v>584</v>
+      </c>
+      <c r="F142" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="G142" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="H142" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="I142" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J142" s="12">
+        <v>1</v>
+      </c>
+      <c r="K142" s="12"/>
+    </row>
+    <row r="143" ht="48.75" spans="1:11">
+      <c r="A143" s="2"/>
+      <c r="B143" s="7">
+        <f>ROW(B143)-ROW($B$2)</f>
+        <v>141</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="E143" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="F143" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G140" s="21" t="s">
-        <v>577</v>
-      </c>
-      <c r="H140" s="18" t="s">
-        <v>578</v>
-      </c>
-      <c r="I140" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="J140" s="18">
-        <v>2</v>
-      </c>
-      <c r="K140" s="18"/>
-    </row>
-    <row r="141" spans="1:11" ht="25.5">
-      <c r="B141" s="19">
-        <f t="shared" si="4"/>
-        <v>139</v>
-      </c>
-      <c r="C141" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="D141" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E141" s="21" t="s">
-        <v>579</v>
-      </c>
-      <c r="F141" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G141" s="21" t="s">
-        <v>580</v>
-      </c>
-      <c r="H141" s="18" t="s">
-        <v>581</v>
-      </c>
-      <c r="I141" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="J141" s="18">
-        <v>1</v>
-      </c>
-      <c r="K141" s="23" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="36">
-      <c r="B142" s="19">
-        <f t="shared" si="4"/>
-        <v>140</v>
-      </c>
-      <c r="C142" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="D142" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E142" s="17" t="s">
-        <v>583</v>
-      </c>
-      <c r="F142" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G142" s="17" t="s">
-        <v>584</v>
-      </c>
-      <c r="H142" s="22" t="s">
-        <v>585</v>
-      </c>
-      <c r="I142" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="J142" s="22">
-        <v>1</v>
-      </c>
-      <c r="K142" s="22"/>
-    </row>
-    <row r="143" spans="1:11" ht="24">
-      <c r="B143" s="19">
-        <f t="shared" si="4"/>
-        <v>141</v>
-      </c>
-      <c r="C143" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="D143" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E143" s="17" t="s">
-        <v>586</v>
-      </c>
-      <c r="F143" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G143" s="17" t="s">
-        <v>587</v>
-      </c>
-      <c r="H143" s="22" t="s">
-        <v>588</v>
-      </c>
-      <c r="I143" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="J143" s="22">
-        <v>2</v>
-      </c>
-      <c r="K143" s="22"/>
-    </row>
-    <row r="144" spans="1:11" ht="36">
-      <c r="B144" s="19">
-        <f t="shared" si="4"/>
+      <c r="G143" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="I143" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J143" s="9">
+        <v>1</v>
+      </c>
+      <c r="K143" s="9"/>
+    </row>
+    <row r="144" ht="15.75" spans="1:11">
+      <c r="A144" s="2"/>
+      <c r="B144" s="7">
+        <f>ROW(B144)-ROW($B$2)</f>
         <v>142</v>
       </c>
-      <c r="C144" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="D144" s="18" t="s">
-        <v>145</v>
+      <c r="C144" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>592</v>
       </c>
       <c r="E144" s="13" t="s">
         <v>593</v>
       </c>
-      <c r="F144" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G144" s="17"/>
-      <c r="H144" s="22"/>
-      <c r="I144" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="J144" s="22">
-        <v>1</v>
-      </c>
-      <c r="K144" s="9" t="s">
+      <c r="F144" s="12" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="145" spans="2:11" ht="24.75" thickBot="1">
-      <c r="B145" s="19">
-        <f t="shared" si="4"/>
+      <c r="G144" s="13" t="s">
+        <v>595</v>
+      </c>
+      <c r="H144" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="I144" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J144" s="12">
+        <v>1</v>
+      </c>
+      <c r="K144" s="12"/>
+    </row>
+    <row r="145" ht="36.75" spans="1:11">
+      <c r="A145" s="2"/>
+      <c r="B145" s="7">
+        <f>ROW(B145)-ROW($B$2)</f>
         <v>143</v>
       </c>
-      <c r="C145" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="D145" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E145" s="17" t="s">
-        <v>589</v>
-      </c>
-      <c r="F145" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G145" s="17" t="s">
-        <v>590</v>
-      </c>
-      <c r="H145" s="22" t="s">
-        <v>591</v>
-      </c>
-      <c r="I145" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="J145" s="22">
-        <v>1</v>
-      </c>
-      <c r="K145" s="22" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="146" spans="2:11" ht="24.75" thickBot="1">
-      <c r="B146" s="19">
+      <c r="C145" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="E145" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="G145" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="I145" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="J145" s="9">
+        <v>1</v>
+      </c>
+      <c r="K145" s="9"/>
+    </row>
+    <row r="146" spans="1:11">
+      <c r="A146" s="2"/>
+      <c r="B146" s="7">
         <f>ROW(B146)-ROW($B$2)</f>
         <v>144</v>
       </c>
-      <c r="C146" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="D146" s="18" t="s">
+      <c r="C146" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="G146" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="I146" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="J146" s="12">
+        <v>2</v>
+      </c>
+      <c r="K146" s="12"/>
+    </row>
+    <row r="147" ht="36.75" spans="1:11">
+      <c r="A147" s="2"/>
+      <c r="B147" s="7">
+        <f>ROW(B147)-ROW($B$2)</f>
         <v>145</v>
       </c>
-      <c r="E146" s="13" t="s">
-        <v>595</v>
-      </c>
-      <c r="F146" s="22" t="s">
+      <c r="C147" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="E147" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="G147" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="I147" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="J147" s="9">
+        <v>1</v>
+      </c>
+      <c r="K147" s="9"/>
+    </row>
+    <row r="148" ht="24.75" spans="2:11">
+      <c r="B148" s="7">
+        <f>ROW(B148)-ROW($B$2)</f>
+        <v>146</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D148" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="F148" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G146" s="17">
+      <c r="G148" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="I148" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J148" s="9">
+        <v>2</v>
+      </c>
+      <c r="K148" s="9"/>
+    </row>
+    <row r="149" ht="39" spans="2:11">
+      <c r="B149" s="7">
+        <f>ROW(B149)-ROW($B$2)</f>
+        <v>147</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D149" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="F149" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G149" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="I149" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J149" s="9">
+        <v>1</v>
+      </c>
+      <c r="K149" s="18" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="150" ht="36.75" spans="2:11">
+      <c r="B150" s="7">
+        <f>ROW(B150)-ROW($B$2)</f>
+        <v>148</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E150" s="13" t="s">
+        <v>624</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G150" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="H150" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="I150" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J150" s="12">
+        <v>1</v>
+      </c>
+      <c r="K150" s="12"/>
+    </row>
+    <row r="151" ht="24.75" spans="2:11">
+      <c r="B151" s="7">
+        <f>ROW(B151)-ROW($B$2)</f>
+        <v>149</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D151" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E151" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G151" s="13" t="s">
+        <v>628</v>
+      </c>
+      <c r="H151" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="I151" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J151" s="12">
+        <v>2</v>
+      </c>
+      <c r="K151" s="12"/>
+    </row>
+    <row r="152" ht="26.25" spans="2:11">
+      <c r="B152" s="7">
+        <f>ROW(B152)-ROW($B$2)</f>
+        <v>150</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D152" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E152" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="F152" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G152" s="13"/>
+      <c r="H152" s="12"/>
+      <c r="I152" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J152" s="12">
+        <v>1</v>
+      </c>
+      <c r="K152" s="18" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="153" ht="24.75" spans="2:11">
+      <c r="B153" s="7">
+        <f>ROW(B153)-ROW($B$2)</f>
+        <v>151</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D153" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="F153" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G153" s="13" t="s">
+        <v>633</v>
+      </c>
+      <c r="H153" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="I153" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J153" s="12">
+        <v>1</v>
+      </c>
+      <c r="K153" s="18" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="154" ht="24.75" spans="2:11">
+      <c r="B154" s="7">
+        <f>ROW(B154)-ROW($B$2)</f>
+        <v>152</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="F154" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G154" s="13">
         <v>8900</v>
       </c>
-      <c r="H146" s="22" t="s">
-        <v>596</v>
-      </c>
-      <c r="I146" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="J146" s="22">
+      <c r="H154" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="I154" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J154" s="12">
         <v>4</v>
       </c>
-      <c r="K146" s="22"/>
+      <c r="K154" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7094,5 +8012,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Design-Files/OFP_MCM_v1.6/BOM/Client-BOM-OFP_MCM_v1.6.xlsx
+++ b/Design-Files/OFP_MCM_v1.6/BOM/Client-BOM-OFP_MCM_v1.6.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="639">
   <si>
     <t>#</t>
   </si>
@@ -440,6 +440,9 @@
     <t>DNP</t>
   </si>
   <si>
+    <t>DO NOT PLACE</t>
+  </si>
+  <si>
     <t>C143</t>
   </si>
   <si>
@@ -734,6 +737,9 @@
     <t>6.8uH</t>
   </si>
   <si>
+    <t>Inductor</t>
+  </si>
+  <si>
     <t>L2, L3, L4</t>
   </si>
   <si>
@@ -761,9 +767,6 @@
     <t>Bourns</t>
   </si>
   <si>
-    <t>Inductor</t>
-  </si>
-  <si>
     <t>L6</t>
   </si>
   <si>
@@ -1049,6 +1052,18 @@
     <t>RT0402BRD0710KL</t>
   </si>
   <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>RES SMD 11K OHM 0.1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RT0402BRE0711KL</t>
+  </si>
+  <si>
+    <t>11K</t>
+  </si>
+  <si>
     <t>R17</t>
   </si>
   <si>
@@ -1253,9 +1268,6 @@
     <t>RES 30K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>RC0603FR-0730KL</t>
-  </si>
-  <si>
     <t>30K</t>
   </si>
   <si>
@@ -1491,15 +1503,6 @@
   </si>
   <si>
     <t>R113</t>
-  </si>
-  <si>
-    <t>R116</t>
-  </si>
-  <si>
-    <t>RES 680 OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RC0402FR-07680RL</t>
   </si>
   <si>
     <t>R122</t>
@@ -3098,7 +3101,7 @@
     <col min="8" max="8" width="20.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="8.14285714285714" customWidth="1"/>
     <col min="10" max="10" width="9.28571428571429" customWidth="1"/>
-    <col min="11" max="11" width="23.8571428571429" customWidth="1"/>
+    <col min="11" max="11" width="28.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:11">
@@ -3441,7 +3444,7 @@
         <f>ROW(B12)-ROW($B$2)</f>
         <v>10</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="12" t="s">
@@ -3467,14 +3470,14 @@
       </c>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" ht="15.75" spans="1:11">
+    <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="7">
         <f>ROW(B13)-ROW($B$2)</f>
         <v>11</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>58</v>
@@ -3499,13 +3502,13 @@
       </c>
       <c r="K13" s="9"/>
     </row>
-    <row r="14" ht="15.75" spans="1:11">
+    <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="7">
         <f>ROW(B14)-ROW($B$2)</f>
         <v>12</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="12" t="s">
@@ -3531,14 +3534,14 @@
       </c>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" ht="15.75" spans="1:11">
+    <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="7">
         <f>ROW(B15)-ROW($B$2)</f>
         <v>13</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>67</v>
@@ -3563,14 +3566,14 @@
       </c>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" ht="15.75" spans="1:11">
+    <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="7">
         <f>ROW(B16)-ROW($B$2)</f>
         <v>14</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>10</v>
+      <c r="C16" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>71</v>
@@ -3595,14 +3598,14 @@
       </c>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" ht="15.75" spans="1:11">
+    <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="7">
         <f>ROW(B17)-ROW($B$2)</f>
         <v>15</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>76</v>
@@ -3627,14 +3630,14 @@
       </c>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" ht="15.75" spans="1:11">
+    <row r="18" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="7">
         <f>ROW(B18)-ROW($B$2)</f>
         <v>16</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>10</v>
+      <c r="C18" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>80</v>
@@ -3659,14 +3662,14 @@
       </c>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" ht="15.75" spans="1:11">
+    <row r="19" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="7">
         <f>ROW(B19)-ROW($B$2)</f>
         <v>17</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>83</v>
@@ -3691,14 +3694,14 @@
       </c>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" ht="15.75" spans="1:11">
+    <row r="20" spans="1:11">
       <c r="A20" s="2"/>
       <c r="B20" s="7">
         <f>ROW(B20)-ROW($B$2)</f>
         <v>18</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>10</v>
+      <c r="C20" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>87</v>
@@ -3730,7 +3733,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>91</v>
@@ -3761,8 +3764,8 @@
         <f>ROW(B22)-ROW($B$2)</f>
         <v>20</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>10</v>
+      <c r="C22" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>94</v>
@@ -3793,8 +3796,8 @@
         <f>ROW(B23)-ROW($B$2)</f>
         <v>21</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>10</v>
+      <c r="C23" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>98</v>
@@ -3825,8 +3828,8 @@
         <f>ROW(B24)-ROW($B$2)</f>
         <v>22</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>10</v>
+      <c r="C24" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>102</v>
@@ -3857,8 +3860,8 @@
         <f>ROW(B25)-ROW($B$2)</f>
         <v>23</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>10</v>
+      <c r="C25" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>106</v>
@@ -3889,8 +3892,8 @@
         <f>ROW(B26)-ROW($B$2)</f>
         <v>24</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>10</v>
+      <c r="C26" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>112</v>
@@ -3921,8 +3924,8 @@
         <f>ROW(B27)-ROW($B$2)</f>
         <v>25</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>10</v>
+      <c r="C27" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>116</v>
@@ -3953,8 +3956,8 @@
         <f>ROW(B28)-ROW($B$2)</f>
         <v>26</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>10</v>
+      <c r="C28" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>120</v>
@@ -4105,7 +4108,9 @@
       <c r="J32" s="14">
         <v>7</v>
       </c>
-      <c r="K32" s="17"/>
+      <c r="K32" s="17" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="33" ht="15.75" spans="1:11">
       <c r="A33" s="2"/>
@@ -4117,7 +4122,7 @@
         <v>21</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>39</v>
@@ -4137,7 +4142,9 @@
       <c r="J33" s="14">
         <v>1</v>
       </c>
-      <c r="K33" s="17"/>
+      <c r="K33" s="17" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="34" ht="15.75" spans="1:11">
       <c r="A34" s="2"/>
@@ -4149,22 +4156,22 @@
         <v>21</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J34" s="12">
         <v>1</v>
@@ -4181,16 +4188,16 @@
         <v>21</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>64</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>74</v>
@@ -4213,19 +4220,19 @@
         <v>21</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I36" s="13" t="s">
         <v>111</v>
@@ -4242,25 +4249,25 @@
         <v>35</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J37" s="9">
         <v>9</v>
@@ -4274,25 +4281,25 @@
         <v>36</v>
       </c>
       <c r="C38" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="I38" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="J38" s="12">
         <v>1</v>
@@ -4306,22 +4313,22 @@
         <v>37</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>136</v>
@@ -4329,7 +4336,9 @@
       <c r="J39" s="14">
         <v>1</v>
       </c>
-      <c r="K39" s="17"/>
+      <c r="K39" s="17" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="40" ht="24.75" spans="1:11">
       <c r="A40" s="2"/>
@@ -4338,25 +4347,25 @@
         <v>38</v>
       </c>
       <c r="C40" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="I40" s="13" t="s">
         <v>159</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>158</v>
       </c>
       <c r="J40" s="12">
         <v>1</v>
@@ -4370,121 +4379,121 @@
         <v>39</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J41" s="9">
         <v>1</v>
       </c>
       <c r="K41" s="9"/>
     </row>
-    <row r="42" ht="15.75" spans="1:11">
+    <row r="42" spans="1:11">
       <c r="A42" s="2"/>
       <c r="B42" s="7">
         <f>ROW(B42)-ROW($B$2)</f>
         <v>40</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J42" s="12">
         <v>1</v>
       </c>
       <c r="K42" s="12"/>
     </row>
-    <row r="43" ht="15.75" spans="1:11">
+    <row r="43" spans="1:11">
       <c r="A43" s="2"/>
       <c r="B43" s="7">
         <f>ROW(B43)-ROW($B$2)</f>
         <v>41</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J43" s="9">
         <v>2</v>
       </c>
       <c r="K43" s="9"/>
     </row>
-    <row r="44" ht="15.75" spans="1:11">
+    <row r="44" spans="1:11">
       <c r="A44" s="2"/>
       <c r="B44" s="7">
         <f>ROW(B44)-ROW($B$2)</f>
         <v>42</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J44" s="12">
         <v>3</v>
@@ -4498,25 +4507,25 @@
         <v>43</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J45" s="9">
         <v>2</v>
@@ -4530,13 +4539,13 @@
         <v>44</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>34</v>
@@ -4545,10 +4554,10 @@
         <v>5027740891</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J46" s="12">
         <v>1</v>
@@ -4562,25 +4571,25 @@
         <v>45</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J47" s="9">
         <v>1</v>
@@ -4594,57 +4603,57 @@
         <v>46</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J48" s="12">
         <v>1</v>
       </c>
       <c r="K48" s="12"/>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" ht="15.75" spans="1:11">
       <c r="A49" s="2"/>
       <c r="B49" s="7">
         <f>ROW(B49)-ROW($B$2)</f>
         <v>47</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J49" s="9">
         <v>1</v>
@@ -4658,25 +4667,25 @@
         <v>48</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J50" s="12">
         <v>2</v>
@@ -4690,22 +4699,22 @@
         <v>49</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="G51" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="H51" s="14" t="s">
         <v>219</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="F51" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G51" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>218</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>136</v>
@@ -4713,7 +4722,9 @@
       <c r="J51" s="14">
         <v>1</v>
       </c>
-      <c r="K51" s="17"/>
+      <c r="K51" s="17" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="52" ht="26.25" spans="1:11">
       <c r="A52" s="2"/>
@@ -4722,25 +4733,25 @@
         <v>50</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J52" s="12">
         <v>1</v>
@@ -4754,25 +4765,25 @@
         <v>51</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J53" s="12">
         <v>1</v>
@@ -4785,26 +4796,26 @@
         <f>ROW(B54)-ROW($B$2)</f>
         <v>52</v>
       </c>
-      <c r="C54" s="11" t="s">
-        <v>229</v>
+      <c r="C54" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J54" s="9">
         <v>3</v>
@@ -4817,26 +4828,26 @@
         <f>ROW(B55)-ROW($B$2)</f>
         <v>53</v>
       </c>
-      <c r="C55" s="11" t="s">
-        <v>229</v>
+      <c r="C55" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J55" s="12">
         <v>1</v>
@@ -4850,25 +4861,25 @@
         <v>54</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J56" s="9">
         <v>1</v>
@@ -4882,19 +4893,19 @@
         <v>55</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H57" s="14" t="s">
         <v>15</v>
@@ -4905,7 +4916,9 @@
       <c r="J57" s="14">
         <v>1</v>
       </c>
-      <c r="K57" s="17"/>
+      <c r="K57" s="17" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="58" ht="24.75" spans="1:11">
       <c r="A58" s="2"/>
@@ -4914,25 +4927,25 @@
         <v>56</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J58" s="9">
         <v>1</v>
@@ -4946,25 +4959,25 @@
         <v>57</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J59" s="12">
         <v>1</v>
@@ -4978,25 +4991,25 @@
         <v>58</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J60" s="9">
         <v>5</v>
@@ -5010,25 +5023,25 @@
         <v>59</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J61" s="12">
         <v>2</v>
@@ -5042,25 +5055,25 @@
         <v>60</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D62" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="H62" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="E62" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>273</v>
-      </c>
       <c r="I62" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J62" s="9">
         <v>1</v>
@@ -5074,25 +5087,25 @@
         <v>61</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J63" s="12">
         <v>1</v>
@@ -5106,25 +5119,25 @@
         <v>62</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J64" s="9">
         <v>1</v>
@@ -5138,25 +5151,25 @@
         <v>63</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J65" s="12">
         <v>1</v>
@@ -5170,25 +5183,25 @@
         <v>64</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J66" s="9">
         <v>6</v>
@@ -5202,25 +5215,25 @@
         <v>65</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J67" s="12">
         <v>1</v>
@@ -5234,25 +5247,25 @@
         <v>66</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H68" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J68" s="9">
         <v>7</v>
@@ -5266,25 +5279,25 @@
         <v>67</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H69" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J69" s="12">
         <v>1</v>
@@ -5298,25 +5311,25 @@
         <v>68</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J70" s="9">
         <v>1</v>
@@ -5330,25 +5343,25 @@
         <v>69</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H71" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J71" s="12">
         <v>1</v>
@@ -5362,25 +5375,25 @@
         <v>70</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J72" s="9">
         <v>1</v>
@@ -5394,25 +5407,25 @@
         <v>71</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H73" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J73" s="12">
         <v>1</v>
@@ -5426,25 +5439,25 @@
         <v>72</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H74" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J74" s="9">
         <v>1</v>
@@ -5458,222 +5471,222 @@
         <v>73</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H75" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J75" s="12">
         <v>1</v>
       </c>
       <c r="K75" s="12"/>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" ht="15.75" spans="1:11">
       <c r="A76" s="2"/>
       <c r="B76" s="7">
         <f>ROW(B76)-ROW($B$2)</f>
         <v>74</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H76" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J76" s="9">
         <v>1</v>
       </c>
       <c r="K76" s="9"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" ht="15.75" spans="1:11">
       <c r="A77" s="2"/>
       <c r="B77" s="7">
         <f>ROW(B77)-ROW($B$2)</f>
         <v>75</v>
       </c>
-      <c r="C77" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="E77" s="10" t="s">
+      <c r="C77" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="G77" s="10" t="s">
+      <c r="E77" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="H77" s="9" t="s">
+      <c r="F77" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="H77" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I77" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="J77" s="9">
-        <v>1</v>
-      </c>
-      <c r="K77" s="9"/>
-    </row>
-    <row r="78" spans="1:11">
+      <c r="I77" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="J77" s="12">
+        <v>1</v>
+      </c>
+      <c r="K77" s="12"/>
+    </row>
+    <row r="78" ht="15.75" spans="1:11">
       <c r="A78" s="2"/>
       <c r="B78" s="7">
         <f>ROW(B78)-ROW($B$2)</f>
         <v>76</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="E78" s="13" t="s">
+      <c r="C78" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D78" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="F78" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G78" s="13" t="s">
+      <c r="E78" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="H78" s="12" t="s">
+      <c r="F78" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="H78" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I78" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="J78" s="12">
-        <v>6</v>
-      </c>
-      <c r="K78" s="12"/>
-    </row>
-    <row r="79" ht="15.75" spans="1:11">
+      <c r="I78" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="J78" s="9">
+        <v>1</v>
+      </c>
+      <c r="K78" s="9"/>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="2"/>
       <c r="B79" s="7">
         <f>ROW(B79)-ROW($B$2)</f>
         <v>77</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="E79" s="10" t="s">
+      <c r="C79" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="F79" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G79" s="10" t="s">
+      <c r="E79" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="H79" s="9" t="s">
+      <c r="F79" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="H79" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I79" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="J79" s="9">
-        <v>1</v>
-      </c>
-      <c r="K79" s="9"/>
-    </row>
-    <row r="80" ht="24.75" spans="1:11">
+      <c r="I79" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="J79" s="12">
+        <v>6</v>
+      </c>
+      <c r="K79" s="12"/>
+    </row>
+    <row r="80" ht="15.75" spans="1:11">
       <c r="A80" s="2"/>
       <c r="B80" s="7">
         <f>ROW(B80)-ROW($B$2)</f>
         <v>78</v>
       </c>
-      <c r="C80" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="E80" s="13" t="s">
+      <c r="C80" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D80" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="F80" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G80" s="13" t="s">
+      <c r="E80" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="H80" s="12" t="s">
+      <c r="F80" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="H80" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I80" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="J80" s="12">
-        <v>18</v>
-      </c>
-      <c r="K80" s="12"/>
-    </row>
-    <row r="81" ht="15.75" spans="1:11">
+      <c r="I80" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="J80" s="9">
+        <v>1</v>
+      </c>
+      <c r="K80" s="9"/>
+    </row>
+    <row r="81" ht="24.75" spans="1:11">
       <c r="A81" s="2"/>
       <c r="B81" s="7">
         <f>ROW(B81)-ROW($B$2)</f>
         <v>79</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="E81" s="10" t="s">
+      <c r="C81" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="G81" s="10" t="s">
+      <c r="E81" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="H81" s="9" t="s">
+      <c r="F81" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="H81" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I81" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J81" s="9">
-        <v>2</v>
-      </c>
-      <c r="K81" s="9"/>
+      <c r="I81" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="J81" s="12">
+        <v>18</v>
+      </c>
+      <c r="K81" s="12"/>
     </row>
     <row r="82" ht="15.75" spans="1:11">
       <c r="A82" s="2"/>
@@ -5681,31 +5694,31 @@
         <f>ROW(B82)-ROW($B$2)</f>
         <v>80</v>
       </c>
-      <c r="C82" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E82" s="13" t="s">
+      <c r="C82" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="F82" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G82" s="13" t="s">
+      <c r="E82" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="H82" s="12" t="s">
+      <c r="F82" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="H82" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I82" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="J82" s="12">
-        <v>1</v>
-      </c>
-      <c r="K82" s="12"/>
+      <c r="I82" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="J82" s="9">
+        <v>2</v>
+      </c>
+      <c r="K82" s="9"/>
     </row>
     <row r="83" ht="15.75" spans="1:11">
       <c r="A83" s="2"/>
@@ -5713,95 +5726,95 @@
         <f>ROW(B83)-ROW($B$2)</f>
         <v>81</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="E83" s="10" t="s">
+      <c r="C83" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D83" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="F83" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="G83" s="10" t="s">
+      <c r="E83" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="H83" s="9" t="s">
+      <c r="F83" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="H83" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I83" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="J83" s="9">
-        <v>1</v>
-      </c>
-      <c r="K83" s="9"/>
-    </row>
-    <row r="84" ht="24.75" spans="1:11">
+      <c r="I83" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="J83" s="12">
+        <v>1</v>
+      </c>
+      <c r="K83" s="12"/>
+    </row>
+    <row r="84" ht="15.75" spans="1:11">
       <c r="A84" s="2"/>
       <c r="B84" s="7">
         <f>ROW(B84)-ROW($B$2)</f>
         <v>82</v>
       </c>
-      <c r="C84" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="E84" s="13" t="s">
+      <c r="C84" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D84" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="F84" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G84" s="13" t="s">
+      <c r="E84" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="H84" s="12" t="s">
+      <c r="F84" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="H84" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I84" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="J84" s="12">
-        <v>10</v>
-      </c>
-      <c r="K84" s="12"/>
-    </row>
-    <row r="85" ht="15.75" spans="1:11">
+      <c r="I84" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="J84" s="9">
+        <v>1</v>
+      </c>
+      <c r="K84" s="9"/>
+    </row>
+    <row r="85" ht="24.75" spans="1:11">
       <c r="A85" s="2"/>
       <c r="B85" s="7">
         <f>ROW(B85)-ROW($B$2)</f>
         <v>83</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G85" s="10" t="s">
+      <c r="C85" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D85" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="H85" s="9" t="s">
+      <c r="E85" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="H85" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I85" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="J85" s="9">
-        <v>1</v>
-      </c>
-      <c r="K85" s="9"/>
+      <c r="I85" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="J85" s="12">
+        <v>10</v>
+      </c>
+      <c r="K85" s="12"/>
     </row>
     <row r="86" ht="15.75" spans="1:11">
       <c r="A86" s="2"/>
@@ -5809,31 +5822,31 @@
         <f>ROW(B86)-ROW($B$2)</f>
         <v>84</v>
       </c>
-      <c r="C86" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="E86" s="13" t="s">
+      <c r="C86" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="F86" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G86" s="13" t="s">
+      <c r="E86" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="H86" s="12" t="s">
+      <c r="F86" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="H86" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I86" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="J86" s="12">
-        <v>1</v>
-      </c>
-      <c r="K86" s="12"/>
+      <c r="I86" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="J86" s="9">
+        <v>1</v>
+      </c>
+      <c r="K86" s="9"/>
     </row>
     <row r="87" ht="15.75" spans="1:11">
       <c r="A87" s="2"/>
@@ -5841,31 +5854,31 @@
         <f>ROW(B87)-ROW($B$2)</f>
         <v>85</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="E87" s="10" t="s">
+      <c r="C87" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D87" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="F87" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G87" s="10" t="s">
+      <c r="E87" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="H87" s="9" t="s">
+      <c r="F87" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G87" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="H87" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I87" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="J87" s="9">
-        <v>1</v>
-      </c>
-      <c r="K87" s="9"/>
+      <c r="I87" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="J87" s="12">
+        <v>1</v>
+      </c>
+      <c r="K87" s="12"/>
     </row>
     <row r="88" ht="15.75" spans="1:11">
       <c r="A88" s="2"/>
@@ -5873,31 +5886,31 @@
         <f>ROW(B88)-ROW($B$2)</f>
         <v>86</v>
       </c>
-      <c r="C88" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="E88" s="13" t="s">
+      <c r="C88" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D88" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="F88" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G88" s="13" t="s">
+      <c r="E88" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="H88" s="12" t="s">
+      <c r="F88" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="H88" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I88" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="J88" s="12">
-        <v>1</v>
-      </c>
-      <c r="K88" s="12"/>
+      <c r="I88" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="J88" s="9">
+        <v>1</v>
+      </c>
+      <c r="K88" s="9"/>
     </row>
     <row r="89" ht="15.75" spans="1:11">
       <c r="A89" s="2"/>
@@ -5905,31 +5918,31 @@
         <f>ROW(B89)-ROW($B$2)</f>
         <v>87</v>
       </c>
-      <c r="C89" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="E89" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="F89" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="G89" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="H89" s="14" t="s">
+      <c r="C89" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G89" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="H89" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I89" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J89" s="14">
-        <v>4</v>
-      </c>
-      <c r="K89" s="17"/>
+      <c r="I89" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="J89" s="12">
+        <v>1</v>
+      </c>
+      <c r="K89" s="12"/>
     </row>
     <row r="90" ht="15.75" spans="1:11">
       <c r="A90" s="2"/>
@@ -5937,31 +5950,33 @@
         <f>ROW(B90)-ROW($B$2)</f>
         <v>88</v>
       </c>
-      <c r="C90" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="F90" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G90" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="H90" s="12" t="s">
+      <c r="C90" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="F90" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="G90" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="H90" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I90" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="J90" s="12">
-        <v>1</v>
-      </c>
-      <c r="K90" s="12"/>
+      <c r="I90" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J90" s="14">
+        <v>4</v>
+      </c>
+      <c r="K90" s="17" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="91" ht="15.75" spans="1:11">
       <c r="A91" s="2"/>
@@ -5969,223 +5984,219 @@
         <f>ROW(B91)-ROW($B$2)</f>
         <v>89</v>
       </c>
-      <c r="C91" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="E91" s="10" t="s">
+      <c r="C91" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D91" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="F91" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G91" s="10" t="s">
+      <c r="E91" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="H91" s="9" t="s">
+      <c r="F91" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="H91" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I91" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="J91" s="9">
-        <v>7</v>
-      </c>
-      <c r="K91" s="9"/>
-    </row>
-    <row r="92" ht="24.75" spans="1:11">
+      <c r="I91" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="J91" s="12">
+        <v>1</v>
+      </c>
+      <c r="K91" s="12"/>
+    </row>
+    <row r="92" ht="15.75" spans="1:11">
       <c r="A92" s="2"/>
       <c r="B92" s="7">
         <f>ROW(B92)-ROW($B$2)</f>
         <v>90</v>
       </c>
-      <c r="C92" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="F92" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G92" s="13" t="s">
+      <c r="C92" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D92" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="H92" s="12" t="s">
+      <c r="E92" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="H92" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I92" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="J92" s="12">
-        <v>9</v>
-      </c>
-      <c r="K92" s="12"/>
-    </row>
-    <row r="93" spans="1:11">
+      <c r="I92" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="J92" s="9">
+        <v>7</v>
+      </c>
+      <c r="K92" s="9"/>
+    </row>
+    <row r="93" ht="24.75" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="7">
         <f>ROW(B93)-ROW($B$2)</f>
         <v>91</v>
       </c>
-      <c r="C93" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="E93" s="10" t="s">
+      <c r="C93" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D93" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="F93" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G93" s="10" t="s">
+      <c r="E93" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="H93" s="9" t="s">
+      <c r="F93" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G93" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="H93" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I93" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="J93" s="9">
-        <v>5</v>
-      </c>
-      <c r="K93" s="9"/>
-    </row>
-    <row r="94" ht="15.75" spans="1:11">
+      <c r="I93" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="J93" s="12">
+        <v>9</v>
+      </c>
+      <c r="K93" s="12"/>
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94" s="2"/>
       <c r="B94" s="7">
         <f>ROW(B94)-ROW($B$2)</f>
         <v>92</v>
       </c>
-      <c r="C94" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="E94" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="F94" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G94" s="13" t="s">
+      <c r="C94" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D94" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="H94" s="12" t="s">
+      <c r="E94" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="H94" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I94" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="J94" s="12">
-        <v>1</v>
-      </c>
-      <c r="K94" s="12"/>
-    </row>
-    <row r="95" ht="15.75" spans="1:11">
+      <c r="I94" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="J94" s="9">
+        <v>5</v>
+      </c>
+      <c r="K94" s="9"/>
+    </row>
+    <row r="95" spans="1:11">
       <c r="A95" s="2"/>
       <c r="B95" s="7">
         <f>ROW(B95)-ROW($B$2)</f>
         <v>93</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="E95" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D95" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="F95" s="9" t="s">
-        <v>326</v>
+      <c r="E95" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>327</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="H95" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="H95" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I95" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="J95" s="9">
-        <v>2</v>
-      </c>
-      <c r="K95" s="9"/>
-    </row>
-    <row r="96" ht="15.75" spans="1:11">
+      <c r="I95" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="J95" s="12">
+        <v>1</v>
+      </c>
+      <c r="K95" s="12"/>
+    </row>
+    <row r="96" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="7">
         <f>ROW(B96)-ROW($B$2)</f>
         <v>94</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="E96" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D96" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="F96" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G96" s="13" t="s">
+      <c r="E96" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="H96" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="I96" s="13" t="s">
+      <c r="F96" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G96" s="10"/>
+      <c r="H96" s="9"/>
+      <c r="I96" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="J96" s="12">
-        <v>1</v>
-      </c>
-      <c r="K96" s="12"/>
-    </row>
-    <row r="97" ht="15.75" spans="1:11">
+      <c r="J96" s="9">
+        <v>2</v>
+      </c>
+      <c r="K96" s="9"/>
+    </row>
+    <row r="97" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="7">
         <f>ROW(B97)-ROW($B$2)</f>
         <v>95</v>
       </c>
-      <c r="C97" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D97" s="9" t="s">
+      <c r="C97" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="F97" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G97" s="10" t="s">
+      <c r="F97" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G97" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="H97" s="9" t="s">
+      <c r="H97" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I97" s="10" t="s">
+      <c r="I97" s="13" t="s">
         <v>417</v>
       </c>
-      <c r="J97" s="9">
-        <v>1</v>
-      </c>
-      <c r="K97" s="9"/>
+      <c r="J97" s="12">
+        <v>1</v>
+      </c>
+      <c r="K97" s="12"/>
     </row>
     <row r="98" ht="15.75" spans="1:11">
       <c r="A98" s="2"/>
@@ -6193,31 +6204,31 @@
         <f>ROW(B98)-ROW($B$2)</f>
         <v>96</v>
       </c>
-      <c r="C98" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D98" s="12" t="s">
+      <c r="C98" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D98" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="E98" s="13" t="s">
+      <c r="E98" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="F98" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G98" s="13" t="s">
+      <c r="F98" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G98" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="H98" s="12" t="s">
+      <c r="H98" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I98" s="13" t="s">
+      <c r="I98" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="J98" s="12">
-        <v>1</v>
-      </c>
-      <c r="K98" s="12"/>
+      <c r="J98" s="9">
+        <v>1</v>
+      </c>
+      <c r="K98" s="9"/>
     </row>
     <row r="99" ht="15.75" spans="1:11">
       <c r="A99" s="2"/>
@@ -6225,31 +6236,31 @@
         <f>ROW(B99)-ROW($B$2)</f>
         <v>97</v>
       </c>
-      <c r="C99" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D99" s="9" t="s">
+      <c r="C99" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D99" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="E99" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="F99" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="G99" s="10" t="s">
+      <c r="F99" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G99" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="H99" s="9" t="s">
+      <c r="H99" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I99" s="10" t="s">
+      <c r="I99" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="J99" s="9">
-        <v>1</v>
-      </c>
-      <c r="K99" s="9"/>
+      <c r="J99" s="12">
+        <v>1</v>
+      </c>
+      <c r="K99" s="12"/>
     </row>
     <row r="100" ht="15.75" spans="1:11">
       <c r="A100" s="2"/>
@@ -6257,31 +6268,31 @@
         <f>ROW(B100)-ROW($B$2)</f>
         <v>98</v>
       </c>
-      <c r="C100" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D100" s="12" t="s">
+      <c r="C100" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D100" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="E100" s="13" t="s">
+      <c r="E100" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="F100" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G100" s="13" t="s">
+      <c r="F100" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G100" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="H100" s="12" t="s">
+      <c r="H100" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I100" s="13" t="s">
+      <c r="I100" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="J100" s="12">
-        <v>1</v>
-      </c>
-      <c r="K100" s="12"/>
+      <c r="J100" s="9">
+        <v>1</v>
+      </c>
+      <c r="K100" s="9"/>
     </row>
     <row r="101" ht="15.75" spans="1:11">
       <c r="A101" s="2"/>
@@ -6289,31 +6300,31 @@
         <f>ROW(B101)-ROW($B$2)</f>
         <v>99</v>
       </c>
-      <c r="C101" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D101" s="9" t="s">
+      <c r="C101" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D101" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="E101" s="10" t="s">
+      <c r="E101" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="F101" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G101" s="10" t="s">
+      <c r="F101" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="G101" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="H101" s="9" t="s">
+      <c r="H101" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I101" s="10" t="s">
+      <c r="I101" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="J101" s="9">
-        <v>1</v>
-      </c>
-      <c r="K101" s="9"/>
+      <c r="J101" s="12">
+        <v>1</v>
+      </c>
+      <c r="K101" s="12"/>
     </row>
     <row r="102" ht="15.75" spans="1:11">
       <c r="A102" s="2"/>
@@ -6321,63 +6332,63 @@
         <f>ROW(B102)-ROW($B$2)</f>
         <v>100</v>
       </c>
-      <c r="C102" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D102" s="12" t="s">
+      <c r="C102" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D102" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="E102" s="13" t="s">
+      <c r="E102" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="F102" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G102" s="13" t="s">
+      <c r="F102" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G102" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="H102" s="12" t="s">
+      <c r="H102" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I102" s="13" t="s">
+      <c r="I102" s="10" t="s">
         <v>437</v>
       </c>
-      <c r="J102" s="12">
-        <v>3</v>
-      </c>
-      <c r="K102" s="12"/>
-    </row>
-    <row r="103" spans="1:11">
+      <c r="J102" s="9">
+        <v>1</v>
+      </c>
+      <c r="K102" s="9"/>
+    </row>
+    <row r="103" ht="15.75" spans="1:11">
       <c r="A103" s="2"/>
       <c r="B103" s="7">
         <f>ROW(B103)-ROW($B$2)</f>
         <v>101</v>
       </c>
-      <c r="C103" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D103" s="9" t="s">
+      <c r="C103" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D103" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="E103" s="10" t="s">
+      <c r="E103" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="F103" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G103" s="10" t="s">
+      <c r="F103" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G103" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="H103" s="9" t="s">
+      <c r="H103" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I103" s="10" t="s">
+      <c r="I103" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="J103" s="9">
-        <v>8</v>
-      </c>
-      <c r="K103" s="9"/>
+      <c r="J103" s="12">
+        <v>3</v>
+      </c>
+      <c r="K103" s="12"/>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="2"/>
@@ -6385,31 +6396,31 @@
         <f>ROW(B104)-ROW($B$2)</f>
         <v>102</v>
       </c>
-      <c r="C104" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D104" s="12" t="s">
+      <c r="C104" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="E104" s="13" t="s">
+      <c r="E104" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="F104" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G104" s="13" t="s">
+      <c r="F104" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G104" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="H104" s="12" t="s">
+      <c r="H104" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I104" s="13" t="s">
+      <c r="I104" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="J104" s="12">
-        <v>1</v>
-      </c>
-      <c r="K104" s="12"/>
+      <c r="J104" s="9">
+        <v>8</v>
+      </c>
+      <c r="K104" s="9"/>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="2"/>
@@ -6418,62 +6429,62 @@
         <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D105" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="D105" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="E105" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="F105" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G105" s="10" t="s">
+      <c r="F105" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G105" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="H105" s="9" t="s">
+      <c r="H105" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I105" s="10" t="s">
+      <c r="I105" s="13" t="s">
         <v>449</v>
       </c>
-      <c r="J105" s="9">
-        <v>1</v>
-      </c>
-      <c r="K105" s="9"/>
-    </row>
-    <row r="106" ht="15.75" spans="1:11">
+      <c r="J105" s="12">
+        <v>1</v>
+      </c>
+      <c r="K105" s="12"/>
+    </row>
+    <row r="106" spans="1:11">
       <c r="A106" s="2"/>
       <c r="B106" s="7">
         <f>ROW(B106)-ROW($B$2)</f>
         <v>104</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D106" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="D106" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="E106" s="13" t="s">
+      <c r="E106" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="F106" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G106" s="13" t="s">
+      <c r="F106" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G106" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="H106" s="12" t="s">
+      <c r="H106" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I106" s="13" t="s">
+      <c r="I106" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="J106" s="12">
-        <v>1</v>
-      </c>
-      <c r="K106" s="12"/>
+      <c r="J106" s="9">
+        <v>1</v>
+      </c>
+      <c r="K106" s="9"/>
     </row>
     <row r="107" ht="15.75" spans="1:11">
       <c r="A107" s="2"/>
@@ -6481,31 +6492,31 @@
         <f>ROW(B107)-ROW($B$2)</f>
         <v>105</v>
       </c>
-      <c r="C107" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D107" s="14" t="s">
+      <c r="C107" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D107" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="E107" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="F107" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="G107" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H107" s="14" t="s">
+      <c r="E107" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G107" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="H107" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I107" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J107" s="14">
-        <v>1</v>
-      </c>
-      <c r="K107" s="17"/>
+      <c r="I107" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="J107" s="12">
+        <v>1</v>
+      </c>
+      <c r="K107" s="12"/>
     </row>
     <row r="108" ht="15.75" spans="1:11">
       <c r="A108" s="2"/>
@@ -6513,95 +6524,97 @@
         <f>ROW(B108)-ROW($B$2)</f>
         <v>106</v>
       </c>
-      <c r="C108" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="E108" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="F108" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G108" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="H108" s="12" t="s">
+      <c r="C108" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="E108" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="F108" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="G108" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="H108" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I108" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="J108" s="12">
-        <v>1</v>
-      </c>
-      <c r="K108" s="12"/>
-    </row>
-    <row r="109" ht="36.75" spans="1:11">
+      <c r="I108" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J108" s="14">
+        <v>1</v>
+      </c>
+      <c r="K108" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" spans="1:11">
       <c r="A109" s="2"/>
       <c r="B109" s="7">
         <f>ROW(B109)-ROW($B$2)</f>
         <v>107</v>
       </c>
-      <c r="C109" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D109" s="9" t="s">
+      <c r="C109" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D109" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="E109" s="10" t="s">
+      <c r="E109" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="F109" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="G109" s="10" t="s">
+      <c r="F109" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G109" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="H109" s="9" t="s">
+      <c r="H109" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I109" s="10" t="s">
+      <c r="I109" s="13" t="s">
         <v>462</v>
       </c>
-      <c r="J109" s="9">
-        <v>1</v>
-      </c>
-      <c r="K109" s="9"/>
-    </row>
-    <row r="110" ht="15.75" spans="1:11">
+      <c r="J109" s="12">
+        <v>1</v>
+      </c>
+      <c r="K109" s="12"/>
+    </row>
+    <row r="110" ht="36.75" spans="1:11">
       <c r="A110" s="2"/>
       <c r="B110" s="7">
         <f>ROW(B110)-ROW($B$2)</f>
         <v>108</v>
       </c>
-      <c r="C110" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D110" s="12" t="s">
+      <c r="C110" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D110" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="E110" s="13" t="s">
+      <c r="E110" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="F110" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G110" s="13" t="s">
+      <c r="F110" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G110" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="H110" s="12" t="s">
+      <c r="H110" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I110" s="13" t="s">
+      <c r="I110" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="J110" s="12">
-        <v>1</v>
-      </c>
-      <c r="K110" s="12"/>
+      <c r="J110" s="9">
+        <v>1</v>
+      </c>
+      <c r="K110" s="9"/>
     </row>
     <row r="111" ht="15.75" spans="1:11">
       <c r="A111" s="2"/>
@@ -6609,31 +6622,31 @@
         <f>ROW(B111)-ROW($B$2)</f>
         <v>109</v>
       </c>
-      <c r="C111" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D111" s="9" t="s">
+      <c r="C111" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D111" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="E111" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="F111" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G111" s="10" t="s">
+      <c r="F111" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G111" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="H111" s="9" t="s">
+      <c r="H111" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I111" s="10" t="s">
+      <c r="I111" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="J111" s="9">
-        <v>1</v>
-      </c>
-      <c r="K111" s="9"/>
+      <c r="J111" s="12">
+        <v>1</v>
+      </c>
+      <c r="K111" s="12"/>
     </row>
     <row r="112" ht="15.75" spans="1:11">
       <c r="A112" s="2"/>
@@ -6641,31 +6654,31 @@
         <f>ROW(B112)-ROW($B$2)</f>
         <v>110</v>
       </c>
-      <c r="C112" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D112" s="12" t="s">
+      <c r="C112" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D112" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="E112" s="13" t="s">
+      <c r="E112" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="F112" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G112" s="13" t="s">
+      <c r="F112" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G112" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="H112" s="12" t="s">
+      <c r="H112" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I112" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="J112" s="12">
-        <v>1</v>
-      </c>
-      <c r="K112" s="12"/>
+      <c r="I112" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="J112" s="9">
+        <v>1</v>
+      </c>
+      <c r="K112" s="9"/>
     </row>
     <row r="113" ht="15.75" spans="1:11">
       <c r="A113" s="2"/>
@@ -6673,31 +6686,31 @@
         <f>ROW(B113)-ROW($B$2)</f>
         <v>111</v>
       </c>
-      <c r="C113" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D113" s="14" t="s">
-        <v>474</v>
-      </c>
-      <c r="E113" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="F113" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="G113" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="H113" s="14" t="s">
+      <c r="C113" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G113" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="H113" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I113" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J113" s="14">
-        <v>1</v>
-      </c>
-      <c r="K113" s="17"/>
+      <c r="I113" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="J113" s="12">
+        <v>1</v>
+      </c>
+      <c r="K113" s="12"/>
     </row>
     <row r="114" ht="15.75" spans="1:11">
       <c r="A114" s="2"/>
@@ -6705,31 +6718,33 @@
         <f>ROW(B114)-ROW($B$2)</f>
         <v>112</v>
       </c>
-      <c r="C114" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D114" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="E114" s="13" t="s">
-        <v>476</v>
-      </c>
-      <c r="F114" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G114" s="13" t="s">
-        <v>477</v>
-      </c>
-      <c r="H114" s="12" t="s">
+      <c r="C114" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D114" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="F114" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="G114" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="H114" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I114" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="J114" s="12">
-        <v>1</v>
-      </c>
-      <c r="K114" s="12"/>
+      <c r="I114" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J114" s="14">
+        <v>1</v>
+      </c>
+      <c r="K114" s="17" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="115" ht="15.75" spans="1:11">
       <c r="A115" s="2"/>
@@ -6737,31 +6752,31 @@
         <f>ROW(B115)-ROW($B$2)</f>
         <v>113</v>
       </c>
-      <c r="C115" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D115" s="14" t="s">
-        <v>478</v>
-      </c>
-      <c r="E115" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="F115" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="G115" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="H115" s="14" t="s">
+      <c r="C115" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G115" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="H115" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I115" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J115" s="14">
-        <v>1</v>
-      </c>
-      <c r="K115" s="17"/>
+      <c r="I115" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="J115" s="12">
+        <v>1</v>
+      </c>
+      <c r="K115" s="12"/>
     </row>
     <row r="116" ht="15.75" spans="1:11">
       <c r="A116" s="2"/>
@@ -6769,31 +6784,33 @@
         <f>ROW(B116)-ROW($B$2)</f>
         <v>114</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D116" s="12" t="s">
-        <v>479</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="F116" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G116" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="H116" s="12" t="s">
+      <c r="C116" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D116" s="14" t="s">
+        <v>482</v>
+      </c>
+      <c r="E116" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="F116" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="G116" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="H116" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I116" s="13" t="s">
-        <v>482</v>
-      </c>
-      <c r="J116" s="12">
-        <v>4</v>
-      </c>
-      <c r="K116" s="12"/>
+      <c r="I116" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J116" s="14">
+        <v>1</v>
+      </c>
+      <c r="K116" s="17" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="117" ht="15.75" spans="1:11">
       <c r="A117" s="2"/>
@@ -6801,31 +6818,31 @@
         <f>ROW(B117)-ROW($B$2)</f>
         <v>115</v>
       </c>
-      <c r="C117" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="D117" s="9" t="s">
+      <c r="C117" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D117" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="E117" s="10" t="s">
+      <c r="E117" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="F117" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G117" s="10" t="s">
+      <c r="F117" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="G117" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="H117" s="9" t="s">
+      <c r="H117" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I117" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="J117" s="9">
-        <v>1</v>
-      </c>
-      <c r="K117" s="9"/>
+      <c r="I117" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="J117" s="12">
+        <v>4</v>
+      </c>
+      <c r="K117" s="12"/>
     </row>
     <row r="118" ht="15.75" spans="1:11">
       <c r="A118" s="2"/>
@@ -6833,31 +6850,31 @@
         <f>ROW(B118)-ROW($B$2)</f>
         <v>116</v>
       </c>
-      <c r="C118" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D118" s="14" t="s">
-        <v>486</v>
-      </c>
-      <c r="E118" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="F118" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="G118" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="H118" s="14" t="s">
+      <c r="C118" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G118" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="H118" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I118" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="J118" s="14">
-        <v>1</v>
-      </c>
-      <c r="K118" s="17"/>
+      <c r="I118" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="J118" s="9">
+        <v>1</v>
+      </c>
+      <c r="K118" s="9"/>
     </row>
     <row r="119" ht="15.75" spans="1:11">
       <c r="A119" s="2"/>
@@ -6865,20 +6882,20 @@
         <f>ROW(B119)-ROW($B$2)</f>
         <v>117</v>
       </c>
-      <c r="C119" s="8" t="s">
-        <v>311</v>
+      <c r="C119" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>353</v>
+        <v>460</v>
       </c>
       <c r="F119" s="14" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="G119" s="15" t="s">
-        <v>354</v>
+        <v>461</v>
       </c>
       <c r="H119" s="14" t="s">
         <v>74</v>
@@ -6889,7 +6906,9 @@
       <c r="J119" s="14">
         <v>1</v>
       </c>
-      <c r="K119" s="17"/>
+      <c r="K119" s="17" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="120" ht="15.75" spans="1:11">
       <c r="A120" s="2"/>
@@ -6898,30 +6917,32 @@
         <v>118</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D120" s="12" t="s">
-        <v>488</v>
-      </c>
-      <c r="E120" s="13" t="s">
-        <v>489</v>
-      </c>
-      <c r="F120" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G120" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="H120" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="D120" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="E120" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="G120" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="H120" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="I120" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="J120" s="12">
-        <v>1</v>
-      </c>
-      <c r="K120" s="12"/>
+      <c r="I120" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J120" s="14">
+        <v>1</v>
+      </c>
+      <c r="K120" s="17" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="121" ht="15.75" spans="1:11">
       <c r="A121" s="2"/>
@@ -6930,57 +6951,57 @@
         <v>119</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F121" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H121" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J121" s="9">
         <v>1</v>
       </c>
       <c r="K121" s="9"/>
     </row>
-    <row r="122" ht="15.75" spans="1:11">
+    <row r="122" spans="1:11">
       <c r="A122" s="2"/>
       <c r="B122" s="7">
         <f>ROW(B122)-ROW($B$2)</f>
         <v>120</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G122" s="13" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I122" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J122" s="12">
         <v>1</v>
@@ -6994,25 +7015,25 @@
         <v>121</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J123" s="9">
         <v>1</v>
@@ -7026,25 +7047,25 @@
         <v>122</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G124" s="13" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H124" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I124" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J124" s="12">
         <v>4</v>
@@ -7058,25 +7079,25 @@
         <v>123</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F125" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J125" s="9">
         <v>1</v>
@@ -7090,25 +7111,25 @@
         <v>124</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G126" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H126" s="12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J126" s="12">
         <v>1</v>
@@ -7122,25 +7143,25 @@
         <v>125</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J127" s="9">
         <v>1</v>
@@ -7154,25 +7175,25 @@
         <v>126</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F128" s="12" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G128" s="13" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H128" s="12" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I128" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J128" s="12">
         <v>1</v>
@@ -7186,25 +7207,25 @@
         <v>127</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F129" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J129" s="9">
         <v>1</v>
@@ -7218,25 +7239,25 @@
         <v>128</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G130" s="13" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H130" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J130" s="12">
         <v>1</v>
@@ -7250,25 +7271,25 @@
         <v>129</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I131" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J131" s="9">
         <v>1</v>
@@ -7282,25 +7303,25 @@
         <v>130</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F132" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G132" s="13" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J132" s="12">
         <v>1</v>
@@ -7314,25 +7335,25 @@
         <v>131</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J133" s="9">
         <v>1</v>
@@ -7346,25 +7367,25 @@
         <v>132</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J134" s="12">
         <v>1</v>
@@ -7378,25 +7399,25 @@
         <v>133</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J135" s="9">
         <v>1</v>
@@ -7410,25 +7431,25 @@
         <v>134</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F136" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J136" s="12">
         <v>1</v>
@@ -7442,25 +7463,25 @@
         <v>135</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I137" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J137" s="9">
         <v>1</v>
@@ -7474,25 +7495,25 @@
         <v>136</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I138" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J138" s="12">
         <v>1</v>
@@ -7506,25 +7527,25 @@
         <v>137</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I139" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J139" s="9">
         <v>1</v>
@@ -7538,25 +7559,25 @@
         <v>138</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F140" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I140" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J140" s="12">
         <v>1</v>
@@ -7570,25 +7591,25 @@
         <v>139</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F141" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I141" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J141" s="9">
         <v>1</v>
@@ -7602,25 +7623,25 @@
         <v>140</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F142" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I142" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J142" s="12">
         <v>1</v>
@@ -7634,25 +7655,25 @@
         <v>141</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I143" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J143" s="9">
         <v>1</v>
@@ -7666,25 +7687,25 @@
         <v>142</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D144" s="12" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F144" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G144" s="13" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H144" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I144" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J144" s="12">
         <v>1</v>
@@ -7698,57 +7719,57 @@
         <v>143</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F145" s="9" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J145" s="9">
         <v>1</v>
       </c>
       <c r="K145" s="9"/>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" ht="15.75" spans="1:11">
       <c r="A146" s="2"/>
       <c r="B146" s="7">
         <f>ROW(B146)-ROW($B$2)</f>
         <v>144</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F146" s="12" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H146" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I146" s="13" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J146" s="12">
         <v>2</v>
@@ -7762,25 +7783,25 @@
         <v>145</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F147" s="9" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J147" s="9">
         <v>1</v>
@@ -7793,62 +7814,62 @@
         <v>146</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H148" s="9" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I148" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J148" s="9">
         <v>2</v>
       </c>
       <c r="K148" s="9"/>
     </row>
-    <row r="149" ht="39" spans="2:11">
+    <row r="149" ht="26.25" spans="2:11">
       <c r="B149" s="7">
         <f>ROW(B149)-ROW($B$2)</f>
         <v>147</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F149" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J149" s="9">
         <v>1</v>
       </c>
       <c r="K149" s="18" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="150" ht="36.75" spans="2:11">
@@ -7857,25 +7878,25 @@
         <v>148</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F150" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H150" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="I150" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J150" s="12">
         <v>1</v>
@@ -7888,44 +7909,44 @@
         <v>149</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F151" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H151" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="I151" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J151" s="12">
         <v>2</v>
       </c>
       <c r="K151" s="12"/>
     </row>
-    <row r="152" ht="26.25" spans="2:11">
+    <row r="152" ht="24.75" spans="2:11">
       <c r="B152" s="7">
         <f>ROW(B152)-ROW($B$2)</f>
         <v>150</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E152" s="13" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F152" s="12" t="s">
         <v>34</v>
@@ -7933,13 +7954,13 @@
       <c r="G152" s="13"/>
       <c r="H152" s="12"/>
       <c r="I152" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J152" s="12">
         <v>1</v>
       </c>
       <c r="K152" s="18" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="153" ht="24.75" spans="2:11">
@@ -7948,31 +7969,31 @@
         <v>151</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F153" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H153" s="12" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I153" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J153" s="12">
         <v>1</v>
       </c>
       <c r="K153" s="18" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="154" ht="24.75" spans="2:11">
@@ -7981,13 +8002,13 @@
         <v>152</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F154" s="12" t="s">
         <v>34</v>
@@ -7996,10 +8017,10 @@
         <v>8900</v>
       </c>
       <c r="H154" s="12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I154" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J154" s="12">
         <v>4</v>

--- a/Design-Files/OFP_MCM_v1.6/BOM/Client-BOM-OFP_MCM_v1.6.xlsx
+++ b/Design-Files/OFP_MCM_v1.6/BOM/Client-BOM-OFP_MCM_v1.6.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\nabilfesal-smartmeter-hw\Design-Files\OFP_MCM_v1.6\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7699DC48-84A6-4EEC-85C0-DA480E328EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -581,12 +588,6 @@
     <t>D14</t>
   </si>
   <si>
-    <t>TVS DIODE 12VWM 19.9VC DO214AA</t>
-  </si>
-  <si>
-    <t>SMBJ12A</t>
-  </si>
-  <si>
     <t>Littelfuse</t>
   </si>
   <si>
@@ -1550,12 +1551,6 @@
     <t>SW3, SW4, SW5, SW6</t>
   </si>
   <si>
-    <t>6mm 12mm Round Button 50mA Standing paste 6mm SPST 12V SMD,6x6mm Tactile Switches ROHS</t>
-  </si>
-  <si>
-    <t>TS-1002S-12026C</t>
-  </si>
-  <si>
     <t>IC</t>
   </si>
   <si>
@@ -1944,19 +1939,25 @@
   </si>
   <si>
     <t>Keystone</t>
+  </si>
+  <si>
+    <t>TVS DIODE 13VWM 21.5VC DO-214AA</t>
+  </si>
+  <si>
+    <t>SMBJ13A</t>
+  </si>
+  <si>
+    <t>TS-1002S-13026C</t>
+  </si>
+  <si>
+    <t>6mm 13mm Round Button 50mA Standing paste 6mm SPST 12V SMD,6x6mm Tactile Switches ROHS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2024,152 +2025,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2188,194 +2045,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2466,251 +2137,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2755,77 +2184,33 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="0003A4CB"/>
-      <color rgb="002CD0B2"/>
+      <color rgb="FF03A4CB"/>
+      <color rgb="FF2CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3083,28 +2468,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="4.57142857142857" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7142857142857" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="23.1428571428571" customWidth="1"/>
-    <col min="7" max="7" width="27.2857142857143" customWidth="1"/>
-    <col min="8" max="8" width="20.8571428571429" customWidth="1"/>
-    <col min="9" max="9" width="8.14285714285714" customWidth="1"/>
-    <col min="10" max="10" width="9.28571428571429" customWidth="1"/>
-    <col min="11" max="11" width="28.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="23.109375" customWidth="1"/>
+    <col min="7" max="7" width="27.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.88671875" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" customWidth="1"/>
+    <col min="11" max="11" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:11">
+    <row r="1" spans="1:11">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3113,11 +2499,11 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-    </row>
-    <row r="2" ht="15.75" spans="1:11">
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -3150,10 +2536,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="1:11">
+    <row r="3" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="7">
-        <f>ROW(B3)-ROW($B$2)</f>
+        <f t="shared" ref="B3:B34" si="0">ROW(B3)-ROW($B$2)</f>
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -3182,10 +2568,10 @@
       </c>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" ht="15.75" spans="1:11">
+    <row r="4" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="7">
-        <f>ROW(B4)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -3214,10 +2600,10 @@
       </c>
       <c r="K4" s="12"/>
     </row>
-    <row r="5" ht="24.75" spans="1:11">
+    <row r="5" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="7">
-        <f>ROW(B5)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -3246,10 +2632,10 @@
       </c>
       <c r="K5" s="9"/>
     </row>
-    <row r="6" ht="48.75" spans="1:11">
+    <row r="6" spans="1:11" ht="48">
       <c r="A6" s="2"/>
       <c r="B6" s="7">
-        <f>ROW(B6)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C6" s="11" t="s">
@@ -3281,7 +2667,7 @@
     <row r="7" spans="1:11">
       <c r="A7" s="2"/>
       <c r="B7" s="7">
-        <f>ROW(B7)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -3310,10 +2696,10 @@
       </c>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" ht="24.75" spans="1:11">
+    <row r="8" spans="1:11" ht="24">
       <c r="A8" s="2"/>
       <c r="B8" s="7">
-        <f>ROW(B8)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -3345,7 +2731,7 @@
     <row r="9" spans="1:11">
       <c r="A9" s="2"/>
       <c r="B9" s="7">
-        <f>ROW(B9)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C9" s="8" t="s">
@@ -3377,7 +2763,7 @@
     <row r="10" spans="1:11">
       <c r="A10" s="2"/>
       <c r="B10" s="7">
-        <f>ROW(B10)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C10" s="8" t="s">
@@ -3409,7 +2795,7 @@
     <row r="11" spans="1:11">
       <c r="A11" s="2"/>
       <c r="B11" s="7">
-        <f>ROW(B11)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C11" s="8" t="s">
@@ -3438,10 +2824,10 @@
       </c>
       <c r="K11" s="9"/>
     </row>
-    <row r="12" ht="24.75" spans="1:11">
+    <row r="12" spans="1:11" ht="24">
       <c r="A12" s="2"/>
       <c r="B12" s="7">
-        <f>ROW(B12)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C12" s="8" t="s">
@@ -3473,7 +2859,7 @@
     <row r="13" spans="1:11">
       <c r="A13" s="2"/>
       <c r="B13" s="7">
-        <f>ROW(B13)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -3505,7 +2891,7 @@
     <row r="14" spans="1:11">
       <c r="A14" s="2"/>
       <c r="B14" s="7">
-        <f>ROW(B14)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C14" s="8" t="s">
@@ -3537,7 +2923,7 @@
     <row r="15" spans="1:11">
       <c r="A15" s="2"/>
       <c r="B15" s="7">
-        <f>ROW(B15)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -3569,7 +2955,7 @@
     <row r="16" spans="1:11">
       <c r="A16" s="2"/>
       <c r="B16" s="7">
-        <f>ROW(B16)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C16" s="8" t="s">
@@ -3601,7 +2987,7 @@
     <row r="17" spans="1:11">
       <c r="A17" s="2"/>
       <c r="B17" s="7">
-        <f>ROW(B17)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C17" s="8" t="s">
@@ -3633,7 +3019,7 @@
     <row r="18" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="7">
-        <f>ROW(B18)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C18" s="8" t="s">
@@ -3665,7 +3051,7 @@
     <row r="19" spans="1:11">
       <c r="A19" s="2"/>
       <c r="B19" s="7">
-        <f>ROW(B19)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C19" s="8" t="s">
@@ -3697,7 +3083,7 @@
     <row r="20" spans="1:11">
       <c r="A20" s="2"/>
       <c r="B20" s="7">
-        <f>ROW(B20)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -3729,7 +3115,7 @@
     <row r="21" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="7">
-        <f>ROW(B21)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C21" s="8" t="s">
@@ -3761,7 +3147,7 @@
     <row r="22" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="7">
-        <f>ROW(B22)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -3793,7 +3179,7 @@
     <row r="23" spans="1:11">
       <c r="A23" s="2"/>
       <c r="B23" s="7">
-        <f>ROW(B23)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C23" s="8" t="s">
@@ -3825,7 +3211,7 @@
     <row r="24" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="7">
-        <f>ROW(B24)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C24" s="8" t="s">
@@ -3857,7 +3243,7 @@
     <row r="25" spans="1:11">
       <c r="A25" s="2"/>
       <c r="B25" s="7">
-        <f>ROW(B25)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -3889,7 +3275,7 @@
     <row r="26" spans="1:11">
       <c r="A26" s="2"/>
       <c r="B26" s="7">
-        <f>ROW(B26)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -3921,7 +3307,7 @@
     <row r="27" spans="1:11">
       <c r="A27" s="2"/>
       <c r="B27" s="7">
-        <f>ROW(B27)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -3953,7 +3339,7 @@
     <row r="28" spans="1:11">
       <c r="A28" s="2"/>
       <c r="B28" s="7">
-        <f>ROW(B28)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -3985,7 +3371,7 @@
     <row r="29" spans="1:11">
       <c r="A29" s="2"/>
       <c r="B29" s="7">
-        <f>ROW(B29)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -4017,7 +3403,7 @@
     <row r="30" spans="1:11">
       <c r="A30" s="2"/>
       <c r="B30" s="7">
-        <f>ROW(B30)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C30" s="8" t="s">
@@ -4046,10 +3432,10 @@
       </c>
       <c r="K30" s="12"/>
     </row>
-    <row r="31" ht="15.75" spans="1:11">
+    <row r="31" spans="1:11">
       <c r="A31" s="2"/>
       <c r="B31" s="7">
-        <f>ROW(B31)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -4078,10 +3464,10 @@
       </c>
       <c r="K31" s="9"/>
     </row>
-    <row r="32" ht="15.75" spans="1:11">
+    <row r="32" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="7">
-        <f>ROW(B32)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C32" s="8" t="s">
@@ -4108,14 +3494,14 @@
       <c r="J32" s="14">
         <v>7</v>
       </c>
-      <c r="K32" s="17" t="s">
+      <c r="K32" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="33" ht="15.75" spans="1:11">
+    <row r="33" spans="1:11">
       <c r="A33" s="2"/>
       <c r="B33" s="7">
-        <f>ROW(B33)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C33" s="8" t="s">
@@ -4142,14 +3528,14 @@
       <c r="J33" s="14">
         <v>1</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="K33" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="34" ht="15.75" spans="1:11">
+    <row r="34" spans="1:11">
       <c r="A34" s="2"/>
       <c r="B34" s="7">
-        <f>ROW(B34)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C34" s="8" t="s">
@@ -4181,7 +3567,7 @@
     <row r="35" spans="1:11">
       <c r="A35" s="2"/>
       <c r="B35" s="7">
-        <f>ROW(B35)-ROW($B$2)</f>
+        <f t="shared" ref="B35:B66" si="1">ROW(B35)-ROW($B$2)</f>
         <v>33</v>
       </c>
       <c r="C35" s="8" t="s">
@@ -4213,7 +3599,7 @@
     <row r="36" spans="1:11">
       <c r="A36" s="2"/>
       <c r="B36" s="7">
-        <f>ROW(B36)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -4242,10 +3628,10 @@
       </c>
       <c r="K36" s="12"/>
     </row>
-    <row r="37" ht="24.75" spans="1:11">
+    <row r="37" spans="1:11" ht="24">
       <c r="A37" s="2"/>
       <c r="B37" s="7">
-        <f>ROW(B37)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -4274,10 +3660,10 @@
       </c>
       <c r="K37" s="9"/>
     </row>
-    <row r="38" ht="24.75" spans="1:11">
+    <row r="38" spans="1:11" ht="24">
       <c r="A38" s="2"/>
       <c r="B38" s="7">
-        <f>ROW(B38)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="C38" s="11" t="s">
@@ -4306,10 +3692,10 @@
       </c>
       <c r="K38" s="12"/>
     </row>
-    <row r="39" ht="15.75" spans="1:11">
+    <row r="39" spans="1:11">
       <c r="A39" s="2"/>
       <c r="B39" s="7">
-        <f>ROW(B39)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -4336,14 +3722,14 @@
       <c r="J39" s="14">
         <v>1</v>
       </c>
-      <c r="K39" s="17" t="s">
+      <c r="K39" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="40" ht="24.75" spans="1:11">
+    <row r="40" spans="1:11" ht="24">
       <c r="A40" s="2"/>
       <c r="B40" s="7">
-        <f>ROW(B40)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -4375,7 +3761,7 @@
     <row r="41" spans="1:11">
       <c r="A41" s="2"/>
       <c r="B41" s="7">
-        <f>ROW(B41)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="C41" s="8" t="s">
@@ -4407,7 +3793,7 @@
     <row r="42" spans="1:11">
       <c r="A42" s="2"/>
       <c r="B42" s="7">
-        <f>ROW(B42)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="C42" s="11" t="s">
@@ -4417,16 +3803,16 @@
         <v>183</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>184</v>
+        <v>635</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>173</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>185</v>
+        <v>636</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I42" s="13" t="s">
         <v>159</v>
@@ -4439,26 +3825,26 @@
     <row r="43" spans="1:11">
       <c r="A43" s="2"/>
       <c r="B43" s="7">
-        <f>ROW(B43)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D43" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F43" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="G43" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="H43" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>159</v>
@@ -4471,26 +3857,26 @@
     <row r="44" spans="1:11">
       <c r="A44" s="2"/>
       <c r="B44" s="7">
-        <f>ROW(B44)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D44" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F44" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="G44" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="F44" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>195</v>
-      </c>
       <c r="H44" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I44" s="13" t="s">
         <v>159</v>
@@ -4500,26 +3886,26 @@
       </c>
       <c r="K44" s="12"/>
     </row>
-    <row r="45" ht="15.75" spans="1:11">
+    <row r="45" spans="1:11">
       <c r="A45" s="2"/>
       <c r="B45" s="7">
-        <f>ROW(B45)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="C45" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E45" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="F45" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="G45" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>15</v>
@@ -4532,20 +3918,20 @@
       </c>
       <c r="K45" s="9"/>
     </row>
-    <row r="46" ht="36.75" spans="1:11">
+    <row r="46" spans="1:11" ht="36">
       <c r="A46" s="2"/>
       <c r="B46" s="7">
-        <f>ROW(B46)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="C46" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="E46" s="13" t="s">
         <v>201</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>203</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>34</v>
@@ -4554,7 +3940,7 @@
         <v>5027740891</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I46" s="13" t="s">
         <v>159</v>
@@ -4564,29 +3950,29 @@
       </c>
       <c r="K46" s="12"/>
     </row>
-    <row r="47" ht="48.75" spans="1:11">
+    <row r="47" spans="1:11" ht="48">
       <c r="A47" s="2"/>
       <c r="B47" s="7">
-        <f>ROW(B47)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="C47" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E47" s="10" t="s">
         <v>205</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>207</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>159</v>
@@ -4596,29 +3982,29 @@
       </c>
       <c r="K47" s="9"/>
     </row>
-    <row r="48" ht="24.75" spans="1:11">
+    <row r="48" spans="1:11" ht="24">
       <c r="A48" s="2"/>
       <c r="B48" s="7">
-        <f>ROW(B48)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="C48" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E48" s="13" t="s">
         <v>210</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>212</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I48" s="13" t="s">
         <v>159</v>
@@ -4628,29 +4014,29 @@
       </c>
       <c r="K48" s="12"/>
     </row>
-    <row r="49" ht="15.75" spans="1:11">
+    <row r="49" spans="1:11">
       <c r="A49" s="2"/>
       <c r="B49" s="7">
-        <f>ROW(B49)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="C49" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>215</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>217</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>159</v>
@@ -4660,29 +4046,29 @@
       </c>
       <c r="K49" s="9"/>
     </row>
-    <row r="50" ht="26.25" spans="1:11">
+    <row r="50" spans="1:11" ht="27.6">
       <c r="A50" s="2"/>
       <c r="B50" s="7">
-        <f>ROW(B50)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>220</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>222</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I50" s="13" t="s">
         <v>159</v>
@@ -4692,29 +4078,29 @@
       </c>
       <c r="K50" s="12"/>
     </row>
-    <row r="51" ht="26.25" spans="1:11">
+    <row r="51" spans="1:11" ht="27.6">
       <c r="A51" s="2"/>
       <c r="B51" s="7">
-        <f>ROW(B51)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="E51" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="D51" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>222</v>
-      </c>
       <c r="F51" s="14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H51" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>136</v>
@@ -4722,33 +4108,33 @@
       <c r="J51" s="14">
         <v>1</v>
       </c>
-      <c r="K51" s="17" t="s">
+      <c r="K51" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="52" ht="26.25" spans="1:11">
+    <row r="52" spans="1:11" ht="27.6">
       <c r="A52" s="2"/>
       <c r="B52" s="7">
-        <f>ROW(B52)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="C52" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>225</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>227</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I52" s="13" t="s">
         <v>159</v>
@@ -4761,61 +4147,61 @@
     <row r="53" spans="1:11">
       <c r="A53" s="2"/>
       <c r="B53" s="7">
-        <f>ROW(B53)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="C53" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E53" s="13" t="s">
         <v>230</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>232</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G53" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="I53" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="H53" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>235</v>
-      </c>
       <c r="J53" s="12">
         <v>1</v>
       </c>
       <c r="K53" s="12"/>
     </row>
-    <row r="54" ht="24.75" spans="1:11">
+    <row r="54" spans="1:11" ht="24">
       <c r="A54" s="2"/>
       <c r="B54" s="7">
-        <f>ROW(B54)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="C54" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E54" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>238</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G54" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="I54" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="J54" s="9">
         <v>3</v>
@@ -4825,87 +4211,87 @@
     <row r="55" spans="1:11">
       <c r="A55" s="2"/>
       <c r="B55" s="7">
-        <f>ROW(B55)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J55" s="12">
         <v>1</v>
       </c>
       <c r="K55" s="12"/>
     </row>
-    <row r="56" ht="24.75" spans="1:11">
+    <row r="56" spans="1:11" ht="24">
       <c r="A56" s="2"/>
       <c r="B56" s="7">
-        <f>ROW(B56)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G56" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="I56" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="H56" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>250</v>
-      </c>
       <c r="J56" s="9">
         <v>1</v>
       </c>
       <c r="K56" s="9"/>
     </row>
-    <row r="57" ht="15.75" spans="1:11">
+    <row r="57" spans="1:11">
       <c r="A57" s="2"/>
       <c r="B57" s="7">
-        <f>ROW(B57)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D57" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="G57" s="15" t="s">
         <v>251</v>
-      </c>
-      <c r="E57" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="F57" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="G57" s="15" t="s">
-        <v>253</v>
       </c>
       <c r="H57" s="14" t="s">
         <v>15</v>
@@ -4916,65 +4302,65 @@
       <c r="J57" s="14">
         <v>1</v>
       </c>
-      <c r="K57" s="17" t="s">
+      <c r="K57" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="58" ht="24.75" spans="1:11">
+    <row r="58" spans="1:11" ht="24">
       <c r="A58" s="2"/>
       <c r="B58" s="7">
-        <f>ROW(B58)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G58" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="I58" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="H58" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>258</v>
-      </c>
       <c r="J58" s="9">
         <v>1</v>
       </c>
       <c r="K58" s="9"/>
     </row>
-    <row r="59" ht="24.75" spans="1:11">
+    <row r="59" spans="1:11">
       <c r="A59" s="2"/>
       <c r="B59" s="7">
-        <f>ROW(B59)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="C59" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E59" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="F59" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="E59" s="13" t="s">
+      <c r="G59" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="F59" s="12" t="s">
+      <c r="H59" s="12" t="s">
         <v>262</v>
-      </c>
-      <c r="G59" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>264</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>159</v>
@@ -4984,29 +4370,29 @@
       </c>
       <c r="K59" s="12"/>
     </row>
-    <row r="60" ht="24.75" spans="1:11">
+    <row r="60" spans="1:11" ht="24">
       <c r="A60" s="2"/>
       <c r="B60" s="7">
-        <f>ROW(B60)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D60" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F60" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="G60" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="H60" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="I60" s="13" t="s">
         <v>159</v>
@@ -5016,29 +4402,29 @@
       </c>
       <c r="K60" s="9"/>
     </row>
-    <row r="61" ht="24.75" spans="1:11">
+    <row r="61" spans="1:11" ht="24">
       <c r="A61" s="2"/>
       <c r="B61" s="7">
-        <f>ROW(B61)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D61" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="F61" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="E61" s="13" t="s">
+      <c r="G61" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="H61" s="12" t="s">
         <v>272</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="H61" s="12" t="s">
-        <v>274</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>159</v>
@@ -5051,26 +4437,26 @@
     <row r="62" spans="1:11">
       <c r="A62" s="2"/>
       <c r="B62" s="7">
-        <f>ROW(B62)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D62" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="G62" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="F62" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>278</v>
-      </c>
       <c r="H62" s="9" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I62" s="13" t="s">
         <v>159</v>
@@ -5080,29 +4466,29 @@
       </c>
       <c r="K62" s="9"/>
     </row>
-    <row r="63" ht="24.75" spans="1:11">
+    <row r="63" spans="1:11" ht="24">
       <c r="A63" s="2"/>
       <c r="B63" s="7">
-        <f>ROW(B63)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D63" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G63" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="E63" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="F63" s="12" t="s">
+      <c r="H63" s="12" t="s">
         <v>267</v>
-      </c>
-      <c r="G63" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="H63" s="12" t="s">
-        <v>269</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>159</v>
@@ -5112,29 +4498,29 @@
       </c>
       <c r="K63" s="12"/>
     </row>
-    <row r="64" ht="36.75" spans="1:11">
+    <row r="64" spans="1:11" ht="36">
       <c r="A64" s="2"/>
       <c r="B64" s="7">
-        <f>ROW(B64)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="C64" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="E64" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>284</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I64" s="13" t="s">
         <v>159</v>
@@ -5144,26 +4530,26 @@
       </c>
       <c r="K64" s="9"/>
     </row>
-    <row r="65" ht="15.75" spans="1:11">
+    <row r="65" spans="1:11">
       <c r="A65" s="2"/>
       <c r="B65" s="7">
-        <f>ROW(B65)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="C65" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E65" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="F65" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="E65" s="13" t="s">
+      <c r="G65" s="13" t="s">
         <v>289</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="G65" s="13" t="s">
-        <v>291</v>
       </c>
       <c r="H65" s="12" t="s">
         <v>170</v>
@@ -5179,26 +4565,26 @@
     <row r="66" spans="1:11">
       <c r="A66" s="2"/>
       <c r="B66" s="7">
-        <f>ROW(B66)-ROW($B$2)</f>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D66" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="F66" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="G66" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="H66" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="I66" s="13" t="s">
         <v>159</v>
@@ -5208,29 +4594,29 @@
       </c>
       <c r="K66" s="9"/>
     </row>
-    <row r="67" ht="24.75" spans="1:11">
+    <row r="67" spans="1:11" ht="24">
       <c r="A67" s="2"/>
       <c r="B67" s="7">
-        <f>ROW(B67)-ROW($B$2)</f>
+        <f t="shared" ref="B67:B98" si="2">ROW(B67)-ROW($B$2)</f>
         <v>65</v>
       </c>
       <c r="C67" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="E67" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="F67" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="G67" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="E67" s="13" t="s">
+      <c r="H67" s="12" t="s">
         <v>299</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="G67" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="H67" s="12" t="s">
-        <v>301</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>159</v>
@@ -5243,29 +4629,29 @@
     <row r="68" spans="1:11">
       <c r="A68" s="2"/>
       <c r="B68" s="7">
-        <f>ROW(B68)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>66</v>
       </c>
       <c r="C68" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E68" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="D68" s="9" t="s">
+      <c r="F68" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="G68" s="10" t="s">
         <v>304</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>306</v>
       </c>
       <c r="H68" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="J68" s="9">
         <v>7</v>
@@ -5275,29 +4661,29 @@
     <row r="69" spans="1:11">
       <c r="A69" s="2"/>
       <c r="B69" s="7">
-        <f>ROW(B69)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>67</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D69" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="G69" s="13" t="s">
         <v>308</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="G69" s="13" t="s">
-        <v>310</v>
       </c>
       <c r="H69" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J69" s="12">
         <v>1</v>
@@ -5307,285 +4693,285 @@
     <row r="70" spans="1:11">
       <c r="A70" s="2"/>
       <c r="B70" s="7">
-        <f>ROW(B70)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="C70" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="E70" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="D70" s="9" t="s">
+      <c r="F70" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G70" s="10" t="s">
         <v>313</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>315</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J70" s="9">
         <v>1</v>
       </c>
       <c r="K70" s="9"/>
     </row>
-    <row r="71" ht="15.75" spans="1:11">
+    <row r="71" spans="1:11">
       <c r="A71" s="2"/>
       <c r="B71" s="7">
-        <f>ROW(B71)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D71" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="G71" s="13" t="s">
         <v>317</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="F71" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="G71" s="13" t="s">
-        <v>319</v>
       </c>
       <c r="H71" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J71" s="12">
         <v>1</v>
       </c>
       <c r="K71" s="12"/>
     </row>
-    <row r="72" ht="15.75" spans="1:11">
+    <row r="72" spans="1:11">
       <c r="A72" s="2"/>
       <c r="B72" s="7">
-        <f>ROW(B72)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D72" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G72" s="10" t="s">
         <v>321</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>323</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J72" s="9">
         <v>1</v>
       </c>
       <c r="K72" s="9"/>
     </row>
-    <row r="73" ht="15.75" spans="1:11">
+    <row r="73" spans="1:11">
       <c r="A73" s="2"/>
       <c r="B73" s="7">
-        <f>ROW(B73)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>71</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D73" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="F73" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="E73" s="13" t="s">
+      <c r="G73" s="13" t="s">
         <v>326</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G73" s="13" t="s">
-        <v>328</v>
       </c>
       <c r="H73" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J73" s="12">
         <v>1</v>
       </c>
       <c r="K73" s="12"/>
     </row>
-    <row r="74" ht="15.75" spans="1:11">
+    <row r="74" spans="1:11">
       <c r="A74" s="2"/>
       <c r="B74" s="7">
-        <f>ROW(B74)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D74" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G74" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="H74" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J74" s="9">
         <v>1</v>
       </c>
       <c r="K74" s="9"/>
     </row>
-    <row r="75" ht="15.75" spans="1:11">
+    <row r="75" spans="1:11">
       <c r="A75" s="2"/>
       <c r="B75" s="7">
-        <f>ROW(B75)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D75" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="G75" s="13" t="s">
         <v>334</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="F75" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="G75" s="13" t="s">
-        <v>336</v>
       </c>
       <c r="H75" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J75" s="12">
         <v>1</v>
       </c>
       <c r="K75" s="12"/>
     </row>
-    <row r="76" ht="15.75" spans="1:11">
+    <row r="76" spans="1:11">
       <c r="A76" s="2"/>
       <c r="B76" s="7">
-        <f>ROW(B76)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>74</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D76" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G76" s="10" t="s">
         <v>338</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>340</v>
       </c>
       <c r="H76" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J76" s="9">
         <v>1</v>
       </c>
       <c r="K76" s="9"/>
     </row>
-    <row r="77" ht="15.75" spans="1:11">
+    <row r="77" spans="1:11">
       <c r="A77" s="2"/>
       <c r="B77" s="7">
-        <f>ROW(B77)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D77" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="G77" s="13" t="s">
         <v>341</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="G77" s="13" t="s">
-        <v>343</v>
       </c>
       <c r="H77" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J77" s="12">
         <v>1</v>
       </c>
       <c r="K77" s="12"/>
     </row>
-    <row r="78" ht="15.75" spans="1:11">
+    <row r="78" spans="1:11">
       <c r="A78" s="2"/>
       <c r="B78" s="7">
-        <f>ROW(B78)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>76</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D78" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G78" s="10" t="s">
         <v>345</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>347</v>
       </c>
       <c r="H78" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J78" s="9">
         <v>1</v>
@@ -5595,375 +4981,375 @@
     <row r="79" spans="1:11">
       <c r="A79" s="2"/>
       <c r="B79" s="7">
-        <f>ROW(B79)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D79" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="G79" s="13" t="s">
         <v>349</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="F79" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="G79" s="13" t="s">
-        <v>351</v>
       </c>
       <c r="H79" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J79" s="12">
         <v>6</v>
       </c>
       <c r="K79" s="12"/>
     </row>
-    <row r="80" ht="15.75" spans="1:11">
+    <row r="80" spans="1:11">
       <c r="A80" s="2"/>
       <c r="B80" s="7">
-        <f>ROW(B80)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>78</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D80" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G80" s="10" t="s">
         <v>353</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>355</v>
       </c>
       <c r="H80" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J80" s="9">
         <v>1</v>
       </c>
       <c r="K80" s="9"/>
     </row>
-    <row r="81" ht="24.75" spans="1:11">
+    <row r="81" spans="1:11" ht="24">
       <c r="A81" s="2"/>
       <c r="B81" s="7">
-        <f>ROW(B81)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>79</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D81" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="G81" s="13" t="s">
         <v>357</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="G81" s="13" t="s">
-        <v>359</v>
       </c>
       <c r="H81" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J81" s="12">
         <v>18</v>
       </c>
       <c r="K81" s="12"/>
     </row>
-    <row r="82" ht="15.75" spans="1:11">
+    <row r="82" spans="1:11">
       <c r="A82" s="2"/>
       <c r="B82" s="7">
-        <f>ROW(B82)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D82" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G82" s="10" t="s">
         <v>361</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>363</v>
       </c>
       <c r="H82" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J82" s="9">
         <v>2</v>
       </c>
       <c r="K82" s="9"/>
     </row>
-    <row r="83" ht="15.75" spans="1:11">
+    <row r="83" spans="1:11">
       <c r="A83" s="2"/>
       <c r="B83" s="7">
-        <f>ROW(B83)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D83" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="G83" s="13" t="s">
         <v>365</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="F83" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="G83" s="13" t="s">
-        <v>367</v>
       </c>
       <c r="H83" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J83" s="12">
         <v>1</v>
       </c>
       <c r="K83" s="12"/>
     </row>
-    <row r="84" ht="15.75" spans="1:11">
+    <row r="84" spans="1:11">
       <c r="A84" s="2"/>
       <c r="B84" s="7">
-        <f>ROW(B84)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D84" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G84" s="10" t="s">
         <v>369</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>371</v>
       </c>
       <c r="H84" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J84" s="9">
         <v>1</v>
       </c>
       <c r="K84" s="9"/>
     </row>
-    <row r="85" ht="24.75" spans="1:11">
+    <row r="85" spans="1:11">
       <c r="A85" s="2"/>
       <c r="B85" s="7">
-        <f>ROW(B85)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>83</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D85" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G85" s="13" t="s">
         <v>373</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G85" s="13" t="s">
-        <v>375</v>
       </c>
       <c r="H85" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J85" s="12">
         <v>10</v>
       </c>
       <c r="K85" s="12"/>
     </row>
-    <row r="86" ht="15.75" spans="1:11">
+    <row r="86" spans="1:11">
       <c r="A86" s="2"/>
       <c r="B86" s="7">
-        <f>ROW(B86)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D86" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G86" s="10" t="s">
         <v>376</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>378</v>
       </c>
       <c r="H86" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J86" s="9">
         <v>1</v>
       </c>
       <c r="K86" s="9"/>
     </row>
-    <row r="87" ht="15.75" spans="1:11">
+    <row r="87" spans="1:11">
       <c r="A87" s="2"/>
       <c r="B87" s="7">
-        <f>ROW(B87)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>85</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D87" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G87" s="13" t="s">
         <v>380</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="F87" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G87" s="13" t="s">
-        <v>382</v>
       </c>
       <c r="H87" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J87" s="12">
         <v>1</v>
       </c>
       <c r="K87" s="12"/>
     </row>
-    <row r="88" ht="15.75" spans="1:11">
+    <row r="88" spans="1:11">
       <c r="A88" s="2"/>
       <c r="B88" s="7">
-        <f>ROW(B88)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D88" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G88" s="10" t="s">
         <v>384</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>386</v>
       </c>
       <c r="H88" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J88" s="9">
         <v>1</v>
       </c>
       <c r="K88" s="9"/>
     </row>
-    <row r="89" ht="15.75" spans="1:11">
+    <row r="89" spans="1:11">
       <c r="A89" s="2"/>
       <c r="B89" s="7">
-        <f>ROW(B89)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D89" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G89" s="13" t="s">
         <v>388</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="F89" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G89" s="13" t="s">
-        <v>390</v>
       </c>
       <c r="H89" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J89" s="12">
         <v>1</v>
       </c>
       <c r="K89" s="12"/>
     </row>
-    <row r="90" ht="15.75" spans="1:11">
+    <row r="90" spans="1:11">
       <c r="A90" s="2"/>
       <c r="B90" s="7">
-        <f>ROW(B90)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>88</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H90" s="14" t="s">
         <v>74</v>
@@ -5974,100 +5360,100 @@
       <c r="J90" s="14">
         <v>4</v>
       </c>
-      <c r="K90" s="17" t="s">
+      <c r="K90" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="91" ht="15.75" spans="1:11">
+    <row r="91" spans="1:11">
       <c r="A91" s="2"/>
       <c r="B91" s="7">
-        <f>ROW(B91)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>89</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D91" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G91" s="13" t="s">
         <v>393</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="F91" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G91" s="13" t="s">
-        <v>395</v>
       </c>
       <c r="H91" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J91" s="12">
         <v>1</v>
       </c>
       <c r="K91" s="12"/>
     </row>
-    <row r="92" ht="15.75" spans="1:11">
+    <row r="92" spans="1:11">
       <c r="A92" s="2"/>
       <c r="B92" s="7">
-        <f>ROW(B92)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D92" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G92" s="10" t="s">
         <v>397</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>399</v>
       </c>
       <c r="H92" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J92" s="9">
         <v>7</v>
       </c>
       <c r="K92" s="9"/>
     </row>
-    <row r="93" ht="24.75" spans="1:11">
+    <row r="93" spans="1:11">
       <c r="A93" s="2"/>
       <c r="B93" s="7">
-        <f>ROW(B93)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>91</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D93" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G93" s="13" t="s">
         <v>400</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="F93" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G93" s="13" t="s">
-        <v>402</v>
       </c>
       <c r="H93" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J93" s="12">
         <v>9</v>
@@ -6077,29 +5463,29 @@
     <row r="94" spans="1:11">
       <c r="A94" s="2"/>
       <c r="B94" s="7">
-        <f>ROW(B94)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D94" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G94" s="10" t="s">
         <v>404</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>406</v>
       </c>
       <c r="H94" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J94" s="9">
         <v>5</v>
@@ -6109,29 +5495,29 @@
     <row r="95" spans="1:11">
       <c r="A95" s="2"/>
       <c r="B95" s="7">
-        <f>ROW(B95)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>93</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D95" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G95" s="13" t="s">
         <v>407</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="F95" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G95" s="13" t="s">
-        <v>409</v>
       </c>
       <c r="H95" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J95" s="12">
         <v>1</v>
@@ -6141,25 +5527,25 @@
     <row r="96" spans="1:11">
       <c r="A96" s="2"/>
       <c r="B96" s="7">
-        <f>ROW(B96)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>94</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G96" s="10"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J96" s="9">
         <v>2</v>
@@ -6169,221 +5555,221 @@
     <row r="97" spans="1:11">
       <c r="A97" s="2"/>
       <c r="B97" s="7">
-        <f>ROW(B97)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D97" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="F97" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G97" s="13" t="s">
         <v>414</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>415</v>
-      </c>
-      <c r="F97" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G97" s="13" t="s">
-        <v>416</v>
       </c>
       <c r="H97" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J97" s="12">
         <v>1</v>
       </c>
       <c r="K97" s="12"/>
     </row>
-    <row r="98" ht="15.75" spans="1:11">
+    <row r="98" spans="1:11">
       <c r="A98" s="2"/>
       <c r="B98" s="7">
-        <f>ROW(B98)-ROW($B$2)</f>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D98" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G98" s="10" t="s">
         <v>418</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>420</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J98" s="9">
         <v>1</v>
       </c>
       <c r="K98" s="9"/>
     </row>
-    <row r="99" ht="15.75" spans="1:11">
+    <row r="99" spans="1:11">
       <c r="A99" s="2"/>
       <c r="B99" s="7">
-        <f>ROW(B99)-ROW($B$2)</f>
+        <f t="shared" ref="B99:B130" si="3">ROW(B99)-ROW($B$2)</f>
         <v>97</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D99" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G99" s="13" t="s">
         <v>422</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="F99" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G99" s="13" t="s">
-        <v>424</v>
       </c>
       <c r="H99" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J99" s="12">
         <v>1</v>
       </c>
       <c r="K99" s="12"/>
     </row>
-    <row r="100" ht="15.75" spans="1:11">
+    <row r="100" spans="1:11">
       <c r="A100" s="2"/>
       <c r="B100" s="7">
-        <f>ROW(B100)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>98</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D100" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G100" s="10" t="s">
         <v>426</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G100" s="10" t="s">
-        <v>428</v>
       </c>
       <c r="H100" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J100" s="9">
         <v>1</v>
       </c>
       <c r="K100" s="9"/>
     </row>
-    <row r="101" ht="15.75" spans="1:11">
+    <row r="101" spans="1:11">
       <c r="A101" s="2"/>
       <c r="B101" s="7">
-        <f>ROW(B101)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>99</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D101" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="F101" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="G101" s="13" t="s">
         <v>430</v>
-      </c>
-      <c r="E101" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="F101" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="G101" s="13" t="s">
-        <v>432</v>
       </c>
       <c r="H101" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J101" s="12">
         <v>1</v>
       </c>
       <c r="K101" s="12"/>
     </row>
-    <row r="102" ht="15.75" spans="1:11">
+    <row r="102" spans="1:11">
       <c r="A102" s="2"/>
       <c r="B102" s="7">
-        <f>ROW(B102)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D102" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G102" s="10" t="s">
         <v>434</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G102" s="10" t="s">
-        <v>436</v>
       </c>
       <c r="H102" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J102" s="9">
         <v>1</v>
       </c>
       <c r="K102" s="9"/>
     </row>
-    <row r="103" ht="15.75" spans="1:11">
+    <row r="103" spans="1:11">
       <c r="A103" s="2"/>
       <c r="B103" s="7">
-        <f>ROW(B103)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>101</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D103" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="F103" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G103" s="13" t="s">
         <v>438</v>
-      </c>
-      <c r="E103" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="F103" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G103" s="13" t="s">
-        <v>440</v>
       </c>
       <c r="H103" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J103" s="12">
         <v>3</v>
@@ -6393,29 +5779,29 @@
     <row r="104" spans="1:11">
       <c r="A104" s="2"/>
       <c r="B104" s="7">
-        <f>ROW(B104)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>102</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D104" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G104" s="10" t="s">
         <v>442</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>444</v>
       </c>
       <c r="H104" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J104" s="9">
         <v>8</v>
@@ -6425,29 +5811,29 @@
     <row r="105" spans="1:11">
       <c r="A105" s="2"/>
       <c r="B105" s="7">
-        <f>ROW(B105)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D105" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G105" s="13" t="s">
         <v>446</v>
-      </c>
-      <c r="E105" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="F105" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G105" s="13" t="s">
-        <v>448</v>
       </c>
       <c r="H105" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J105" s="12">
         <v>1</v>
@@ -6457,87 +5843,87 @@
     <row r="106" spans="1:11">
       <c r="A106" s="2"/>
       <c r="B106" s="7">
-        <f>ROW(B106)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>104</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D106" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G106" s="10" t="s">
         <v>450</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="F106" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G106" s="10" t="s">
-        <v>452</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J106" s="9">
         <v>1</v>
       </c>
       <c r="K106" s="9"/>
     </row>
-    <row r="107" ht="15.75" spans="1:11">
+    <row r="107" spans="1:11">
       <c r="A107" s="2"/>
       <c r="B107" s="7">
-        <f>ROW(B107)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>105</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D107" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="E107" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G107" s="13" t="s">
         <v>454</v>
-      </c>
-      <c r="E107" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="F107" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G107" s="13" t="s">
-        <v>456</v>
       </c>
       <c r="H107" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J107" s="12">
         <v>1</v>
       </c>
       <c r="K107" s="12"/>
     </row>
-    <row r="108" ht="15.75" spans="1:11">
+    <row r="108" spans="1:11">
       <c r="A108" s="2"/>
       <c r="B108" s="7">
-        <f>ROW(B108)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>106</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H108" s="14" t="s">
         <v>74</v>
@@ -6548,190 +5934,190 @@
       <c r="J108" s="14">
         <v>1</v>
       </c>
-      <c r="K108" s="17" t="s">
+      <c r="K108" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="109" ht="15.75" spans="1:11">
+    <row r="109" spans="1:11">
       <c r="A109" s="2"/>
       <c r="B109" s="7">
-        <f>ROW(B109)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D109" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G109" s="13" t="s">
         <v>459</v>
-      </c>
-      <c r="E109" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="F109" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G109" s="13" t="s">
-        <v>461</v>
       </c>
       <c r="H109" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J109" s="12">
         <v>1</v>
       </c>
       <c r="K109" s="12"/>
     </row>
-    <row r="110" ht="36.75" spans="1:11">
+    <row r="110" spans="1:11" ht="36">
       <c r="A110" s="2"/>
       <c r="B110" s="7">
-        <f>ROW(B110)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>108</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D110" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G110" s="10" t="s">
         <v>463</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>464</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G110" s="10" t="s">
-        <v>465</v>
       </c>
       <c r="H110" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J110" s="9">
         <v>1</v>
       </c>
       <c r="K110" s="9"/>
     </row>
-    <row r="111" ht="15.75" spans="1:11">
+    <row r="111" spans="1:11">
       <c r="A111" s="2"/>
       <c r="B111" s="7">
-        <f>ROW(B111)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>109</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D111" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G111" s="13" t="s">
         <v>467</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>468</v>
-      </c>
-      <c r="F111" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G111" s="13" t="s">
-        <v>469</v>
       </c>
       <c r="H111" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J111" s="12">
         <v>1</v>
       </c>
       <c r="K111" s="12"/>
     </row>
-    <row r="112" ht="15.75" spans="1:11">
+    <row r="112" spans="1:11">
       <c r="A112" s="2"/>
       <c r="B112" s="7">
-        <f>ROW(B112)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>110</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D112" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G112" s="10" t="s">
         <v>471</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G112" s="10" t="s">
-        <v>473</v>
       </c>
       <c r="H112" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="J112" s="9">
         <v>1</v>
       </c>
       <c r="K112" s="9"/>
     </row>
-    <row r="113" ht="15.75" spans="1:11">
+    <row r="113" spans="1:11">
       <c r="A113" s="2"/>
       <c r="B113" s="7">
-        <f>ROW(B113)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>111</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D113" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G113" s="13" t="s">
         <v>475</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>476</v>
-      </c>
-      <c r="F113" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G113" s="13" t="s">
-        <v>477</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J113" s="12">
         <v>1</v>
       </c>
       <c r="K113" s="12"/>
     </row>
-    <row r="114" ht="15.75" spans="1:11">
+    <row r="114" spans="1:11">
       <c r="A114" s="2"/>
       <c r="B114" s="7">
-        <f>ROW(B114)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>112</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H114" s="14" t="s">
         <v>74</v>
@@ -6742,62 +6128,62 @@
       <c r="J114" s="14">
         <v>1</v>
       </c>
-      <c r="K114" s="17" t="s">
+      <c r="K114" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="115" ht="15.75" spans="1:11">
+    <row r="115" spans="1:11">
       <c r="A115" s="2"/>
       <c r="B115" s="7">
-        <f>ROW(B115)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>113</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D115" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G115" s="13" t="s">
         <v>479</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G115" s="13" t="s">
-        <v>481</v>
       </c>
       <c r="H115" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="J115" s="12">
         <v>1</v>
       </c>
       <c r="K115" s="12"/>
     </row>
-    <row r="116" ht="15.75" spans="1:11">
+    <row r="116" spans="1:11">
       <c r="A116" s="2"/>
       <c r="B116" s="7">
-        <f>ROW(B116)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>114</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H116" s="14" t="s">
         <v>74</v>
@@ -6808,94 +6194,94 @@
       <c r="J116" s="14">
         <v>1</v>
       </c>
-      <c r="K116" s="17" t="s">
+      <c r="K116" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="117" ht="15.75" spans="1:11">
+    <row r="117" spans="1:11">
       <c r="A117" s="2"/>
       <c r="B117" s="7">
-        <f>ROW(B117)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>115</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D117" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G117" s="13" t="s">
         <v>483</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="F117" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G117" s="13" t="s">
-        <v>485</v>
       </c>
       <c r="H117" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J117" s="12">
         <v>4</v>
       </c>
       <c r="K117" s="12"/>
     </row>
-    <row r="118" ht="15.75" spans="1:11">
+    <row r="118" spans="1:11">
       <c r="A118" s="2"/>
       <c r="B118" s="7">
-        <f>ROW(B118)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>116</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D118" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="G118" s="10" t="s">
         <v>487</v>
-      </c>
-      <c r="E118" s="10" t="s">
-        <v>488</v>
-      </c>
-      <c r="F118" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G118" s="10" t="s">
-        <v>489</v>
       </c>
       <c r="H118" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J118" s="9">
         <v>1</v>
       </c>
       <c r="K118" s="9"/>
     </row>
-    <row r="119" ht="15.75" spans="1:11">
+    <row r="119" spans="1:11">
       <c r="A119" s="2"/>
       <c r="B119" s="7">
-        <f>ROW(B119)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>117</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F119" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G119" s="15" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H119" s="14" t="s">
         <v>74</v>
@@ -6906,30 +6292,30 @@
       <c r="J119" s="14">
         <v>1</v>
       </c>
-      <c r="K119" s="17" t="s">
+      <c r="K119" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="120" ht="15.75" spans="1:11">
+    <row r="120" spans="1:11">
       <c r="A120" s="2"/>
       <c r="B120" s="7">
-        <f>ROW(B120)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>118</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F120" s="14" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G120" s="15" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H120" s="14" t="s">
         <v>74</v>
@@ -6940,36 +6326,36 @@
       <c r="J120" s="14">
         <v>1</v>
       </c>
-      <c r="K120" s="17" t="s">
+      <c r="K120" s="16" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="121" ht="15.75" spans="1:11">
+    <row r="121" spans="1:11">
       <c r="A121" s="2"/>
       <c r="B121" s="7">
-        <f>ROW(B121)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>119</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D121" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G121" s="10" t="s">
         <v>492</v>
-      </c>
-      <c r="E121" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="G121" s="10" t="s">
-        <v>494</v>
       </c>
       <c r="H121" s="9" t="s">
         <v>74</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J121" s="9">
         <v>1</v>
@@ -6979,26 +6365,26 @@
     <row r="122" spans="1:11">
       <c r="A122" s="2"/>
       <c r="B122" s="7">
-        <f>ROW(B122)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="C122" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="E122" s="13" t="s">
         <v>496</v>
-      </c>
-      <c r="D122" s="12" t="s">
-        <v>497</v>
-      </c>
-      <c r="E122" s="13" t="s">
-        <v>498</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G122" s="13" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I122" s="13" t="s">
         <v>159</v>
@@ -7008,29 +6394,29 @@
       </c>
       <c r="K122" s="12"/>
     </row>
-    <row r="123" ht="48.75" spans="1:11">
+    <row r="123" spans="1:11" ht="48">
       <c r="A123" s="2"/>
       <c r="B123" s="7">
-        <f>ROW(B123)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>121</v>
       </c>
       <c r="C123" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="E123" s="10" t="s">
         <v>501</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>503</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>159</v>
@@ -7040,29 +6426,29 @@
       </c>
       <c r="K123" s="9"/>
     </row>
-    <row r="124" ht="36.75" spans="1:11">
+    <row r="124" spans="1:11" ht="36">
       <c r="A124" s="2"/>
       <c r="B124" s="7">
-        <f>ROW(B124)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>122</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>507</v>
+        <v>638</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G124" s="13" t="s">
-        <v>508</v>
+        <v>637</v>
       </c>
       <c r="H124" s="12" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="I124" s="13" t="s">
         <v>159</v>
@@ -7072,29 +6458,29 @@
       </c>
       <c r="K124" s="12"/>
     </row>
-    <row r="125" ht="24.75" spans="1:11">
+    <row r="125" spans="1:11" ht="24">
       <c r="A125" s="2"/>
       <c r="B125" s="7">
-        <f>ROW(B125)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>123</v>
       </c>
       <c r="C125" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="G125" s="10" t="s">
         <v>509</v>
       </c>
-      <c r="D125" s="9" t="s">
+      <c r="H125" s="9" t="s">
         <v>510</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="G125" s="10" t="s">
-        <v>513</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>514</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>159</v>
@@ -7107,26 +6493,26 @@
     <row r="126" spans="1:11">
       <c r="A126" s="2"/>
       <c r="B126" s="7">
-        <f>ROW(B126)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>124</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D126" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="E126" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="F126" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="G126" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="H126" s="12" t="s">
         <v>515</v>
-      </c>
-      <c r="E126" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="F126" s="12" t="s">
-        <v>517</v>
-      </c>
-      <c r="G126" s="13" t="s">
-        <v>518</v>
-      </c>
-      <c r="H126" s="12" t="s">
-        <v>519</v>
       </c>
       <c r="I126" s="13" t="s">
         <v>159</v>
@@ -7139,26 +6525,26 @@
     <row r="127" spans="1:11">
       <c r="A127" s="2"/>
       <c r="B127" s="7">
-        <f>ROW(B127)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>125</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D127" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="G127" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="H127" s="9" t="s">
         <v>520</v>
-      </c>
-      <c r="E127" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="F127" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="G127" s="10" t="s">
-        <v>523</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>524</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>159</v>
@@ -7168,29 +6554,29 @@
       </c>
       <c r="K127" s="9"/>
     </row>
-    <row r="128" ht="24.75" spans="1:11">
+    <row r="128" spans="1:11" ht="24">
       <c r="A128" s="2"/>
       <c r="B128" s="7">
-        <f>ROW(B128)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>126</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D128" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="F128" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="G128" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="H128" s="12" t="s">
         <v>525</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="F128" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="G128" s="13" t="s">
-        <v>528</v>
-      </c>
-      <c r="H128" s="12" t="s">
-        <v>529</v>
       </c>
       <c r="I128" s="13" t="s">
         <v>159</v>
@@ -7203,26 +6589,26 @@
     <row r="129" spans="1:11">
       <c r="A129" s="2"/>
       <c r="B129" s="7">
-        <f>ROW(B129)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>127</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F129" s="9" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>159</v>
@@ -7235,26 +6621,26 @@
     <row r="130" spans="1:11">
       <c r="A130" s="2"/>
       <c r="B130" s="7">
-        <f>ROW(B130)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>128</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="G130" s="13" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="H130" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I130" s="13" t="s">
         <v>159</v>
@@ -7267,26 +6653,26 @@
     <row r="131" spans="1:11">
       <c r="A131" s="2"/>
       <c r="B131" s="7">
-        <f>ROW(B131)-ROW($B$2)</f>
+        <f t="shared" ref="B131:B154" si="4">ROW(B131)-ROW($B$2)</f>
         <v>129</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>159</v>
@@ -7299,26 +6685,26 @@
     <row r="132" spans="1:11">
       <c r="A132" s="2"/>
       <c r="B132" s="7">
-        <f>ROW(B132)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>130</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F132" s="12" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G132" s="13" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H132" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I132" s="13" t="s">
         <v>159</v>
@@ -7331,26 +6717,26 @@
     <row r="133" spans="1:11">
       <c r="A133" s="2"/>
       <c r="B133" s="7">
-        <f>ROW(B133)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>131</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>159</v>
@@ -7363,26 +6749,26 @@
     <row r="134" spans="1:11">
       <c r="A134" s="2"/>
       <c r="B134" s="7">
-        <f>ROW(B134)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>132</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I134" s="13" t="s">
         <v>159</v>
@@ -7392,29 +6778,29 @@
       </c>
       <c r="K134" s="12"/>
     </row>
-    <row r="135" ht="24.75" spans="1:11">
+    <row r="135" spans="1:11">
       <c r="A135" s="2"/>
       <c r="B135" s="7">
-        <f>ROW(B135)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>133</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D135" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>554</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>555</v>
-      </c>
-      <c r="F135" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="G135" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>558</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>159</v>
@@ -7427,26 +6813,26 @@
     <row r="136" spans="1:11">
       <c r="A136" s="2"/>
       <c r="B136" s="7">
-        <f>ROW(B136)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>134</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F136" s="12" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I136" s="13" t="s">
         <v>159</v>
@@ -7456,29 +6842,29 @@
       </c>
       <c r="K136" s="12"/>
     </row>
-    <row r="137" ht="15.75" spans="1:11">
+    <row r="137" spans="1:11">
       <c r="A137" s="2"/>
       <c r="B137" s="7">
-        <f>ROW(B137)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>135</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I137" s="13" t="s">
         <v>159</v>
@@ -7488,29 +6874,29 @@
       </c>
       <c r="K137" s="9"/>
     </row>
-    <row r="138" ht="24.75" spans="1:11">
+    <row r="138" spans="1:11">
       <c r="A138" s="2"/>
       <c r="B138" s="7">
-        <f>ROW(B138)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>136</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="H138" s="12" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I138" s="13" t="s">
         <v>159</v>
@@ -7520,29 +6906,29 @@
       </c>
       <c r="K138" s="12"/>
     </row>
-    <row r="139" ht="15.75" spans="1:11">
+    <row r="139" spans="1:11">
       <c r="A139" s="2"/>
       <c r="B139" s="7">
-        <f>ROW(B139)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>137</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I139" s="13" t="s">
         <v>159</v>
@@ -7555,26 +6941,26 @@
     <row r="140" spans="1:11">
       <c r="A140" s="2"/>
       <c r="B140" s="7">
-        <f>ROW(B140)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>138</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="F140" s="12" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="H140" s="12" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="I140" s="13" t="s">
         <v>159</v>
@@ -7584,29 +6970,29 @@
       </c>
       <c r="K140" s="12"/>
     </row>
-    <row r="141" ht="36.75" spans="1:11">
+    <row r="141" spans="1:11" ht="36">
       <c r="A141" s="2"/>
       <c r="B141" s="7">
-        <f>ROW(B141)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>139</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>153</v>
       </c>
       <c r="D141" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="G141" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>579</v>
-      </c>
-      <c r="E141" s="10" t="s">
-        <v>580</v>
-      </c>
-      <c r="F141" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="G141" s="10" t="s">
-        <v>582</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>583</v>
       </c>
       <c r="I141" s="13" t="s">
         <v>159</v>
@@ -7616,29 +7002,29 @@
       </c>
       <c r="K141" s="9"/>
     </row>
-    <row r="142" ht="15.75" spans="1:11">
+    <row r="142" spans="1:11">
       <c r="A142" s="2"/>
       <c r="B142" s="7">
-        <f>ROW(B142)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F142" s="12" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I142" s="13" t="s">
         <v>159</v>
@@ -7648,29 +7034,29 @@
       </c>
       <c r="K142" s="12"/>
     </row>
-    <row r="143" ht="48.75" spans="1:11">
+    <row r="143" spans="1:11" ht="48">
       <c r="A143" s="2"/>
       <c r="B143" s="7">
-        <f>ROW(B143)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>141</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>159</v>
@@ -7680,26 +7066,26 @@
       </c>
       <c r="K143" s="9"/>
     </row>
-    <row r="144" ht="15.75" spans="1:11">
+    <row r="144" spans="1:11">
       <c r="A144" s="2"/>
       <c r="B144" s="7">
-        <f>ROW(B144)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>142</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D144" s="12" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F144" s="12" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="G144" s="13" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="H144" s="12" t="s">
         <v>170</v>
@@ -7712,124 +7098,124 @@
       </c>
       <c r="K144" s="12"/>
     </row>
-    <row r="145" ht="36.75" spans="1:11">
+    <row r="145" spans="1:11" ht="36">
       <c r="A145" s="2"/>
       <c r="B145" s="7">
-        <f>ROW(B145)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>143</v>
       </c>
       <c r="C145" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="E145" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="G145" s="10" t="s">
         <v>597</v>
       </c>
-      <c r="D145" s="9" t="s">
+      <c r="H145" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="E145" s="10" t="s">
+      <c r="I145" s="10" t="s">
         <v>599</v>
       </c>
-      <c r="F145" s="9" t="s">
-        <v>600</v>
-      </c>
-      <c r="G145" s="10" t="s">
-        <v>601</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="I145" s="10" t="s">
-        <v>603</v>
-      </c>
       <c r="J145" s="9">
         <v>1</v>
       </c>
       <c r="K145" s="9"/>
     </row>
-    <row r="146" ht="15.75" spans="1:11">
+    <row r="146" spans="1:11">
       <c r="A146" s="2"/>
       <c r="B146" s="7">
-        <f>ROW(B146)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>144</v>
       </c>
       <c r="C146" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>602</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="G146" s="13" t="s">
         <v>604</v>
       </c>
-      <c r="D146" s="12" t="s">
+      <c r="H146" s="12" t="s">
         <v>605</v>
       </c>
-      <c r="E146" s="13" t="s">
+      <c r="I146" s="13" t="s">
         <v>606</v>
-      </c>
-      <c r="F146" s="12" t="s">
-        <v>607</v>
-      </c>
-      <c r="G146" s="13" t="s">
-        <v>608</v>
-      </c>
-      <c r="H146" s="12" t="s">
-        <v>609</v>
-      </c>
-      <c r="I146" s="13" t="s">
-        <v>610</v>
       </c>
       <c r="J146" s="12">
         <v>2</v>
       </c>
       <c r="K146" s="12"/>
     </row>
-    <row r="147" ht="36.75" spans="1:11">
+    <row r="147" spans="1:11" ht="36">
       <c r="A147" s="2"/>
       <c r="B147" s="7">
-        <f>ROW(B147)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>145</v>
       </c>
       <c r="C147" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="E147" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="G147" s="10" t="s">
         <v>611</v>
       </c>
-      <c r="D147" s="9" t="s">
+      <c r="H147" s="9" t="s">
         <v>612</v>
       </c>
-      <c r="E147" s="10" t="s">
+      <c r="I147" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="J147" s="9">
+        <v>1</v>
+      </c>
+      <c r="K147" s="9"/>
+    </row>
+    <row r="148" spans="1:11">
+      <c r="B148" s="7">
+        <f t="shared" si="4"/>
+        <v>146</v>
+      </c>
+      <c r="C148" s="8" t="s">
         <v>613</v>
-      </c>
-      <c r="F147" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="G147" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="I147" s="10" t="s">
-        <v>603</v>
-      </c>
-      <c r="J147" s="9">
-        <v>1</v>
-      </c>
-      <c r="K147" s="9"/>
-    </row>
-    <row r="148" ht="24.75" spans="2:11">
-      <c r="B148" s="7">
-        <f>ROW(B148)-ROW($B$2)</f>
-        <v>146</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>617</v>
       </c>
       <c r="D148" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="H148" s="9" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="I148" s="10" t="s">
         <v>159</v>
@@ -7839,28 +7225,28 @@
       </c>
       <c r="K148" s="9"/>
     </row>
-    <row r="149" ht="26.25" spans="2:11">
+    <row r="149" spans="1:11" ht="27.6">
       <c r="B149" s="7">
-        <f>ROW(B149)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>147</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D149" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F149" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="I149" s="10" t="s">
         <v>159</v>
@@ -7868,32 +7254,32 @@
       <c r="J149" s="9">
         <v>1</v>
       </c>
-      <c r="K149" s="18" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="150" ht="36.75" spans="2:11">
+      <c r="K149" s="17" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="36">
       <c r="B150" s="7">
-        <f>ROW(B150)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>148</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D150" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="F150" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="H150" s="12" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="I150" s="13" t="s">
         <v>159</v>
@@ -7903,28 +7289,28 @@
       </c>
       <c r="K150" s="12"/>
     </row>
-    <row r="151" ht="24.75" spans="2:11">
+    <row r="151" spans="1:11" ht="24">
       <c r="B151" s="7">
-        <f>ROW(B151)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>149</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D151" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="F151" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="H151" s="12" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="I151" s="13" t="s">
         <v>159</v>
@@ -7934,19 +7320,19 @@
       </c>
       <c r="K151" s="12"/>
     </row>
-    <row r="152" ht="24.75" spans="2:11">
+    <row r="152" spans="1:11" ht="36">
       <c r="B152" s="7">
-        <f>ROW(B152)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D152" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E152" s="13" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="F152" s="12" t="s">
         <v>34</v>
@@ -7959,32 +7345,32 @@
       <c r="J152" s="12">
         <v>1</v>
       </c>
-      <c r="K152" s="18" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="153" ht="24.75" spans="2:11">
+      <c r="K152" s="17" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="24">
       <c r="B153" s="7">
-        <f>ROW(B153)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>151</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D153" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="F153" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="H153" s="12" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="I153" s="13" t="s">
         <v>159</v>
@@ -7992,23 +7378,23 @@
       <c r="J153" s="12">
         <v>1</v>
       </c>
-      <c r="K153" s="18" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="154" ht="24.75" spans="2:11">
+      <c r="K153" s="17" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
       <c r="B154" s="7">
-        <f>ROW(B154)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>152</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D154" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="F154" s="12" t="s">
         <v>34</v>
@@ -8017,7 +7403,7 @@
         <v>8900</v>
       </c>
       <c r="H154" s="12" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="I154" s="13" t="s">
         <v>159</v>
@@ -8033,6 +7419,5 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>